--- a/Anjoman accounting - refined.xlsx
+++ b/Anjoman accounting - refined.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R621e85199394451b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly report" sheetId="2" r:id="R41bd8fea9b7444b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project report" sheetId="3" r:id="R63918496dd90466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category report" sheetId="4" r:id="Rf8143bc5ab754df7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original reconciliation" sheetId="5" r:id="R166bcfe4b2d74899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="6" r:id="Rbbbfb1c81c8c43d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="7" r:id="R07b112a0040647fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review items" sheetId="8" r:id="Rcb8b6de95459412f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence register" sheetId="9" r:id="R7216c32d89784530"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram messages" sheetId="10" r:id="Rf8489855825343f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original records" sheetId="11" r:id="R9f51b01d86784201"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="12" r:id="R502a4171d7994c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4a9f4271ec614551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly report" sheetId="2" r:id="R63cce25b3d4c4c0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project report" sheetId="3" r:id="Rb430486f56924b5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category report" sheetId="4" r:id="R227ce80cdd234da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructor payments" sheetId="5" r:id="R101d2ef863814210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original reconciliation" sheetId="6" r:id="R4bfe70809c4e4662"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="7" r:id="Rd5c3ba573aa249db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="8" r:id="R858a50cfac1d461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review items" sheetId="9" r:id="R3518424ddf3d4f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence register" sheetId="10" r:id="Re33b57dd606547a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram messages" sheetId="11" r:id="R172e6d085a944565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original records" sheetId="12" r:id="Rae202dfdac2b4cb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="13" r:id="R81e80365f50b4c62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -79,7 +80,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -96,6 +97,11 @@
         <x:fgColor rgb="FFEDF2F7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -109,7 +115,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -188,6 +194,9 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -196,6 +205,9 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -462,7 +474,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R543c03a89aff4dd1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R87bb17e6ce894254"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -484,7 +496,27 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="TelegrammessagesTable" displayName="TelegrammessagesTable" ref="A4:G192" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="EvidenceregisterTable" displayName="EvidenceregisterTable" ref="A4:K82" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:K82"/>
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="Source ID"/>
+    <x:tableColumn id="2" name="Repository file"/>
+    <x:tableColumn id="3" name="File type"/>
+    <x:tableColumn id="4" name="Bytes"/>
+    <x:tableColumn id="5" name="SHA-256"/>
+    <x:tableColumn id="6" name="Read status"/>
+    <x:tableColumn id="7" name="Ledger IDs"/>
+    <x:tableColumn id="8" name="Message IDs"/>
+    <x:tableColumn id="9" name="Treatment"/>
+    <x:tableColumn id="10" name="Notes"/>
+    <x:tableColumn id="11" name="GitHub source snapshot"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TelegrammessagesTable" displayName="TelegrammessagesTable" ref="A4:G192" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:G192"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Message ID"/>
@@ -499,8 +531,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="OriginalrecordsTable" displayName="OriginalrecordsTable" ref="A4:E3038" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="OriginalrecordsTable" displayName="OriginalrecordsTable" ref="A4:E3038" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:E3038"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Workbook"/>
@@ -513,9 +545,9 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="MethodologyTable" displayName="MethodologyTable" ref="A4:B27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:B27"/>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="MethodologyTable" displayName="MethodologyTable" ref="A4:B30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:B30"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Topic"/>
     <x:tableColumn id="2" name="Policy"/>
@@ -540,8 +572,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ProjectreportTable" displayName="ProjectreportTable" ref="A4:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:E18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ProjectreportTable" displayName="ProjectreportTable" ref="A4:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:E16"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Project"/>
     <x:tableColumn id="2" name="Receipts (toman)"/>
@@ -568,6 +600,26 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="InstructorpaymentsTable" displayName="InstructorpaymentsTable" ref="A4:K9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:K9"/>
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="Transaction ID"/>
+    <x:tableColumn id="2" name="Instructor beneficiary"/>
+    <x:tableColumn id="3" name="Bank account payee"/>
+    <x:tableColumn id="4" name="Course"/>
+    <x:tableColumn id="5" name="Jalali date"/>
+    <x:tableColumn id="6" name="Gregorian date"/>
+    <x:tableColumn id="7" name="Amount (toman)"/>
+    <x:tableColumn id="8" name="User-provided card ending (not printed)"/>
+    <x:tableColumn id="9" name="Matching basis"/>
+    <x:tableColumn id="10" name="Settlement basis"/>
+    <x:tableColumn id="11" name="Source reference"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="OriginalreconciliationTable" displayName="OriginalreconciliationTable" ref="A4:F47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:F47"/>
   <x:tableColumns count="6">
@@ -582,7 +634,7 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TransactionsTable" displayName="TransactionsTable" ref="A4:Y99" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:Y99"/>
   <x:tableColumns count="25">
@@ -616,8 +668,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="InvoicesTable" displayName="InvoicesTable" ref="A4:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="InvoicesTable" displayName="InvoicesTable" ref="A4:K20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:K20"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="ID"/>
@@ -636,9 +688,9 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ReviewitemsTable" displayName="ReviewitemsTable" ref="A4:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H18"/>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="ReviewitemsTable" displayName="ReviewitemsTable" ref="A4:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H19"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Issue ID"/>
     <x:tableColumn id="2" name="Priority"/>
@@ -648,26 +700,6 @@
     <x:tableColumn id="6" name="Transaction IDs"/>
     <x:tableColumn id="7" name="Required action"/>
     <x:tableColumn id="8" name="Source reference"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="EvidenceregisterTable" displayName="EvidenceregisterTable" ref="A4:K82" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:K82"/>
-  <x:tableColumns count="11">
-    <x:tableColumn id="1" name="Source ID"/>
-    <x:tableColumn id="2" name="Repository file"/>
-    <x:tableColumn id="3" name="File type"/>
-    <x:tableColumn id="4" name="Bytes"/>
-    <x:tableColumn id="5" name="SHA-256"/>
-    <x:tableColumn id="6" name="Read status"/>
-    <x:tableColumn id="7" name="Ledger IDs"/>
-    <x:tableColumn id="8" name="Message IDs"/>
-    <x:tableColumn id="9" name="Treatment"/>
-    <x:tableColumn id="10" name="Notes"/>
-    <x:tableColumn id="11" name="GitHub source snapshot"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -881,7 +913,7 @@
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
         <x:v>Anjoman financial report | 10 October 2026</x:v>
       </x:c>
@@ -922,7 +954,7 @@
       </x:c>
       <x:c r="B6" s="19" t="n">
         <x:f>SUM('Transactions'!$X$5:$X$99)</x:f>
-        <x:v>41121825</x:v>
+        <x:v>99085195</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
         <x:v>Payments with status Supported</x:v>
@@ -934,7 +966,7 @@
       </x:c>
       <x:c r="B7" s="20" t="n">
         <x:f>B5-B6</x:f>
-        <x:v>71430175</x:v>
+        <x:v>13466805</x:v>
       </x:c>
       <x:c r="C7" s="17" t="str">
         <x:v>Receipts less payments; excludes opening balance</x:v>
@@ -970,7 +1002,7 @@
       </x:c>
       <x:c r="B10" s="19" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$N$5:$N$99,"Review",'Transactions'!$E$5:$E$99,"Payment")</x:f>
-        <x:v>54508973.9</x:v>
+        <x:v>8334723.9</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
         <x:v>Excluded from supported totals</x:v>
@@ -982,7 +1014,7 @@
       </x:c>
       <x:c r="B11" s="19" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$N$5:$N$99,"Review",'Transactions'!$E$5:$E$99,"Unknown")</x:f>
-        <x:v>2101220</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
         <x:v>Direction unresolved; excluded from totals</x:v>
@@ -1006,7 +1038,7 @@
       </x:c>
       <x:c r="B13" s="19" t="n">
         <x:f>SUMIFS('Invoices'!$F$5:$F$20,'Invoices'!$I$5:$I$20,"Unmatched invoice")</x:f>
-        <x:v>16404600</x:v>
+        <x:v>6416700</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
         <x:v>Not assumed paid or automatically booked as a liability</x:v>
@@ -1030,7 +1062,7 @@
       </x:c>
       <x:c r="B15" s="21" t="n">
         <x:f>COUNTIFS('Transactions'!$N$5:$N$99,"Supported",'Transactions'!$E$5:$E$99,"Receipt")+COUNTIFS('Transactions'!$N$5:$N$99,"Supported",'Transactions'!$E$5:$E$99,"Payment")</x:f>
-        <x:v>47</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
         <x:v>Number of Supported receipt/payment records</x:v>
@@ -1042,7 +1074,7 @@
       </x:c>
       <x:c r="B16" s="21" t="n">
         <x:f>COUNTIFS('Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
         <x:v>Number of ledger records marked Review</x:v>
@@ -1152,18 +1184,2725 @@
         <x:v>Included from original ledger / treasurer statement; bank deposit evidence pending</x:v>
       </x:c>
     </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="27" t="str">
+        <x:v>Summer School 1405</x:v>
+      </x:c>
+      <x:c r="B32" s="27" t="str">
+        <x:v>Matched amount / count</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="str">
+        <x:v>User-confirmed allocation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="29" t="str">
+        <x:v>Instructor fees identified</x:v>
+      </x:c>
+      <x:c r="B33" s="30" t="n">
+        <x:v>11500000</x:v>
+      </x:c>
+      <x:c r="C33" s="29" t="str">
+        <x:v>Five payments identified; user stated six, remaining payment unassigned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="29" t="str">
+        <x:v>Intro-event sticker packs</x:v>
+      </x:c>
+      <x:c r="B34" s="30" t="n">
+        <x:v>950000</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="str">
+        <x:v>Zahra Amiri payment; excluded from instructor fees</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
+    <x:mergeCell ref="A2:C2"/>
     <x:mergeCell ref="A23:C25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3db697ea9dcf4040"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9ed71cc8aab4345"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFEDF2F7"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="85" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="25" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="110" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="120" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+      <x:c r="C1" s="33"/>
+      <x:c r="D1" s="33"/>
+      <x:c r="E1" s="33"/>
+      <x:c r="F1" s="33"/>
+      <x:c r="G1" s="33"/>
+      <x:c r="H1" s="33"/>
+      <x:c r="I1" s="33"/>
+      <x:c r="J1" s="33"/>
+      <x:c r="K1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
+        <x:v>Source inventory and extraction coverage</x:v>
+      </x:c>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
+      <x:c r="G2" s="33"/>
+      <x:c r="H2" s="33"/>
+      <x:c r="I2" s="33"/>
+      <x:c r="J2" s="33"/>
+      <x:c r="K2" s="33"/>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
+      <x:c r="H3" s="33"/>
+      <x:c r="I3" s="33"/>
+      <x:c r="J3" s="33"/>
+      <x:c r="K3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="7" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>Repository file</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>File type</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>Bytes</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>SHA-256</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>Read status</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>Ledger IDs</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
+        <x:v>Message IDs</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str">
+        <x:v>Treatment</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="K4" s="7" t="str">
+        <x:v>GitHub source snapshot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="31" t="str">
+        <x:v>SRC001</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
+        <x:v>Anjoman accounting - refined.xlsx</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>xlsx</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="n">
+        <x:v>63212</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
+        <x:v>d77c540aba056a0bce5abaef9ac974fbf1f91ead2f0ea55d7ac1bc96b94a2228</x:v>
+      </x:c>
+      <x:c r="F5" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G5" s="31" t="str"/>
+      <x:c r="H5" s="31" t="str"/>
+      <x:c r="I5" s="31" t="str">
+        <x:v>Context only</x:v>
+      </x:c>
+      <x:c r="J5" s="31" t="str">
+        <x:v>Derived copy of مجموع plus TX-00044..48 proposals. Errors flagged in ISS012.</x:v>
+      </x:c>
+      <x:c r="K5" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/Anjoman%20accounting%20-%20refined.xlsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" hidden="0" customHeight="1">
+      <x:c r="A6" s="31" t="str">
+        <x:v>SRC002</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="str">
+        <x:v>Anjoman accounting.xlsx</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>xlsx</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="n">
+        <x:v>130028</x:v>
+      </x:c>
+      <x:c r="E6" s="31" t="str">
+        <x:v>5701b246ebee5bd5db7fc022de097f47c34354e420bb59f08f4f2fc74a0bfcf0</x:v>
+      </x:c>
+      <x:c r="F6" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G6" s="31" t="str">
+        <x:v>TX0001, TX0013, TX0014, TX0016, TX0017, TX0045, TX0093, TX0095</x:v>
+      </x:c>
+      <x:c r="H6" s="31" t="str"/>
+      <x:c r="I6" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J6" s="31" t="str">
+        <x:v>Every مجموع row is mapped in original_ledger_reconciliation. The مرداد and شهریور sheets are subsets.</x:v>
+      </x:c>
+      <x:c r="K6" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/Anjoman%20accounting.xlsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="31" t="str">
+        <x:v>SRC003</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="str">
+        <x:v>invoice-61150.pdf</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>pdf</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="n">
+        <x:v>153863</x:v>
+      </x:c>
+      <x:c r="E7" s="31" t="str">
+        <x:v>06626a709e2a23bc59d3a5185c64e0a85b64e59ccf244cbb3b0867344bc07b57</x:v>
+      </x:c>
+      <x:c r="F7" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G7" s="31" t="str">
+        <x:v>TX0082</x:v>
+      </x:c>
+      <x:c r="H7" s="31" t="str"/>
+      <x:c r="I7" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J7" s="31" t="str">
+        <x:v>Invoice only.</x:v>
+      </x:c>
+      <x:c r="K7" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/invoice-61150.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="31" t="str">
+        <x:v>SRC004</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="str">
+        <x:v>physics_intro full report.pdf</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>pdf</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="n">
+        <x:v>52198</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="str">
+        <x:v>993061f6f022016308bbd6585c6ae0e8a2b67575c39f21e740659cc25da7dc70</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="str">
+        <x:v>TX0094</x:v>
+      </x:c>
+      <x:c r="H8" s="31" t="str"/>
+      <x:c r="I8" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="str">
+        <x:v>Summary only.</x:v>
+      </x:c>
+      <x:c r="K8" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/physics_intro%20full%20report.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="31" t="str">
+        <x:v>SRC005</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>recipts/photo_10_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="n">
+        <x:v>49752</x:v>
+      </x:c>
+      <x:c r="E9" s="31" t="str">
+        <x:v>b424f88e66186c7fdfcd19043e65ade1aef245c80f81328c53bd4c1354047ea3</x:v>
+      </x:c>
+      <x:c r="F9" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G9" s="31" t="str">
+        <x:v>TX0090</x:v>
+      </x:c>
+      <x:c r="H9" s="31" t="str"/>
+      <x:c r="I9" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="str"/>
+      <x:c r="K9" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_10_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="31" t="str">
+        <x:v>SRC006</x:v>
+      </x:c>
+      <x:c r="B10" s="31" t="str">
+        <x:v>recipts/photo_11_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="n">
+        <x:v>31986</x:v>
+      </x:c>
+      <x:c r="E10" s="31" t="str">
+        <x:v>4b6a665eaaa0ff0a14e2f665cd7ef1480d78c90efa576fa0f1cf910698baacc6</x:v>
+      </x:c>
+      <x:c r="F10" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G10" s="31" t="str">
+        <x:v>TX0091</x:v>
+      </x:c>
+      <x:c r="H10" s="31" t="str"/>
+      <x:c r="I10" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="str"/>
+      <x:c r="K10" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_11_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="31" t="str">
+        <x:v>SRC007</x:v>
+      </x:c>
+      <x:c r="B11" s="31" t="str">
+        <x:v>recipts/photo_12_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="n">
+        <x:v>50026</x:v>
+      </x:c>
+      <x:c r="E11" s="31" t="str">
+        <x:v>77e952d643e05bc03bdd136daa677561a5610e8049fb8d8aedfc24280909d917</x:v>
+      </x:c>
+      <x:c r="F11" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G11" s="31" t="str">
+        <x:v>TX0092</x:v>
+      </x:c>
+      <x:c r="H11" s="31" t="str"/>
+      <x:c r="I11" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="str"/>
+      <x:c r="K11" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_12_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="31" t="str">
+        <x:v>SRC008</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="str">
+        <x:v>recipts/photo_1_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="n">
+        <x:v>58923</x:v>
+      </x:c>
+      <x:c r="E12" s="31" t="str">
+        <x:v>9b398cb3fd79cacf08994828e10209d3739b9ec072ff9dbdb29e456ad1a29262</x:v>
+      </x:c>
+      <x:c r="F12" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G12" s="31" t="str">
+        <x:v>TX0083</x:v>
+      </x:c>
+      <x:c r="H12" s="31" t="str"/>
+      <x:c r="I12" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="str"/>
+      <x:c r="K12" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_1_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="31" t="str">
+        <x:v>SRC009</x:v>
+      </x:c>
+      <x:c r="B13" s="31" t="str">
+        <x:v>recipts/photo_1_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="n">
+        <x:v>44693</x:v>
+      </x:c>
+      <x:c r="E13" s="31" t="str">
+        <x:v>a50d13d6abcf5b4aacd05fa7fa773b5c01a6d2739577691d719c1bf334433b52</x:v>
+      </x:c>
+      <x:c r="F13" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G13" s="31" t="str">
+        <x:v>TX0022</x:v>
+      </x:c>
+      <x:c r="H13" s="31" t="str"/>
+      <x:c r="I13" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="str">
+        <x:v>Duplicate of photo_16.</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_1_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="31" t="str">
+        <x:v>SRC010</x:v>
+      </x:c>
+      <x:c r="B14" s="31" t="str">
+        <x:v>recipts/photo_2026-10-10_12-16-28.jpg</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="n">
+        <x:v>160143</x:v>
+      </x:c>
+      <x:c r="E14" s="31" t="str">
+        <x:v>99a77eab001c2f3c72a639a7ec75b0a97bb90c5e5e244a8cf575d61107bedcc9</x:v>
+      </x:c>
+      <x:c r="F14" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G14" s="31" t="str">
+        <x:v>TX0089</x:v>
+      </x:c>
+      <x:c r="H14" s="31" t="str"/>
+      <x:c r="I14" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="str">
+        <x:v>Invoice only.</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_2026-10-10_12-16-28.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="31" t="str">
+        <x:v>SRC011</x:v>
+      </x:c>
+      <x:c r="B15" s="31" t="str">
+        <x:v>recipts/photo_2_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C15" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="n">
+        <x:v>57944</x:v>
+      </x:c>
+      <x:c r="E15" s="31" t="str">
+        <x:v>5b8abe4d9a9d270a1a5cb0583fbb4ff555d551b16023d63343affe459769150f</x:v>
+      </x:c>
+      <x:c r="F15" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G15" s="31" t="str">
+        <x:v>TX0084</x:v>
+      </x:c>
+      <x:c r="H15" s="31" t="str"/>
+      <x:c r="I15" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="str"/>
+      <x:c r="K15" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_2_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="31" t="str">
+        <x:v>SRC012</x:v>
+      </x:c>
+      <x:c r="B16" s="31" t="str">
+        <x:v>recipts/photo_2_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="n">
+        <x:v>39945</x:v>
+      </x:c>
+      <x:c r="E16" s="31" t="str">
+        <x:v>6f9a6e2d264b36faa78b41d76c6a1448122e4a243a95c361fd1281ae2bc47e4a</x:v>
+      </x:c>
+      <x:c r="F16" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G16" s="31" t="str">
+        <x:v>TX0076</x:v>
+      </x:c>
+      <x:c r="H16" s="31" t="str"/>
+      <x:c r="I16" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="str"/>
+      <x:c r="K16" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_2_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="31" t="str">
+        <x:v>SRC013</x:v>
+      </x:c>
+      <x:c r="B17" s="31" t="str">
+        <x:v>recipts/photo_3_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="n">
+        <x:v>48603</x:v>
+      </x:c>
+      <x:c r="E17" s="31" t="str">
+        <x:v>5e9f3828411eb9b655e40edf6506756897d37de7bd8a35ea38c9eee80d9742c0</x:v>
+      </x:c>
+      <x:c r="F17" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G17" s="31" t="str">
+        <x:v>TX0085</x:v>
+      </x:c>
+      <x:c r="H17" s="31" t="str"/>
+      <x:c r="I17" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="str"/>
+      <x:c r="K17" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_3_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="31" t="str">
+        <x:v>SRC014</x:v>
+      </x:c>
+      <x:c r="B18" s="31" t="str">
+        <x:v>recipts/photo_3_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="n">
+        <x:v>45037</x:v>
+      </x:c>
+      <x:c r="E18" s="31" t="str">
+        <x:v>89cfe54d6ab70d44461da04c4318c4b7a11f78947d9a61bda0e7266fbcc3bdab</x:v>
+      </x:c>
+      <x:c r="F18" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G18" s="31" t="str">
+        <x:v>TX0075</x:v>
+      </x:c>
+      <x:c r="H18" s="31" t="str"/>
+      <x:c r="I18" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="str"/>
+      <x:c r="K18" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_3_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="31" t="str">
+        <x:v>SRC015</x:v>
+      </x:c>
+      <x:c r="B19" s="31" t="str">
+        <x:v>recipts/photo_4_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="n">
+        <x:v>49704</x:v>
+      </x:c>
+      <x:c r="E19" s="31" t="str">
+        <x:v>da2ff247cc7b5f3f295635d3052d3d599eebc0806a657613e584d1cce0639769</x:v>
+      </x:c>
+      <x:c r="F19" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G19" s="31" t="str">
+        <x:v>TX0081</x:v>
+      </x:c>
+      <x:c r="H19" s="31" t="str"/>
+      <x:c r="I19" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="str"/>
+      <x:c r="K19" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_4_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="31" t="str">
+        <x:v>SRC016</x:v>
+      </x:c>
+      <x:c r="B20" s="31" t="str">
+        <x:v>recipts/photo_4_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="n">
+        <x:v>44990</x:v>
+      </x:c>
+      <x:c r="E20" s="31" t="str">
+        <x:v>44a438cc79650702edcbab92c8d1b6d5bc74008f068089c928f463f0657d2162</x:v>
+      </x:c>
+      <x:c r="F20" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G20" s="31" t="str">
+        <x:v>TX0043</x:v>
+      </x:c>
+      <x:c r="H20" s="31" t="str"/>
+      <x:c r="I20" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="str"/>
+      <x:c r="K20" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_4_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="31" t="str">
+        <x:v>SRC017</x:v>
+      </x:c>
+      <x:c r="B21" s="31" t="str">
+        <x:v>recipts/photo_5_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C21" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="n">
+        <x:v>49513</x:v>
+      </x:c>
+      <x:c r="E21" s="31" t="str">
+        <x:v>556c6c35f9ce9e0fb5845f3b0d5b9a1b2696d7e1377af7f4c39d6a23e4360af2</x:v>
+      </x:c>
+      <x:c r="F21" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G21" s="31" t="str">
+        <x:v>TX0080</x:v>
+      </x:c>
+      <x:c r="H21" s="31" t="str"/>
+      <x:c r="I21" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="str"/>
+      <x:c r="K21" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_5_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="31" t="str">
+        <x:v>SRC018</x:v>
+      </x:c>
+      <x:c r="B22" s="31" t="str">
+        <x:v>recipts/photo_5_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D22" s="31" t="n">
+        <x:v>39739</x:v>
+      </x:c>
+      <x:c r="E22" s="31" t="str">
+        <x:v>63f59a169b5a2bb5dd1bc0587d75173d88da586a0b9b30cbe7effcd5b676c67c</x:v>
+      </x:c>
+      <x:c r="F22" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G22" s="31" t="str">
+        <x:v>TX0077</x:v>
+      </x:c>
+      <x:c r="H22" s="31" t="str"/>
+      <x:c r="I22" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="str"/>
+      <x:c r="K22" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_5_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="31" t="str">
+        <x:v>SRC019</x:v>
+      </x:c>
+      <x:c r="B23" s="31" t="str">
+        <x:v>recipts/photo_6_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="n">
+        <x:v>57246</x:v>
+      </x:c>
+      <x:c r="E23" s="31" t="str">
+        <x:v>3e2419ef0ccbe67c3e775ffb4f32e97152e3923bab3c3760071727253938e142</x:v>
+      </x:c>
+      <x:c r="F23" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G23" s="31" t="str">
+        <x:v>TX0088</x:v>
+      </x:c>
+      <x:c r="H23" s="31" t="str"/>
+      <x:c r="I23" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="str"/>
+      <x:c r="K23" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_6_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="31" t="str">
+        <x:v>SRC020</x:v>
+      </x:c>
+      <x:c r="B24" s="31" t="str">
+        <x:v>recipts/photo_6_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C24" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="n">
+        <x:v>41211</x:v>
+      </x:c>
+      <x:c r="E24" s="31" t="str">
+        <x:v>2a51ef05147371b78e220f491a2c3e82578cb8a9cc8a65128cd503f3f2eaf183</x:v>
+      </x:c>
+      <x:c r="F24" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G24" s="31" t="str">
+        <x:v>TX0061</x:v>
+      </x:c>
+      <x:c r="H24" s="31" t="str"/>
+      <x:c r="I24" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="str"/>
+      <x:c r="K24" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_6_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="31" t="str">
+        <x:v>SRC021</x:v>
+      </x:c>
+      <x:c r="B25" s="31" t="str">
+        <x:v>recipts/photo_7_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C25" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D25" s="31" t="n">
+        <x:v>49510</x:v>
+      </x:c>
+      <x:c r="E25" s="31" t="str">
+        <x:v>805ebbd2b231c7cf1c2858b5a056938b59dd5c7ccaed44d74c4edc20f4b57ce2</x:v>
+      </x:c>
+      <x:c r="F25" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G25" s="31" t="str">
+        <x:v>TX0086</x:v>
+      </x:c>
+      <x:c r="H25" s="31" t="str"/>
+      <x:c r="I25" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="str"/>
+      <x:c r="K25" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_7_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="31" t="str">
+        <x:v>SRC022</x:v>
+      </x:c>
+      <x:c r="B26" s="31" t="str">
+        <x:v>recipts/photo_7_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C26" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D26" s="31" t="n">
+        <x:v>44918</x:v>
+      </x:c>
+      <x:c r="E26" s="31" t="str">
+        <x:v>1bfe3e9b9076ece14313b068bc35b4b58c247e5b9fbf0c8ac9d9161c5a1eab10</x:v>
+      </x:c>
+      <x:c r="F26" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G26" s="31" t="str">
+        <x:v>TX0079</x:v>
+      </x:c>
+      <x:c r="H26" s="31" t="str"/>
+      <x:c r="I26" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="str"/>
+      <x:c r="K26" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_7_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="31" t="str">
+        <x:v>SRC023</x:v>
+      </x:c>
+      <x:c r="B27" s="31" t="str">
+        <x:v>recipts/photo_8_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D27" s="31" t="n">
+        <x:v>48893</x:v>
+      </x:c>
+      <x:c r="E27" s="31" t="str">
+        <x:v>75fee797d13ddb85ea935721b36fb145c6c9fe6b2ea11406f10a551c57acac32</x:v>
+      </x:c>
+      <x:c r="F27" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G27" s="31" t="str">
+        <x:v>TX0087</x:v>
+      </x:c>
+      <x:c r="H27" s="31" t="str"/>
+      <x:c r="I27" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="str"/>
+      <x:c r="K27" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_8_2026-10-10_11-09-04.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="31" t="str">
+        <x:v>SRC024</x:v>
+      </x:c>
+      <x:c r="B28" s="31" t="str">
+        <x:v>recipts/photo_8_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+      <x:c r="C28" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D28" s="31" t="n">
+        <x:v>39907</x:v>
+      </x:c>
+      <x:c r="E28" s="31" t="str">
+        <x:v>ae9fe7eccdae6bf86a1de9ecb8dc330494dec3835c76a1f55a0dd695297689b8</x:v>
+      </x:c>
+      <x:c r="F28" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G28" s="31" t="str">
+        <x:v>TX0078</x:v>
+      </x:c>
+      <x:c r="H28" s="31" t="str"/>
+      <x:c r="I28" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="str"/>
+      <x:c r="K28" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_8_2026-10-10_14-07-27.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" hidden="0" customHeight="1">
+      <x:c r="A29" s="31" t="str">
+        <x:v>SRC025</x:v>
+      </x:c>
+      <x:c r="B29" s="31" t="str">
+        <x:v>telegram export/files/CamScanner 13-05-2026 12.43 (1).pdf</x:v>
+      </x:c>
+      <x:c r="C29" s="31" t="str">
+        <x:v>pdf</x:v>
+      </x:c>
+      <x:c r="D29" s="31" t="n">
+        <x:v>7377808</x:v>
+      </x:c>
+      <x:c r="E29" s="31" t="str">
+        <x:v>6710c8248b7f8f3fb3ccc8ef74c9e5f017aa69fcd6c02fb1e5e4f8d33d134b2b</x:v>
+      </x:c>
+      <x:c r="F29" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G29" s="31" t="str">
+        <x:v>TX0064, TX0065, TX0066, TX0067, TX0068, TX0069, TX0070, TX0071, TX0072, TX0073, TX0074</x:v>
+      </x:c>
+      <x:c r="H29" s="31" t="str">
+        <x:v>message124</x:v>
+      </x:c>
+      <x:c r="I29" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="str">
+        <x:v>11 pages = scan_pages_01-03, 04-06, 07-09, 10-11. Independent page review used.</x:v>
+      </x:c>
+      <x:c r="K29" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/CamScanner%2013-05-2026%2012.43%20(1).pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="31" t="str">
+        <x:v>SRC026</x:v>
+      </x:c>
+      <x:c r="B30" s="31" t="str">
+        <x:v>telegram export/files/dk-file-2025-10-16-14-43-08.pdf</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="str">
+        <x:v>pdf</x:v>
+      </x:c>
+      <x:c r="D30" s="31" t="n">
+        <x:v>326283</x:v>
+      </x:c>
+      <x:c r="E30" s="31" t="str">
+        <x:v>6e8ce528a639e8464eeb696a426eea1e00398cec8ff5e910340153fd01552139</x:v>
+      </x:c>
+      <x:c r="F30" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G30" s="31" t="str">
+        <x:v>TX0032</x:v>
+      </x:c>
+      <x:c r="H30" s="31" t="str">
+        <x:v>message66</x:v>
+      </x:c>
+      <x:c r="I30" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="str">
+        <x:v>INV001/002.</x:v>
+      </x:c>
+      <x:c r="K30" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/dk-file-2025-10-16-14-43-08.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="31" t="str">
+        <x:v>SRC027</x:v>
+      </x:c>
+      <x:c r="B31" s="31" t="str">
+        <x:v>telegram export/files/report_LaTeX.txt</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="str">
+        <x:v>txt</x:v>
+      </x:c>
+      <x:c r="D31" s="31" t="n">
+        <x:v>6858</x:v>
+      </x:c>
+      <x:c r="E31" s="31" t="str">
+        <x:v>31bbba72112289413c94d94087af8adf90da26ee8f61c7340c3042896a931038</x:v>
+      </x:c>
+      <x:c r="F31" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G31" s="31" t="str">
+        <x:v>TX0001</x:v>
+      </x:c>
+      <x:c r="H31" s="31" t="str">
+        <x:v>message7</x:v>
+      </x:c>
+      <x:c r="I31" s="31" t="str">
+        <x:v>Context only</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="str">
+        <x:v>Allocation control.</x:v>
+      </x:c>
+      <x:c r="K31" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/report_LaTeX.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="31" t="str">
+        <x:v>SRC028</x:v>
+      </x:c>
+      <x:c r="B32" s="31" t="str">
+        <x:v>telegram export/files/report_Mathematica.txt</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="str">
+        <x:v>txt</x:v>
+      </x:c>
+      <x:c r="D32" s="31" t="n">
+        <x:v>5711</x:v>
+      </x:c>
+      <x:c r="E32" s="31" t="str">
+        <x:v>63b8607b7119b6c9b55fc9d03c59faa2b7722b6d12fd9ec43f51827b9048224b</x:v>
+      </x:c>
+      <x:c r="F32" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G32" s="31" t="str">
+        <x:v>TX0001</x:v>
+      </x:c>
+      <x:c r="H32" s="31" t="str">
+        <x:v>message8</x:v>
+      </x:c>
+      <x:c r="I32" s="31" t="str">
+        <x:v>Context only</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="str">
+        <x:v>Allocation control.</x:v>
+      </x:c>
+      <x:c r="K32" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/report_Mathematica.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="31" t="str">
+        <x:v>SRC029</x:v>
+      </x:c>
+      <x:c r="B33" s="31" t="str">
+        <x:v>telegram export/files/report_Python.txt</x:v>
+      </x:c>
+      <x:c r="C33" s="31" t="str">
+        <x:v>txt</x:v>
+      </x:c>
+      <x:c r="D33" s="31" t="n">
+        <x:v>6285</x:v>
+      </x:c>
+      <x:c r="E33" s="31" t="str">
+        <x:v>8ff96f7277fc07553a6ac271872413e31de240ec23f25984e53ebd6202e8e6b6</x:v>
+      </x:c>
+      <x:c r="F33" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G33" s="31" t="str">
+        <x:v>TX0001</x:v>
+      </x:c>
+      <x:c r="H33" s="31" t="str">
+        <x:v>message6</x:v>
+      </x:c>
+      <x:c r="I33" s="31" t="str">
+        <x:v>Context only</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="str">
+        <x:v>Allocation control; contains personal data.</x:v>
+      </x:c>
+      <x:c r="K33" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/report_Python.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="36" hidden="0" customHeight="1">
+      <x:c r="A34" s="31" t="str">
+        <x:v>SRC030</x:v>
+      </x:c>
+      <x:c r="B34" s="31" t="str">
+        <x:v>telegram export/messages.html</x:v>
+      </x:c>
+      <x:c r="C34" s="31" t="str">
+        <x:v>html</x:v>
+      </x:c>
+      <x:c r="D34" s="31" t="n">
+        <x:v>116651</x:v>
+      </x:c>
+      <x:c r="E34" s="31" t="str">
+        <x:v>4ac19a5c1db97672da0893539fa00e862d2f986c2b12a577bfe816891b24e7e4</x:v>
+      </x:c>
+      <x:c r="F34" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G34" s="31" t="str">
+        <x:v>TX0008, TX0018, TX0029, TX0030, TX0035, TX0036, TX0039, TX0040, TX0041, TX0047, TX0048, TX0049, TX0058</x:v>
+      </x:c>
+      <x:c r="H34" s="31" t="str"/>
+      <x:c r="I34" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="str">
+        <x:v>All financial messages were mapped. Non-financial chat is context only (commitments in project_notes).</x:v>
+      </x:c>
+      <x:c r="K34" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/messages.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="31" t="str">
+        <x:v>SRC031</x:v>
+      </x:c>
+      <x:c r="B35" s="31" t="str">
+        <x:v>telegram export/photos/photo_10@15-08-2025_18-28-22.jpg</x:v>
+      </x:c>
+      <x:c r="C35" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D35" s="31" t="n">
+        <x:v>74672</x:v>
+      </x:c>
+      <x:c r="E35" s="31" t="str">
+        <x:v>28455c00bd0229cddc0b8874a8b025fc25700f4e553b6c67bdfc9082b2cad0b7</x:v>
+      </x:c>
+      <x:c r="F35" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G35" s="31" t="str">
+        <x:v>TX0012</x:v>
+      </x:c>
+      <x:c r="H35" s="31" t="str">
+        <x:v>message47</x:v>
+      </x:c>
+      <x:c r="I35" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="str"/>
+      <x:c r="K35" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_10%4015-08-2025_18-28-22.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="31" t="str">
+        <x:v>SRC032</x:v>
+      </x:c>
+      <x:c r="B36" s="31" t="str">
+        <x:v>telegram export/photos/photo_11@04-09-2025_14-05-56.jpg</x:v>
+      </x:c>
+      <x:c r="C36" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D36" s="31" t="n">
+        <x:v>56585</x:v>
+      </x:c>
+      <x:c r="E36" s="31" t="str">
+        <x:v>dba6c9549b471a9a2d016b29b57970c53eedf21a4f80e3a841478cf04784555e</x:v>
+      </x:c>
+      <x:c r="F36" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G36" s="31" t="str">
+        <x:v>TX0015</x:v>
+      </x:c>
+      <x:c r="H36" s="31" t="str">
+        <x:v>message48</x:v>
+      </x:c>
+      <x:c r="I36" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="str"/>
+      <x:c r="K36" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_11%4004-09-2025_14-05-56.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="31" t="str">
+        <x:v>SRC033</x:v>
+      </x:c>
+      <x:c r="B37" s="31" t="str">
+        <x:v>telegram export/photos/photo_12@01-10-2025_18-02-44.jpg</x:v>
+      </x:c>
+      <x:c r="C37" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D37" s="31" t="n">
+        <x:v>48640</x:v>
+      </x:c>
+      <x:c r="E37" s="31" t="str">
+        <x:v>6295ac27d8bc4463d51132d3a86a8e01dc37946b107ee50d0c77ceffe9470b4c</x:v>
+      </x:c>
+      <x:c r="F37" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G37" s="31" t="str">
+        <x:v>TX0018</x:v>
+      </x:c>
+      <x:c r="H37" s="31" t="str">
+        <x:v>message51</x:v>
+      </x:c>
+      <x:c r="I37" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="str"/>
+      <x:c r="K37" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_12%4001-10-2025_18-02-44.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="31" t="str">
+        <x:v>SRC034</x:v>
+      </x:c>
+      <x:c r="B38" s="31" t="str">
+        <x:v>telegram export/photos/photo_13@12-10-2025_10-24-38.jpg</x:v>
+      </x:c>
+      <x:c r="C38" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D38" s="31" t="n">
+        <x:v>66592</x:v>
+      </x:c>
+      <x:c r="E38" s="31" t="str">
+        <x:v>6d79bcdee6b1e2fb274811a327e44deb472e519ef16ca2cb2633fddb9da7e083</x:v>
+      </x:c>
+      <x:c r="F38" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G38" s="31" t="str">
+        <x:v>TX0020</x:v>
+      </x:c>
+      <x:c r="H38" s="31" t="str">
+        <x:v>message61</x:v>
+      </x:c>
+      <x:c r="I38" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="str"/>
+      <x:c r="K38" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_13%4012-10-2025_10-24-38.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="31" t="str">
+        <x:v>SRC035</x:v>
+      </x:c>
+      <x:c r="B39" s="31" t="str">
+        <x:v>telegram export/photos/photo_14@15-10-2025_14-18-25.jpg</x:v>
+      </x:c>
+      <x:c r="C39" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D39" s="31" t="n">
+        <x:v>69226</x:v>
+      </x:c>
+      <x:c r="E39" s="31" t="str">
+        <x:v>b214b33a77c58bb0428ba09719496e21696b82ae4055292c9711694e4e16fd3b</x:v>
+      </x:c>
+      <x:c r="F39" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G39" s="31" t="str">
+        <x:v>TX0024</x:v>
+      </x:c>
+      <x:c r="H39" s="31" t="str">
+        <x:v>message62</x:v>
+      </x:c>
+      <x:c r="I39" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="str"/>
+      <x:c r="K39" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_14%4015-10-2025_14-18-25.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="31" t="str">
+        <x:v>SRC036</x:v>
+      </x:c>
+      <x:c r="B40" s="31" t="str">
+        <x:v>telegram export/photos/photo_15@15-10-2025_14-18-25.jpg</x:v>
+      </x:c>
+      <x:c r="C40" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D40" s="31" t="n">
+        <x:v>64998</x:v>
+      </x:c>
+      <x:c r="E40" s="31" t="str">
+        <x:v>f31ffa6bdd2395d18e073911daffc69b21952eaef6f5b1d6bcf7beacb8193f96</x:v>
+      </x:c>
+      <x:c r="F40" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G40" s="31" t="str">
+        <x:v>TX0019</x:v>
+      </x:c>
+      <x:c r="H40" s="31" t="str">
+        <x:v>message63</x:v>
+      </x:c>
+      <x:c r="I40" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="str"/>
+      <x:c r="K40" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_15%4015-10-2025_14-18-25.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="31" t="str">
+        <x:v>SRC037</x:v>
+      </x:c>
+      <x:c r="B41" s="31" t="str">
+        <x:v>telegram export/photos/photo_16@15-10-2025_14-18-26.jpg</x:v>
+      </x:c>
+      <x:c r="C41" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D41" s="31" t="n">
+        <x:v>68536</x:v>
+      </x:c>
+      <x:c r="E41" s="31" t="str">
+        <x:v>28db8e201da1e5584cadcf90b8a007d7293f769983b96c5cee2f7e2e3fd3fa83</x:v>
+      </x:c>
+      <x:c r="F41" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G41" s="31" t="str">
+        <x:v>TX0021</x:v>
+      </x:c>
+      <x:c r="H41" s="31" t="str">
+        <x:v>message64</x:v>
+      </x:c>
+      <x:c r="I41" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="str"/>
+      <x:c r="K41" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_16%4015-10-2025_14-18-26.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="31" t="str">
+        <x:v>SRC038</x:v>
+      </x:c>
+      <x:c r="B42" s="31" t="str">
+        <x:v>telegram export/photos/photo_17@15-10-2025_14-18-26.jpg</x:v>
+      </x:c>
+      <x:c r="C42" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D42" s="31" t="n">
+        <x:v>68859</x:v>
+      </x:c>
+      <x:c r="E42" s="31" t="str">
+        <x:v>ed8841b0f4a343d505b7aecc8f250fbe6f41fbcf2dcf64ca77e75a72fcf51b2b</x:v>
+      </x:c>
+      <x:c r="F42" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G42" s="31" t="str">
+        <x:v>TX0023</x:v>
+      </x:c>
+      <x:c r="H42" s="31" t="str">
+        <x:v>message65</x:v>
+      </x:c>
+      <x:c r="I42" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="str"/>
+      <x:c r="K42" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_17%4015-10-2025_14-18-26.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="31" t="str">
+        <x:v>SRC039</x:v>
+      </x:c>
+      <x:c r="B43" s="31" t="str">
+        <x:v>telegram export/photos/photo_18@28-10-2025_01-53-01.jpg</x:v>
+      </x:c>
+      <x:c r="C43" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D43" s="31" t="n">
+        <x:v>69491</x:v>
+      </x:c>
+      <x:c r="E43" s="31" t="str">
+        <x:v>52872081d1c4fc01e8f48c9cae4df8a96c78c269d03384ab89a398a382fda9e2</x:v>
+      </x:c>
+      <x:c r="F43" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G43" s="31" t="str">
+        <x:v>TX0027</x:v>
+      </x:c>
+      <x:c r="H43" s="31" t="str">
+        <x:v>message67</x:v>
+      </x:c>
+      <x:c r="I43" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="str"/>
+      <x:c r="K43" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_18%4028-10-2025_01-53-01.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="31" t="str">
+        <x:v>SRC040</x:v>
+      </x:c>
+      <x:c r="B44" s="31" t="str">
+        <x:v>telegram export/photos/photo_19@28-10-2025_01-58-07.jpg</x:v>
+      </x:c>
+      <x:c r="C44" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D44" s="31" t="n">
+        <x:v>65290</x:v>
+      </x:c>
+      <x:c r="E44" s="31" t="str">
+        <x:v>6406d711ff22151beab2efc5ad32dff29634b42c4df6d6c1de3e76cff738b2ca</x:v>
+      </x:c>
+      <x:c r="F44" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G44" s="31" t="str">
+        <x:v>TX0032</x:v>
+      </x:c>
+      <x:c r="H44" s="31" t="str">
+        <x:v>message69</x:v>
+      </x:c>
+      <x:c r="I44" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="str"/>
+      <x:c r="K44" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_19%4028-10-2025_01-58-07.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" s="31" t="str">
+        <x:v>SRC041</x:v>
+      </x:c>
+      <x:c r="B45" s="31" t="str">
+        <x:v>telegram export/photos/photo_1@24-07-2025_21-00-16.jpg</x:v>
+      </x:c>
+      <x:c r="C45" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D45" s="31" t="n">
+        <x:v>73477</x:v>
+      </x:c>
+      <x:c r="E45" s="31" t="str">
+        <x:v>79265bb04e6428f336712238ba43edcc9065f4a4313a8b75c7f937a113c99ce2</x:v>
+      </x:c>
+      <x:c r="F45" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G45" s="31" t="str">
+        <x:v>TX0002</x:v>
+      </x:c>
+      <x:c r="H45" s="31" t="str">
+        <x:v>message25</x:v>
+      </x:c>
+      <x:c r="I45" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J45" s="31" t="str"/>
+      <x:c r="K45" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_1%4024-07-2025_21-00-16.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" s="31" t="str">
+        <x:v>SRC042</x:v>
+      </x:c>
+      <x:c r="B46" s="31" t="str">
+        <x:v>telegram export/photos/photo_20@28-10-2025_22-07-57.jpg</x:v>
+      </x:c>
+      <x:c r="C46" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D46" s="31" t="n">
+        <x:v>145202</x:v>
+      </x:c>
+      <x:c r="E46" s="31" t="str">
+        <x:v>18a41c8ef151421d6a8438c0c292c313bd9d69817efed89507abf1bb0e852e6b</x:v>
+      </x:c>
+      <x:c r="F46" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G46" s="31" t="str">
+        <x:v>TX0026</x:v>
+      </x:c>
+      <x:c r="H46" s="31" t="str">
+        <x:v>message71</x:v>
+      </x:c>
+      <x:c r="I46" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J46" s="31" t="str"/>
+      <x:c r="K46" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_20%4028-10-2025_22-07-57.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
+      <x:c r="A47" s="31" t="str">
+        <x:v>SRC043</x:v>
+      </x:c>
+      <x:c r="B47" s="31" t="str">
+        <x:v>telegram export/photos/photo_21@09-11-2025_23-16-09.jpg</x:v>
+      </x:c>
+      <x:c r="C47" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D47" s="31" t="n">
+        <x:v>89073</x:v>
+      </x:c>
+      <x:c r="E47" s="31" t="str">
+        <x:v>430d605cb4bf4e4aaaf901e209b69c43c2d82946451612543b40ef112ba1fe22</x:v>
+      </x:c>
+      <x:c r="F47" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G47" s="31" t="str">
+        <x:v>TX0037</x:v>
+      </x:c>
+      <x:c r="H47" s="31" t="str">
+        <x:v>message90</x:v>
+      </x:c>
+      <x:c r="I47" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J47" s="31" t="str">
+        <x:v>INV003.</x:v>
+      </x:c>
+      <x:c r="K47" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_21%4009-11-2025_23-16-09.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
+      <x:c r="A48" s="31" t="str">
+        <x:v>SRC044</x:v>
+      </x:c>
+      <x:c r="B48" s="31" t="str">
+        <x:v>telegram export/photos/photo_22@09-11-2025_23-16-15.jpg</x:v>
+      </x:c>
+      <x:c r="C48" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D48" s="31" t="n">
+        <x:v>84952</x:v>
+      </x:c>
+      <x:c r="E48" s="31" t="str">
+        <x:v>64e9c8107140b08a348e146533350e8bd264e2f59b1f09ade0e80ba76639f360</x:v>
+      </x:c>
+      <x:c r="F48" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G48" s="31" t="str">
+        <x:v>TX0038</x:v>
+      </x:c>
+      <x:c r="H48" s="31" t="str">
+        <x:v>message91</x:v>
+      </x:c>
+      <x:c r="I48" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="str">
+        <x:v>INV004.</x:v>
+      </x:c>
+      <x:c r="K48" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_22%4009-11-2025_23-16-15.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="31" t="str">
+        <x:v>SRC045</x:v>
+      </x:c>
+      <x:c r="B49" s="31" t="str">
+        <x:v>telegram export/photos/photo_23@14-11-2025_04-07-19.jpg</x:v>
+      </x:c>
+      <x:c r="C49" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D49" s="31" t="n">
+        <x:v>65632</x:v>
+      </x:c>
+      <x:c r="E49" s="31" t="str">
+        <x:v>7003f7a94da98c211e78490a0c98ad1e5681266cb40708889b8d9b8cb66f3455</x:v>
+      </x:c>
+      <x:c r="F49" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G49" s="31" t="str">
+        <x:v>TX0037</x:v>
+      </x:c>
+      <x:c r="H49" s="31" t="str">
+        <x:v>message99</x:v>
+      </x:c>
+      <x:c r="I49" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="str"/>
+      <x:c r="K49" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_23%4014-11-2025_04-07-19.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
+      <x:c r="A50" s="31" t="str">
+        <x:v>SRC046</x:v>
+      </x:c>
+      <x:c r="B50" s="31" t="str">
+        <x:v>telegram export/photos/photo_24@14-11-2025_04-07-19.jpg</x:v>
+      </x:c>
+      <x:c r="C50" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D50" s="31" t="n">
+        <x:v>66823</x:v>
+      </x:c>
+      <x:c r="E50" s="31" t="str">
+        <x:v>2944f175b5256a669c1a6407a09eecb566d715c37dd54b80eed0cee2ae943f0c</x:v>
+      </x:c>
+      <x:c r="F50" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G50" s="31" t="str">
+        <x:v>TX0038</x:v>
+      </x:c>
+      <x:c r="H50" s="31" t="str">
+        <x:v>message100</x:v>
+      </x:c>
+      <x:c r="I50" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J50" s="31" t="str"/>
+      <x:c r="K50" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_24%4014-11-2025_04-07-19.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
+      <x:c r="A51" s="31" t="str">
+        <x:v>SRC047</x:v>
+      </x:c>
+      <x:c r="B51" s="31" t="str">
+        <x:v>telegram export/photos/photo_25@19-11-2025_11-46-31.jpg</x:v>
+      </x:c>
+      <x:c r="C51" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D51" s="31" t="n">
+        <x:v>18253</x:v>
+      </x:c>
+      <x:c r="E51" s="31" t="str">
+        <x:v>5c7d3623f81cfec1c847235a9e6124fc4d7090687911db318684c83dc455de7f</x:v>
+      </x:c>
+      <x:c r="F51" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G51" s="31" t="str">
+        <x:v>TX0044</x:v>
+      </x:c>
+      <x:c r="H51" s="31" t="str">
+        <x:v>message102</x:v>
+      </x:c>
+      <x:c r="I51" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="str"/>
+      <x:c r="K51" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_25%4019-11-2025_11-46-31.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
+      <x:c r="A52" s="31" t="str">
+        <x:v>SRC048</x:v>
+      </x:c>
+      <x:c r="B52" s="31" t="str">
+        <x:v>telegram export/photos/photo_26@21-12-2025_05-36-21.jpg</x:v>
+      </x:c>
+      <x:c r="C52" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D52" s="31" t="n">
+        <x:v>35321</x:v>
+      </x:c>
+      <x:c r="E52" s="31" t="str">
+        <x:v>a7ff8727fc0c461dc0be5e4bbc9c6c1409720229eae30931e3ae85f417819512</x:v>
+      </x:c>
+      <x:c r="F52" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G52" s="31" t="str">
+        <x:v>TX0046</x:v>
+      </x:c>
+      <x:c r="H52" s="31" t="str">
+        <x:v>message112</x:v>
+      </x:c>
+      <x:c r="I52" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="str"/>
+      <x:c r="K52" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_26%4021-12-2025_05-36-21.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
+      <x:c r="A53" s="31" t="str">
+        <x:v>SRC049</x:v>
+      </x:c>
+      <x:c r="B53" s="31" t="str">
+        <x:v>telegram export/photos/photo_27@17-05-2026_19-45-07.jpg</x:v>
+      </x:c>
+      <x:c r="C53" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D53" s="31" t="n">
+        <x:v>71982</x:v>
+      </x:c>
+      <x:c r="E53" s="31" t="str">
+        <x:v>e0e7050e5e9b2018e96723ae4831b7cdcbf4f3d79406e74efb72a47e928fe9e5</x:v>
+      </x:c>
+      <x:c r="F53" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G53" s="31" t="str">
+        <x:v>TX0063</x:v>
+      </x:c>
+      <x:c r="H53" s="31" t="str">
+        <x:v>message125</x:v>
+      </x:c>
+      <x:c r="I53" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="str"/>
+      <x:c r="K53" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_27%4017-05-2026_19-45-07.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" s="31" t="str">
+        <x:v>SRC050</x:v>
+      </x:c>
+      <x:c r="B54" s="31" t="str">
+        <x:v>telegram export/photos/photo_28@17-05-2026_19-45-07.jpg</x:v>
+      </x:c>
+      <x:c r="C54" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D54" s="31" t="n">
+        <x:v>72527</x:v>
+      </x:c>
+      <x:c r="E54" s="31" t="str">
+        <x:v>a79a95c1f0e5d599fc42a26df85ffafea142c9cc7caa622a0a1b3e9d5b7dae31</x:v>
+      </x:c>
+      <x:c r="F54" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G54" s="31" t="str">
+        <x:v>TX0062</x:v>
+      </x:c>
+      <x:c r="H54" s="31" t="str">
+        <x:v>message126</x:v>
+      </x:c>
+      <x:c r="I54" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="str"/>
+      <x:c r="K54" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_28%4017-05-2026_19-45-07.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="31" t="str">
+        <x:v>SRC051</x:v>
+      </x:c>
+      <x:c r="B55" s="31" t="str">
+        <x:v>telegram export/photos/photo_29@27-06-2026_18-24-14.jpg</x:v>
+      </x:c>
+      <x:c r="C55" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D55" s="31" t="n">
+        <x:v>89975</x:v>
+      </x:c>
+      <x:c r="E55" s="31" t="str">
+        <x:v>fdfebe75ba5891f2dbc84e11ef7625558452b73f3ce3b50b63d9c1745a4385b5</x:v>
+      </x:c>
+      <x:c r="F55" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G55" s="31" t="str">
+        <x:v>TX0038</x:v>
+      </x:c>
+      <x:c r="H55" s="31" t="str">
+        <x:v>message142</x:v>
+      </x:c>
+      <x:c r="I55" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="str">
+        <x:v>Second photo of INV004.</x:v>
+      </x:c>
+      <x:c r="K55" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_29%4027-06-2026_18-24-14.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
+      <x:c r="A56" s="31" t="str">
+        <x:v>SRC052</x:v>
+      </x:c>
+      <x:c r="B56" s="31" t="str">
+        <x:v>telegram export/photos/photo_2@24-07-2025_21-00-17.jpg</x:v>
+      </x:c>
+      <x:c r="C56" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D56" s="31" t="n">
+        <x:v>74772</x:v>
+      </x:c>
+      <x:c r="E56" s="31" t="str">
+        <x:v>9d1cc7913277237d5bf999452661d8ab00c1add42d2751e54bfa96521f756b17</x:v>
+      </x:c>
+      <x:c r="F56" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G56" s="31" t="str">
+        <x:v>TX0003</x:v>
+      </x:c>
+      <x:c r="H56" s="31" t="str">
+        <x:v>message26</x:v>
+      </x:c>
+      <x:c r="I56" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="str"/>
+      <x:c r="K56" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_2%4024-07-2025_21-00-17.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
+      <x:c r="A57" s="31" t="str">
+        <x:v>SRC053</x:v>
+      </x:c>
+      <x:c r="B57" s="31" t="str">
+        <x:v>telegram export/photos/photo_30@27-06-2026_18-24-31.jpg</x:v>
+      </x:c>
+      <x:c r="C57" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D57" s="31" t="n">
+        <x:v>114397</x:v>
+      </x:c>
+      <x:c r="E57" s="31" t="str">
+        <x:v>f5569b998adf63c1cebcb144277502c32db8088ce75d731cd3a7d98be3b2c669</x:v>
+      </x:c>
+      <x:c r="F57" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G57" s="31" t="str">
+        <x:v>TX0037</x:v>
+      </x:c>
+      <x:c r="H57" s="31" t="str">
+        <x:v>message143</x:v>
+      </x:c>
+      <x:c r="I57" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="str">
+        <x:v>Second photo of INV003.</x:v>
+      </x:c>
+      <x:c r="K57" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_30%4027-06-2026_18-24-31.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
+      <x:c r="A58" s="31" t="str">
+        <x:v>SRC054</x:v>
+      </x:c>
+      <x:c r="B58" s="31" t="str">
+        <x:v>telegram export/photos/photo_31@27-06-2026_18-24-39.jpg</x:v>
+      </x:c>
+      <x:c r="C58" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D58" s="31" t="n">
+        <x:v>51950</x:v>
+      </x:c>
+      <x:c r="E58" s="31" t="str">
+        <x:v>5e693fc6f8303f5ee512c9ec9b3eadec3f3d7319b2c2f969e9875baca06d790b</x:v>
+      </x:c>
+      <x:c r="F58" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G58" s="31" t="str">
+        <x:v>TX0028</x:v>
+      </x:c>
+      <x:c r="H58" s="31" t="str">
+        <x:v>message144</x:v>
+      </x:c>
+      <x:c r="I58" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J58" s="31" t="str"/>
+      <x:c r="K58" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_31%4027-06-2026_18-24-39.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="31" t="str">
+        <x:v>SRC055</x:v>
+      </x:c>
+      <x:c r="B59" s="31" t="str">
+        <x:v>telegram export/photos/photo_32@27-06-2026_18-24-52.jpg</x:v>
+      </x:c>
+      <x:c r="C59" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D59" s="31" t="n">
+        <x:v>66516</x:v>
+      </x:c>
+      <x:c r="E59" s="31" t="str">
+        <x:v>7628c00e8636b2fb53053ed1feaab9c04fbc27a578e143dd6f1f16a64d6e00e3</x:v>
+      </x:c>
+      <x:c r="F59" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G59" s="31" t="str">
+        <x:v>TX0042</x:v>
+      </x:c>
+      <x:c r="H59" s="31" t="str">
+        <x:v>message145</x:v>
+      </x:c>
+      <x:c r="I59" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="str"/>
+      <x:c r="K59" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_32%4027-06-2026_18-24-52.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" s="31" t="str">
+        <x:v>SRC056</x:v>
+      </x:c>
+      <x:c r="B60" s="31" t="str">
+        <x:v>telegram export/photos/photo_33@27-06-2026_18-25-49.jpg</x:v>
+      </x:c>
+      <x:c r="C60" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D60" s="31" t="n">
+        <x:v>69981</x:v>
+      </x:c>
+      <x:c r="E60" s="31" t="str">
+        <x:v>a0ebad23be285a1e51b629326f6f3a8dab9f52662632f4ef6194fea9855b2267</x:v>
+      </x:c>
+      <x:c r="F60" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G60" s="31" t="str">
+        <x:v>TX0033</x:v>
+      </x:c>
+      <x:c r="H60" s="31" t="str">
+        <x:v>message146</x:v>
+      </x:c>
+      <x:c r="I60" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="str"/>
+      <x:c r="K60" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_33%4027-06-2026_18-25-49.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
+      <x:c r="A61" s="31" t="str">
+        <x:v>SRC057</x:v>
+      </x:c>
+      <x:c r="B61" s="31" t="str">
+        <x:v>telegram export/photos/photo_34@27-06-2026_18-26-03.jpg</x:v>
+      </x:c>
+      <x:c r="C61" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D61" s="31" t="n">
+        <x:v>162060</x:v>
+      </x:c>
+      <x:c r="E61" s="31" t="str">
+        <x:v>d7091b678efb3e0f2e1da6270bff602fc8d5dd14fd758484945206f09aec6835</x:v>
+      </x:c>
+      <x:c r="F61" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G61" s="31" t="str">
+        <x:v>TX0033</x:v>
+      </x:c>
+      <x:c r="H61" s="31" t="str">
+        <x:v>message147</x:v>
+      </x:c>
+      <x:c r="I61" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J61" s="31" t="str">
+        <x:v>INV005, uncertain.</x:v>
+      </x:c>
+      <x:c r="K61" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_34%4027-06-2026_18-26-03.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
+      <x:c r="A62" s="31" t="str">
+        <x:v>SRC058</x:v>
+      </x:c>
+      <x:c r="B62" s="31" t="str">
+        <x:v>telegram export/photos/photo_35@27-06-2026_18-26-22.jpg</x:v>
+      </x:c>
+      <x:c r="C62" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D62" s="31" t="n">
+        <x:v>168669</x:v>
+      </x:c>
+      <x:c r="E62" s="31" t="str">
+        <x:v>df1dad972da0ba8c3da2b76b90ccdd5c9ae6c42488b2b0f50e3eb232ab177028</x:v>
+      </x:c>
+      <x:c r="F62" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G62" s="31" t="str">
+        <x:v>TX0034</x:v>
+      </x:c>
+      <x:c r="H62" s="31" t="str">
+        <x:v>message148</x:v>
+      </x:c>
+      <x:c r="I62" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="str"/>
+      <x:c r="K62" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_35%4027-06-2026_18-26-22.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="A63" s="31" t="str">
+        <x:v>SRC059</x:v>
+      </x:c>
+      <x:c r="B63" s="31" t="str">
+        <x:v>telegram export/photos/photo_36@27-06-2026_18-26-45.jpg</x:v>
+      </x:c>
+      <x:c r="C63" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D63" s="31" t="n">
+        <x:v>56182</x:v>
+      </x:c>
+      <x:c r="E63" s="31" t="str">
+        <x:v>c76783f3ab2aa8dfafe81fe1d3273e3a70b017cbb8e04ee0aebf20c7896fd8a6</x:v>
+      </x:c>
+      <x:c r="F63" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G63" s="31" t="str">
+        <x:v>TX0024</x:v>
+      </x:c>
+      <x:c r="H63" s="31" t="str">
+        <x:v>message149</x:v>
+      </x:c>
+      <x:c r="I63" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J63" s="31" t="str">
+        <x:v>Same purchase as photo_14.</x:v>
+      </x:c>
+      <x:c r="K63" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_36%4027-06-2026_18-26-45.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
+      <x:c r="A64" s="31" t="str">
+        <x:v>SRC060</x:v>
+      </x:c>
+      <x:c r="B64" s="31" t="str">
+        <x:v>telegram export/photos/photo_37@27-06-2026_18-27-12.jpg</x:v>
+      </x:c>
+      <x:c r="C64" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D64" s="31" t="n">
+        <x:v>45970</x:v>
+      </x:c>
+      <x:c r="E64" s="31" t="str">
+        <x:v>9a1f8890689207a4000e3fe0fc271e522bb56ace944c1646ccf84577b88f9405</x:v>
+      </x:c>
+      <x:c r="F64" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G64" s="31" t="str">
+        <x:v>TX0023</x:v>
+      </x:c>
+      <x:c r="H64" s="31" t="str">
+        <x:v>message150</x:v>
+      </x:c>
+      <x:c r="I64" s="31" t="str">
+        <x:v>Reconciled</x:v>
+      </x:c>
+      <x:c r="J64" s="31" t="str">
+        <x:v>Same purchase as photo_17.</x:v>
+      </x:c>
+      <x:c r="K64" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_37%4027-06-2026_18-27-12.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
+      <x:c r="A65" s="31" t="str">
+        <x:v>SRC061</x:v>
+      </x:c>
+      <x:c r="B65" s="31" t="str">
+        <x:v>telegram export/photos/photo_38@27-06-2026_18-27-25.jpg</x:v>
+      </x:c>
+      <x:c r="C65" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D65" s="31" t="n">
+        <x:v>41070</x:v>
+      </x:c>
+      <x:c r="E65" s="31" t="str">
+        <x:v>e8a6c9ba9556546fa4abbc8e152e35df08dcc2c6669884f9dc12679882029c3e</x:v>
+      </x:c>
+      <x:c r="F65" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G65" s="31" t="str">
+        <x:v>TX0060</x:v>
+      </x:c>
+      <x:c r="H65" s="31" t="str">
+        <x:v>message151</x:v>
+      </x:c>
+      <x:c r="I65" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J65" s="31" t="str"/>
+      <x:c r="K65" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_38%4027-06-2026_18-27-25.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
+      <x:c r="A66" s="31" t="str">
+        <x:v>SRC062</x:v>
+      </x:c>
+      <x:c r="B66" s="31" t="str">
+        <x:v>telegram export/photos/photo_39@27-06-2026_18-29-10.jpg</x:v>
+      </x:c>
+      <x:c r="C66" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D66" s="31" t="n">
+        <x:v>62596</x:v>
+      </x:c>
+      <x:c r="E66" s="31" t="str">
+        <x:v>2cc0dda007136a8eb626cca071cf976fa2faea1a3ec9461e2f9e61d426d539da</x:v>
+      </x:c>
+      <x:c r="F66" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G66" s="31" t="str">
+        <x:v>TX0059</x:v>
+      </x:c>
+      <x:c r="H66" s="31" t="str">
+        <x:v>message152</x:v>
+      </x:c>
+      <x:c r="I66" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="str"/>
+      <x:c r="K66" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_39%4027-06-2026_18-29-10.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="15" hidden="0" customHeight="1">
+      <x:c r="A67" s="31" t="str">
+        <x:v>SRC063</x:v>
+      </x:c>
+      <x:c r="B67" s="31" t="str">
+        <x:v>telegram export/photos/photo_3@24-07-2025_21-02-51.jpg</x:v>
+      </x:c>
+      <x:c r="C67" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D67" s="31" t="n">
+        <x:v>71647</x:v>
+      </x:c>
+      <x:c r="E67" s="31" t="str">
+        <x:v>3a30db869e1f6a6c63f03739af4268b7b0405346be7199ac5e26f23dc73806fc</x:v>
+      </x:c>
+      <x:c r="F67" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G67" s="31" t="str">
+        <x:v>TX0004</x:v>
+      </x:c>
+      <x:c r="H67" s="31" t="str">
+        <x:v>message27</x:v>
+      </x:c>
+      <x:c r="I67" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J67" s="31" t="str"/>
+      <x:c r="K67" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_3%4024-07-2025_21-02-51.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="15" hidden="0" customHeight="1">
+      <x:c r="A68" s="31" t="str">
+        <x:v>SRC064</x:v>
+      </x:c>
+      <x:c r="B68" s="31" t="str">
+        <x:v>telegram export/photos/photo_40@27-06-2026_18-31-08.jpg</x:v>
+      </x:c>
+      <x:c r="C68" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D68" s="31" t="n">
+        <x:v>59578</x:v>
+      </x:c>
+      <x:c r="E68" s="31" t="str">
+        <x:v>8e9cb970ead01179e35ef3181ee0017987b3e8de78c03c3bb37fc20f4f3ef402</x:v>
+      </x:c>
+      <x:c r="F68" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G68" s="31" t="str">
+        <x:v>TX0031</x:v>
+      </x:c>
+      <x:c r="H68" s="31" t="str">
+        <x:v>message153</x:v>
+      </x:c>
+      <x:c r="I68" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="str"/>
+      <x:c r="K68" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_40%4027-06-2026_18-31-08.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
+      <x:c r="A69" s="31" t="str">
+        <x:v>SRC065</x:v>
+      </x:c>
+      <x:c r="B69" s="31" t="str">
+        <x:v>telegram export/photos/photo_41@27-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+      <x:c r="C69" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D69" s="31" t="n">
+        <x:v>77996</x:v>
+      </x:c>
+      <x:c r="E69" s="31" t="str">
+        <x:v>78ad7571d728263883b5dc1bb9cd22848b5c2e67370643caa12c8c8935da2b20</x:v>
+      </x:c>
+      <x:c r="F69" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G69" s="31" t="str">
+        <x:v>TX0053</x:v>
+      </x:c>
+      <x:c r="H69" s="31" t="str">
+        <x:v>message155</x:v>
+      </x:c>
+      <x:c r="I69" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="str"/>
+      <x:c r="K69" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_41%4027-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="15" hidden="0" customHeight="1">
+      <x:c r="A70" s="31" t="str">
+        <x:v>SRC066</x:v>
+      </x:c>
+      <x:c r="B70" s="31" t="str">
+        <x:v>telegram export/photos/photo_42@27-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+      <x:c r="C70" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D70" s="31" t="n">
+        <x:v>77238</x:v>
+      </x:c>
+      <x:c r="E70" s="31" t="str">
+        <x:v>94ca1e41dc1aa15b41dd5ec0b9bb664d54733c8559fe9e348d1adc782f316712</x:v>
+      </x:c>
+      <x:c r="F70" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G70" s="31" t="str">
+        <x:v>TX0052</x:v>
+      </x:c>
+      <x:c r="H70" s="31" t="str">
+        <x:v>message156</x:v>
+      </x:c>
+      <x:c r="I70" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J70" s="31" t="str"/>
+      <x:c r="K70" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_42%4027-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="15" hidden="0" customHeight="1">
+      <x:c r="A71" s="31" t="str">
+        <x:v>SRC067</x:v>
+      </x:c>
+      <x:c r="B71" s="31" t="str">
+        <x:v>telegram export/photos/photo_43@27-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+      <x:c r="C71" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D71" s="31" t="n">
+        <x:v>85618</x:v>
+      </x:c>
+      <x:c r="E71" s="31" t="str">
+        <x:v>35428512edee92243496c3104d792d4fd07c6d43257d697c19937ccfa0a98517</x:v>
+      </x:c>
+      <x:c r="F71" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G71" s="31" t="str">
+        <x:v>TX0054</x:v>
+      </x:c>
+      <x:c r="H71" s="31" t="str">
+        <x:v>message157</x:v>
+      </x:c>
+      <x:c r="I71" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="str"/>
+      <x:c r="K71" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_43%4027-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="15" hidden="0" customHeight="1">
+      <x:c r="A72" s="31" t="str">
+        <x:v>SRC068</x:v>
+      </x:c>
+      <x:c r="B72" s="31" t="str">
+        <x:v>telegram export/photos/photo_44@27-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+      <x:c r="C72" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D72" s="31" t="n">
+        <x:v>85772</x:v>
+      </x:c>
+      <x:c r="E72" s="31" t="str">
+        <x:v>552ed592df76565fdf834836abf1da6c4b9784e66039b1efaa36e162e69d855b</x:v>
+      </x:c>
+      <x:c r="F72" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G72" s="31" t="str">
+        <x:v>TX0055</x:v>
+      </x:c>
+      <x:c r="H72" s="31" t="str">
+        <x:v>message158</x:v>
+      </x:c>
+      <x:c r="I72" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J72" s="31" t="str"/>
+      <x:c r="K72" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_44%4027-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="15" hidden="0" customHeight="1">
+      <x:c r="A73" s="31" t="str">
+        <x:v>SRC069</x:v>
+      </x:c>
+      <x:c r="B73" s="31" t="str">
+        <x:v>telegram export/photos/photo_45@27-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+      <x:c r="C73" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D73" s="31" t="n">
+        <x:v>65390</x:v>
+      </x:c>
+      <x:c r="E73" s="31" t="str">
+        <x:v>d3cd5d400ad26b008c54a467ede8e780c9606b0a9a460d51c2e11bf69ede9a39</x:v>
+      </x:c>
+      <x:c r="F73" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G73" s="31" t="str">
+        <x:v>TX0050</x:v>
+      </x:c>
+      <x:c r="H73" s="31" t="str">
+        <x:v>message159</x:v>
+      </x:c>
+      <x:c r="I73" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J73" s="31" t="str"/>
+      <x:c r="K73" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_45%4027-06-2026_18-36-09.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
+      <x:c r="A74" s="31" t="str">
+        <x:v>SRC070</x:v>
+      </x:c>
+      <x:c r="B74" s="31" t="str">
+        <x:v>telegram export/photos/photo_46@27-06-2026_18-38-52.jpg</x:v>
+      </x:c>
+      <x:c r="C74" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D74" s="31" t="n">
+        <x:v>145310</x:v>
+      </x:c>
+      <x:c r="E74" s="31" t="str">
+        <x:v>22c0f55d35b72f746c979bd91c0f23f9862ff7f5a4851ab2293686a796fab727</x:v>
+      </x:c>
+      <x:c r="F74" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G74" s="31" t="str">
+        <x:v>TX0056</x:v>
+      </x:c>
+      <x:c r="H74" s="31" t="str">
+        <x:v>message161</x:v>
+      </x:c>
+      <x:c r="I74" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J74" s="31" t="str"/>
+      <x:c r="K74" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_46%4027-06-2026_18-38-52.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
+      <x:c r="A75" s="31" t="str">
+        <x:v>SRC071</x:v>
+      </x:c>
+      <x:c r="B75" s="31" t="str">
+        <x:v>telegram export/photos/photo_47@27-06-2026_18-43-30.jpg</x:v>
+      </x:c>
+      <x:c r="C75" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D75" s="31" t="n">
+        <x:v>145095</x:v>
+      </x:c>
+      <x:c r="E75" s="31" t="str">
+        <x:v>65c4560d70bc56c79da398701f9c98c8ae2ffada8d71d2c3e111e2e24ae1cd86</x:v>
+      </x:c>
+      <x:c r="F75" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G75" s="31" t="str">
+        <x:v>TX0057</x:v>
+      </x:c>
+      <x:c r="H75" s="31" t="str">
+        <x:v>message164</x:v>
+      </x:c>
+      <x:c r="I75" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J75" s="31" t="str">
+        <x:v>Duplicate image.</x:v>
+      </x:c>
+      <x:c r="K75" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_47%4027-06-2026_18-43-30.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
+      <x:c r="A76" s="31" t="str">
+        <x:v>SRC072</x:v>
+      </x:c>
+      <x:c r="B76" s="31" t="str">
+        <x:v>telegram export/photos/photo_48@27-06-2026_18-43-30.jpg</x:v>
+      </x:c>
+      <x:c r="C76" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D76" s="31" t="n">
+        <x:v>64244</x:v>
+      </x:c>
+      <x:c r="E76" s="31" t="str">
+        <x:v>20df96b527f0c957a11188d14f66f9281587d18e0b3e31457b0db70daf899449</x:v>
+      </x:c>
+      <x:c r="F76" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G76" s="31" t="str">
+        <x:v>TX0051</x:v>
+      </x:c>
+      <x:c r="H76" s="31" t="str">
+        <x:v>message165</x:v>
+      </x:c>
+      <x:c r="I76" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J76" s="31" t="str">
+        <x:v>Duplicate image.</x:v>
+      </x:c>
+      <x:c r="K76" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_48%4027-06-2026_18-43-30.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
+      <x:c r="A77" s="31" t="str">
+        <x:v>SRC073</x:v>
+      </x:c>
+      <x:c r="B77" s="31" t="str">
+        <x:v>telegram export/photos/photo_4@25-07-2025_04-04-24.jpg</x:v>
+      </x:c>
+      <x:c r="C77" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D77" s="31" t="n">
+        <x:v>74199</x:v>
+      </x:c>
+      <x:c r="E77" s="31" t="str">
+        <x:v>5034c1ebaa4bd3c07a59eaf0de3840e0ed1486387ba2b1e9c2832c748b3979a7</x:v>
+      </x:c>
+      <x:c r="F77" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G77" s="31" t="str">
+        <x:v>TX0005</x:v>
+      </x:c>
+      <x:c r="H77" s="31" t="str">
+        <x:v>message29</x:v>
+      </x:c>
+      <x:c r="I77" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="str"/>
+      <x:c r="K77" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_4%4025-07-2025_04-04-24.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
+      <x:c r="A78" s="31" t="str">
+        <x:v>SRC074</x:v>
+      </x:c>
+      <x:c r="B78" s="31" t="str">
+        <x:v>telegram export/photos/photo_5@25-07-2025_04-08-41.jpg</x:v>
+      </x:c>
+      <x:c r="C78" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D78" s="31" t="n">
+        <x:v>74870</x:v>
+      </x:c>
+      <x:c r="E78" s="31" t="str">
+        <x:v>097c6be0efefe88b7e213d3f6aba5f4dc6a9e813bd3aed9162a991d6f68aeb4b</x:v>
+      </x:c>
+      <x:c r="F78" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G78" s="31" t="str">
+        <x:v>TX0006</x:v>
+      </x:c>
+      <x:c r="H78" s="31" t="str">
+        <x:v>message30</x:v>
+      </x:c>
+      <x:c r="I78" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J78" s="31" t="str"/>
+      <x:c r="K78" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_5%4025-07-2025_04-08-41.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="15" hidden="0" customHeight="1">
+      <x:c r="A79" s="31" t="str">
+        <x:v>SRC075</x:v>
+      </x:c>
+      <x:c r="B79" s="31" t="str">
+        <x:v>telegram export/photos/photo_6@25-07-2025_15-53-39.jpg</x:v>
+      </x:c>
+      <x:c r="C79" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D79" s="31" t="n">
+        <x:v>74748</x:v>
+      </x:c>
+      <x:c r="E79" s="31" t="str">
+        <x:v>26c18dafda65ecb48d670d908ff9a6c650df2905684e12dc23e64ef7a00a2547</x:v>
+      </x:c>
+      <x:c r="F79" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G79" s="31" t="str">
+        <x:v>TX0007, TX0008</x:v>
+      </x:c>
+      <x:c r="H79" s="31" t="str">
+        <x:v>message31</x:v>
+      </x:c>
+      <x:c r="I79" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J79" s="31" t="str"/>
+      <x:c r="K79" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_6%4025-07-2025_15-53-39.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="15" hidden="0" customHeight="1">
+      <x:c r="A80" s="31" t="str">
+        <x:v>SRC076</x:v>
+      </x:c>
+      <x:c r="B80" s="31" t="str">
+        <x:v>telegram export/photos/photo_7@11-08-2025_15-51-55.jpg</x:v>
+      </x:c>
+      <x:c r="C80" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D80" s="31" t="n">
+        <x:v>71573</x:v>
+      </x:c>
+      <x:c r="E80" s="31" t="str">
+        <x:v>7cea1f63bcc0623f6f084e71e2aeea383f1f5648bfcdf5e8b6785cc5a6ec980d</x:v>
+      </x:c>
+      <x:c r="F80" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G80" s="31" t="str">
+        <x:v>TX0011</x:v>
+      </x:c>
+      <x:c r="H80" s="31" t="str">
+        <x:v>message42</x:v>
+      </x:c>
+      <x:c r="I80" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J80" s="31" t="str"/>
+      <x:c r="K80" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_7%4011-08-2025_15-51-55.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
+      <x:c r="A81" s="31" t="str">
+        <x:v>SRC077</x:v>
+      </x:c>
+      <x:c r="B81" s="31" t="str">
+        <x:v>telegram export/photos/photo_8@12-08-2025_09-58-34.jpg</x:v>
+      </x:c>
+      <x:c r="C81" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D81" s="31" t="n">
+        <x:v>74246</x:v>
+      </x:c>
+      <x:c r="E81" s="31" t="str">
+        <x:v>644eada63dc0f6deb5768ffcb5bf455d0cda0ea15dd20247a08aedaf6a6c2863</x:v>
+      </x:c>
+      <x:c r="F81" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G81" s="31" t="str">
+        <x:v>TX0009</x:v>
+      </x:c>
+      <x:c r="H81" s="31" t="str">
+        <x:v>message44</x:v>
+      </x:c>
+      <x:c r="I81" s="31" t="str">
+        <x:v>Extracted</x:v>
+      </x:c>
+      <x:c r="J81" s="31" t="str"/>
+      <x:c r="K81" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_8%4012-08-2025_09-58-34.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
+      <x:c r="A82" s="31" t="str">
+        <x:v>SRC078</x:v>
+      </x:c>
+      <x:c r="B82" s="31" t="str">
+        <x:v>telegram export/photos/photo_9@12-08-2025_09-58-34.jpg</x:v>
+      </x:c>
+      <x:c r="C82" s="31" t="str">
+        <x:v>jpg</x:v>
+      </x:c>
+      <x:c r="D82" s="31" t="n">
+        <x:v>254809</x:v>
+      </x:c>
+      <x:c r="E82" s="31" t="str">
+        <x:v>5c47322f7a512fb80b48f0044a38ac5a9222176efd200637dbdac21211145ca5</x:v>
+      </x:c>
+      <x:c r="F82" s="31" t="str">
+        <x:v>Read</x:v>
+      </x:c>
+      <x:c r="G82" s="31" t="str">
+        <x:v>TX0009</x:v>
+      </x:c>
+      <x:c r="H82" s="31" t="str">
+        <x:v>message46</x:v>
+      </x:c>
+      <x:c r="I82" s="31" t="str">
+        <x:v>Context only</x:v>
+      </x:c>
+      <x:c r="J82" s="31" t="str">
+        <x:v>Ad screenshot; no transaction.</x:v>
+      </x:c>
+      <x:c r="K82" s="31" t="str">
+        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_9%4012-08-2025_09-58-34.jpg</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R802189b79e394a7a"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFEDF2F7"/>
@@ -1180,33 +3919,33 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="32"/>
-      <x:c r="B1" s="32"/>
-      <x:c r="C1" s="32"/>
-      <x:c r="D1" s="32"/>
-      <x:c r="E1" s="32"/>
-      <x:c r="F1" s="32"/>
-      <x:c r="G1" s="32"/>
-    </x:row>
-    <x:row r="2" ht="100.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A2" s="33" t="str">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+      <x:c r="C1" s="33"/>
+      <x:c r="D1" s="33"/>
+      <x:c r="E1" s="33"/>
+      <x:c r="F1" s="33"/>
+      <x:c r="G1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
         <x:v>Telegram source messages | replies and attachments preserved</x:v>
       </x:c>
-      <x:c r="B2" s="32"/>
-      <x:c r="C2" s="32"/>
-      <x:c r="D2" s="32"/>
-      <x:c r="E2" s="32"/>
-      <x:c r="F2" s="32"/>
-      <x:c r="G2" s="32"/>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
+      <x:c r="G2" s="33"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="32"/>
-      <x:c r="B3" s="32"/>
-      <x:c r="C3" s="32"/>
-      <x:c r="D3" s="32"/>
-      <x:c r="E3" s="32"/>
-      <x:c r="F3" s="32"/>
-      <x:c r="G3" s="32"/>
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -4827,14 +7566,17 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67e494b37c346b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f60271f93344373"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFEDF2F7"/>
@@ -4849,27 +7591,27 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="32"/>
-      <x:c r="B1" s="32"/>
-      <x:c r="C1" s="32"/>
-      <x:c r="D1" s="32"/>
-      <x:c r="E1" s="32"/>
-    </x:row>
-    <x:row r="2" ht="33.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A2" s="33" t="str">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+      <x:c r="C1" s="33"/>
+      <x:c r="D1" s="33"/>
+      <x:c r="E1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
         <x:v>Original workbook cells | unchanged source snapshots</x:v>
       </x:c>
-      <x:c r="B2" s="32"/>
-      <x:c r="C2" s="32"/>
-      <x:c r="D2" s="32"/>
-      <x:c r="E2" s="32"/>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="32"/>
-      <x:c r="B3" s="32"/>
-      <x:c r="C3" s="32"/>
-      <x:c r="D3" s="32"/>
-      <x:c r="E3" s="32"/>
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -50693,14 +53435,17 @@
       <x:c r="E3038" s="31"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ae3a23fe2844693"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729c94d5ac7a42bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFEDF2F7"/>
@@ -50712,18 +53457,18 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="32"/>
-      <x:c r="B1" s="32"/>
-    </x:row>
-    <x:row r="2" ht="33.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A2" s="33" t="str">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
         <x:v>Accounting basis, definitions and refresh instructions</x:v>
       </x:c>
-      <x:c r="B2" s="32"/>
+      <x:c r="B2" s="33"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="32"/>
-      <x:c r="B3" s="32"/>
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -50762,7 +53507,7 @@
         <x:v>Review status</x:v>
       </x:c>
       <x:c r="B8" s="31" t="str">
-        <x:v>Unresolved purpose, entity relationship, settlement, unit, duplicate or cutoff; excluded from supported cash totals.</x:v>
+        <x:v>Unresolved cash direction, entity relationship, settlement, amount, unit, duplicate or cutoff; excluded from supported totals. Confirmed expenses may remain unallocated by project.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -50823,104 +53568,131 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="31" t="str">
-        <x:v>Scope</x:v>
+        <x:v>User confirmation</x:v>
       </x:c>
       <x:c r="B16" s="31" t="str">
-        <x:v>All 188 exported messages, 68 original full-size images, four PDFs, three course reports and both workbooks. Thumbnails and export icons are display derivatives.</x:v>
+        <x:v>All recipts/ items are user-confirmed association expenses. Provisional receipts and the photographed invoice are treated as settled on user attestation, separately from bank-final evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="31" t="str">
-        <x:v>Policy 1</x:v>
+        <x:v>Instructor mapping</x:v>
       </x:c>
       <x:c r="B17" s="31" t="str">
-        <x:v>Reporting unit is toman. Rial documents are divided by 10, and only when the unit is printed. Amounts with no stated unit keep amount_toman null.</x:v>
+        <x:v>Five Summer School 1405 payments total 11,500,000. Alireza is the bank payee for instructor Abolfazl Ahmadi; Zahra Amiri is sticker supplies. Sixth instructor remains unmatched.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="31" t="str">
-        <x:v>Policy 2</x:v>
+        <x:v>Scope</x:v>
       </x:c>
       <x:c r="B18" s="31" t="str">
-        <x:v>The printed document date takes precedence over upload, forward or filename dates. Conflicts are kept in notes.</x:v>
+        <x:v>All 188 exported messages, 68 original full-size images, four PDFs, three course reports and both workbooks. Thumbnails and export icons are display derivatives.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="31" t="str">
-        <x:v>Policy 3</x:v>
+        <x:v>Policy 1</x:v>
       </x:c>
       <x:c r="B19" s="31" t="str">
-        <x:v>Supported totals include only Supported rows. Review, Duplicate, Invoice only and Summary only rows are excluded.</x:v>
+        <x:v>Reporting unit is toman. Rial documents are divided by 10, and only when the unit is printed. Amounts with no stated unit keep amount_toman null.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="31" t="str">
-        <x:v>Policy 4</x:v>
+        <x:v>Policy 2</x:v>
       </x:c>
       <x:c r="B20" s="31" t="str">
-        <x:v>Invoices prove billing, not payment. Cash payments are included only when settled or explicitly recorded in the original ledger; unmatched invoices remain separate.</x:v>
+        <x:v>The printed document date takes precedence over upload, forward or filename dates. Conflicts are kept in notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="31" t="str">
-        <x:v>Policy 5</x:v>
+        <x:v>Policy 3</x:v>
       </x:c>
       <x:c r="B21" s="31" t="str">
-        <x:v>Volunteer-paid purchases support reimbursements. Either the reimbursement or the purchases is recorded as association cash, never both.</x:v>
+        <x:v>Supported totals include only Supported rows. Review, Duplicate, Invoice only and Summary only rows are excluded.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="31" t="str">
-        <x:v>Policy 6</x:v>
+        <x:v>Policy 4</x:v>
       </x:c>
       <x:c r="B22" s="31" t="str">
-        <x:v>Internal transfers (e.g. AMIN-EVENT to SHAHR-8966) are not income or expense.</x:v>
+        <x:v>Invoices prove billing, not payment. Cash payments are included only when settled or explicitly recorded in the original ledger; unmatched invoices remain separate.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="31" t="str">
-        <x:v>Policy 7</x:v>
+        <x:v>Policy 5</x:v>
       </x:c>
       <x:c r="B23" s="31" t="str">
-        <x:v>Opening-funds handovers from the former board are recorded as equity or opening funds, not operating income.</x:v>
+        <x:v>Volunteer-paid purchases support reimbursements. Either the reimbursement or the purchases is recorded as association cash, never both.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="31" t="str">
-        <x:v>Policy 8</x:v>
+        <x:v>Policy 6</x:v>
       </x:c>
       <x:c r="B24" s="31" t="str">
-        <x:v>Debits from custodian Blu or personal accounts stay in Review until the custodian confirms they were association funds.</x:v>
+        <x:v>Internal transfers (e.g. AMIN-EVENT to SHAHR-8966) are not income or expense.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="31" t="str">
-        <x:v>Policy 9</x:v>
+        <x:v>Policy 7</x:v>
       </x:c>
       <x:c r="B25" s="31" t="str">
-        <x:v>Each original مجموع cell maps to ledger rows with a disposition. The مرداد and شهریور sheets are subsets and are not double-mapped.</x:v>
+        <x:v>Opening-funds handovers from the former board are recorded as equity or opening funds, not operating income.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="31" t="str">
-        <x:v>Policy 10</x:v>
+        <x:v>Policy 8</x:v>
       </x:c>
       <x:c r="B26" s="31" t="str">
-        <x:v>Teacher fees round to 100,000 toman (message14). Deviations are flagged, not altered.</x:v>
+        <x:v>Custodian Blu outflows in recipts/ are now confirmed by the user as association expenses. Unknown purposes remain unallocated; statement reconciliation is still required.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="31" t="str">
+        <x:v>Policy 9</x:v>
+      </x:c>
+      <x:c r="B27" s="31" t="str">
+        <x:v>Each original مجموع cell maps to ledger rows with a disposition. The مرداد and شهریور sheets are subsets and are not double-mapped.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="31" t="str">
+        <x:v>Policy 10</x:v>
+      </x:c>
+      <x:c r="B28" s="31" t="str">
+        <x:v>Teacher fees round to 100,000 toman (message14). Deviations are flagged, not altered.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="31" t="str">
         <x:v>Policy 11</x:v>
       </x:c>
-      <x:c r="B27" s="31" t="str">
+      <x:c r="B29" s="31" t="str">
         <x:v>Student phone numbers in the course reports must not appear in published reports.</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" ht="24" hidden="0" customHeight="1">
+      <x:c r="A30" s="31" t="str">
+        <x:v>Policy 12</x:v>
+      </x:c>
+      <x:c r="B30" s="31" t="str">
+        <x:v>User-confirmation revision: all recipts/ images are association expenses. Provisional transfers and the photographed invoice are treated as settled only on explicit user attestation; their original source limitations remain visible. The folder duplicate is retained and excluded. Five Summer School 1405 payments are identified; the sixth is not inferred.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:B2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10d7d17658454deb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00da56e4d26f4d9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50948,7 +53720,7 @@
       <x:c r="E1" s="1"/>
       <x:c r="F1" s="1"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
         <x:v>Monthly cash activity | Jalali calendar</x:v>
       </x:c>
@@ -51121,19 +53893,19 @@
       </x:c>
       <x:c r="C10" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A10)</x:f>
-        <x:v>0</x:v>
+        <x:v>1020000</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
         <x:f>B10-C10</x:f>
-        <x:v>23000000</x:v>
+        <x:v>21980000</x:v>
       </x:c>
       <x:c r="E10" s="10" t="n">
         <x:f>SUM($D$5:D10)</x:f>
-        <x:v>43307175</x:v>
+        <x:v>42287175</x:v>
       </x:c>
       <x:c r="F10" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A10,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>1020000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
@@ -51154,7 +53926,7 @@
       </x:c>
       <x:c r="E11" s="10" t="n">
         <x:f>SUM($D$5:D11)</x:f>
-        <x:v>57480175</x:v>
+        <x:v>56460175</x:v>
       </x:c>
       <x:c r="F11" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A11,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51171,19 +53943,19 @@
       </x:c>
       <x:c r="C12" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A12)</x:f>
-        <x:v>0</x:v>
+        <x:v>1801220</x:v>
       </x:c>
       <x:c r="D12" s="10" t="n">
         <x:f>B12-C12</x:f>
-        <x:v>0</x:v>
+        <x:v>-1801220</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
         <x:f>SUM($D$5:D12)</x:f>
-        <x:v>57480175</x:v>
+        <x:v>54658955</x:v>
       </x:c>
       <x:c r="F12" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A12,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>1801220</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
@@ -51204,7 +53976,7 @@
       </x:c>
       <x:c r="E13" s="10" t="n">
         <x:f>SUM($D$5:D13)</x:f>
-        <x:v>53430175</x:v>
+        <x:v>50608955</x:v>
       </x:c>
       <x:c r="F13" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A13,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51221,19 +53993,19 @@
       </x:c>
       <x:c r="C14" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A14)</x:f>
-        <x:v>0</x:v>
+        <x:v>11217000</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
         <x:f>B14-C14</x:f>
-        <x:v>0</x:v>
+        <x:v>-11217000</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
         <x:f>SUM($D$5:D14)</x:f>
-        <x:v>53430175</x:v>
+        <x:v>39391955</x:v>
       </x:c>
       <x:c r="F14" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A14,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>11217000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
@@ -51246,19 +54018,19 @@
       </x:c>
       <x:c r="C15" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A15)</x:f>
-        <x:v>0</x:v>
+        <x:v>9150000</x:v>
       </x:c>
       <x:c r="D15" s="10" t="n">
         <x:f>B15-C15</x:f>
-        <x:v>0</x:v>
+        <x:v>-9150000</x:v>
       </x:c>
       <x:c r="E15" s="10" t="n">
         <x:f>SUM($D$5:D15)</x:f>
-        <x:v>53430175</x:v>
+        <x:v>30241955</x:v>
       </x:c>
       <x:c r="F15" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A15,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>9150000</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
@@ -51271,19 +54043,19 @@
       </x:c>
       <x:c r="C16" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A16)</x:f>
-        <x:v>5000000</x:v>
+        <x:v>39775150</x:v>
       </x:c>
       <x:c r="D16" s="10" t="n">
         <x:f>B16-C16</x:f>
-        <x:v>18000000</x:v>
+        <x:v>-16775150</x:v>
       </x:c>
       <x:c r="E16" s="10" t="n">
         <x:f>SUM($D$5:D16)</x:f>
-        <x:v>71430175</x:v>
+        <x:v>13466805</x:v>
       </x:c>
       <x:c r="F16" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A16,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>24787250</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
@@ -51304,7 +54076,7 @@
       </x:c>
       <x:c r="E17" s="10" t="n">
         <x:f>SUM($D$5:D17)</x:f>
-        <x:v>71430175</x:v>
+        <x:v>13466805</x:v>
       </x:c>
       <x:c r="F17" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A17,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51312,10 +54084,13 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e5116a1defc43c9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f0135e3e0584163"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf61718cd47914f51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ba6036f48843ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51341,7 +54116,7 @@
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="1"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
         <x:v>Project cash activity | not accrual profitability</x:v>
       </x:c>
@@ -51468,11 +54243,11 @@
       </x:c>
       <x:c r="C9" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A9)</x:f>
-        <x:v>5000000</x:v>
+        <x:v>5950000</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
         <x:f>B9-C9</x:f>
-        <x:v>18000000</x:v>
+        <x:v>17050000</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A9,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51523,7 +54298,7 @@
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="8" t="str">
-        <x:v>Tea &amp; Physics society</x:v>
+        <x:v>Summer School 1405</x:v>
       </x:c>
       <x:c r="B12" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A12)</x:f>
@@ -51531,11 +54306,11 @@
       </x:c>
       <x:c r="C12" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A12)</x:f>
-        <x:v>1702850</x:v>
+        <x:v>11500000</x:v>
       </x:c>
       <x:c r="D12" s="10" t="n">
         <x:f>B12-C12</x:f>
-        <x:v>-1702850</x:v>
+        <x:v>-11500000</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A12,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51544,7 +54319,7 @@
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Tea &amp; Physics society</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A13)</x:f>
@@ -51552,20 +54327,20 @@
       </x:c>
       <x:c r="C13" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A13)</x:f>
-        <x:v>0</x:v>
+        <x:v>1702850</x:v>
       </x:c>
       <x:c r="D13" s="10" t="n">
         <x:f>B13-C13</x:f>
-        <x:v>0</x:v>
+        <x:v>-1702850</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A13,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>2821220</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="B14" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A14)</x:f>
@@ -51573,15 +54348,15 @@
       </x:c>
       <x:c r="C14" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A14)</x:f>
-        <x:v>0</x:v>
+        <x:v>45513370</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
         <x:f>B14-C14</x:f>
-        <x:v>0</x:v>
+        <x:v>-45513370</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A14,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>39504250</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
@@ -51607,71 +54382,32 @@
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="8" t="str">
-        <x:v>Unknown (possibly Intro Event 1405)</x:v>
+        <x:v>Yalda 1404</x:v>
       </x:c>
       <x:c r="B16" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A16)</x:f>
-        <x:v>0</x:v>
+        <x:v>16490000</x:v>
       </x:c>
       <x:c r="C16" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A16)</x:f>
-        <x:v>0</x:v>
+        <x:v>6367000</x:v>
       </x:c>
       <x:c r="D16" s="10" t="n">
         <x:f>B16-C16</x:f>
-        <x:v>0</x:v>
+        <x:v>10123000</x:v>
       </x:c>
       <x:c r="E16" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A16,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>5650000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="27" customHeight="1">
-      <x:c r="A17" s="8" t="str">
-        <x:v>Unknown (possibly Intro Event 1405, 1405/07/02)</x:v>
-      </x:c>
-      <x:c r="B17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="10" t="n">
-        <x:f>B17-C17</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A17,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="27" customHeight="1">
-      <x:c r="A18" s="8" t="str">
-        <x:v>Yalda 1404</x:v>
-      </x:c>
-      <x:c r="B18" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A18)</x:f>
-        <x:v>16490000</x:v>
-      </x:c>
-      <x:c r="C18" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A18)</x:f>
-        <x:v>6367000</x:v>
-      </x:c>
-      <x:c r="D18" s="10" t="n">
-        <x:f>B18-C18</x:f>
-        <x:v>10123000</x:v>
-      </x:c>
-      <x:c r="E18" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A18,'Transactions'!$N$5:$N$99,"Review")</x:f>
         <x:v>7921723.9</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc63eba1f5a2940e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R548e1b0b8dbf4a7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51697,7 +54433,7 @@
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="1"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
         <x:v>Cash receipts and payments by category</x:v>
       </x:c>
@@ -51866,11 +54602,11 @@
       </x:c>
       <x:c r="C11" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A11)</x:f>
-        <x:v>2990225</x:v>
+        <x:v>12978125</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
         <x:f>B11-C11</x:f>
-        <x:v>-2990225</x:v>
+        <x:v>-12978125</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A11,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51929,11 +54665,11 @@
       </x:c>
       <x:c r="C14" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A14)</x:f>
-        <x:v>1296100</x:v>
+        <x:v>2246100</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
         <x:f>B14-C14</x:f>
-        <x:v>-1296100</x:v>
+        <x:v>-2246100</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A14,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51950,11 +54686,11 @@
       </x:c>
       <x:c r="C15" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A15)</x:f>
-        <x:v>12500000</x:v>
+        <x:v>24000000</x:v>
       </x:c>
       <x:c r="D15" s="10" t="n">
         <x:f>B15-C15</x:f>
-        <x:v>-12500000</x:v>
+        <x:v>-24000000</x:v>
       </x:c>
       <x:c r="E15" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A15,'Transactions'!$N$5:$N$99,"Review")</x:f>
@@ -51992,26 +54728,382 @@
       </x:c>
       <x:c r="C17" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A17)</x:f>
-        <x:v>0</x:v>
+        <x:v>35525470</x:v>
       </x:c>
       <x:c r="D17" s="10" t="n">
         <x:f>B17-C17</x:f>
-        <x:v>0</x:v>
+        <x:v>-35525470</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
         <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A17,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>48275470</x:v>
+        <x:v>300000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:E2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f19fae59dd44098"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0477bb1193294e00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFEDF2F7"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="43" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="100" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="85" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+      <x:c r="C1" s="33"/>
+      <x:c r="D1" s="33"/>
+      <x:c r="E1" s="33"/>
+      <x:c r="F1" s="33"/>
+      <x:c r="G1" s="33"/>
+      <x:c r="H1" s="33"/>
+      <x:c r="I1" s="33"/>
+      <x:c r="J1" s="33"/>
+      <x:c r="K1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
+        <x:v>Summer School 1405 instructor payments | five of six identified</x:v>
+      </x:c>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
+      <x:c r="G2" s="33"/>
+      <x:c r="H2" s="33"/>
+      <x:c r="I2" s="33"/>
+      <x:c r="J2" s="33"/>
+      <x:c r="K2" s="33"/>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
+      <x:c r="H3" s="33"/>
+      <x:c r="I3" s="33"/>
+      <x:c r="J3" s="33"/>
+      <x:c r="K3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="24" hidden="0" customHeight="1">
+      <x:c r="A4" s="7" t="str">
+        <x:v>Transaction ID</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>Instructor beneficiary</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>Bank account payee</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>Course</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>Jalali date</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>Gregorian date</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>Amount (toman)</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
+        <x:v>User-provided card ending (not printed)</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str">
+        <x:v>Matching basis</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="str">
+        <x:v>Settlement basis</x:v>
+      </x:c>
+      <x:c r="K4" s="7" t="str">
+        <x:v>Source reference</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" hidden="0" customHeight="1">
+      <x:c r="A5" s="31" t="str">
+        <x:v>TX0083</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
+        <x:v>زهرا صالح کوشالی</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>زهرا صالح کوشالی</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>Course not specified</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
+        <x:v>1405/06/30</x:v>
+      </x:c>
+      <x:c r="F5" s="31" t="str">
+        <x:v>2026-09-21</x:v>
+      </x:c>
+      <x:c r="G5" s="35" t="n">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="H5" s="36" t="str">
+        <x:v>6104</x:v>
+      </x:c>
+      <x:c r="I5" s="31" t="str">
+        <x:v>Exact normalized recipient name; source is IBAN/Pol, not a card transfer.</x:v>
+      </x:c>
+      <x:c r="J5" s="31" t="str">
+        <x:v>User confirmation; original provisional notice preserved</x:v>
+      </x:c>
+      <x:c r="K5" s="31" t="str">
+        <x:v>recipts/photo_1_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" hidden="0" customHeight="1">
+      <x:c r="A6" s="31" t="str">
+        <x:v>TX0084</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="str">
+        <x:v>رضا فرهادی</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>رضا فرهادی</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="str">
+        <x:v>Course not specified</x:v>
+      </x:c>
+      <x:c r="E6" s="31" t="str">
+        <x:v>1405/06/30</x:v>
+      </x:c>
+      <x:c r="F6" s="31" t="str">
+        <x:v>2026-09-21</x:v>
+      </x:c>
+      <x:c r="G6" s="35" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+      <x:c r="H6" s="36" t="str">
+        <x:v>2692</x:v>
+      </x:c>
+      <x:c r="I6" s="31" t="str">
+        <x:v>Exact normalized recipient name; source is IBAN/Pol transfer.</x:v>
+      </x:c>
+      <x:c r="J6" s="31" t="str">
+        <x:v>User confirmation; original provisional notice preserved</x:v>
+      </x:c>
+      <x:c r="K6" s="31" t="str">
+        <x:v>recipts/photo_2_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="24" hidden="0" customHeight="1">
+      <x:c r="A7" s="31" t="str">
+        <x:v>TX0085</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="str">
+        <x:v>ابوالفضل احمدی</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>علیرضا کچویی محقق یعقوبی</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="str">
+        <x:v>LaTeX and API</x:v>
+      </x:c>
+      <x:c r="E7" s="31" t="str">
+        <x:v>1405/06/30</x:v>
+      </x:c>
+      <x:c r="F7" s="31" t="str">
+        <x:v>2026-09-21</x:v>
+      </x:c>
+      <x:c r="G7" s="35" t="n">
+        <x:v>2400000</x:v>
+      </x:c>
+      <x:c r="H7" s="36" t="str"/>
+      <x:c r="I7" s="31" t="str">
+        <x:v>Explicit user confirmation that payment to Alireza was instructor fee for Abolfazl.</x:v>
+      </x:c>
+      <x:c r="J7" s="31" t="str">
+        <x:v>Receipt and user confirmation</x:v>
+      </x:c>
+      <x:c r="K7" s="31" t="str">
+        <x:v>recipts/photo_3_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
+      <x:c r="A8" s="31" t="str">
+        <x:v>TX0086</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="str">
+        <x:v>بهاره خویش خواه</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>بهاره خویش‌خواه</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="str">
+        <x:v>Physical simulation with Python</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="str">
+        <x:v>1405/07/01</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="G8" s="35" t="n">
+        <x:v>4700000</x:v>
+      </x:c>
+      <x:c r="H8" s="36" t="str">
+        <x:v>5740</x:v>
+      </x:c>
+      <x:c r="I8" s="31" t="str">
+        <x:v>Exact normalized recipient name and stated amount. Receipt is an IBAN/Paya transfer, so the supplied card is corroborative contact detail, not an exact on-document card match.</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="str">
+        <x:v>Receipt and user confirmation</x:v>
+      </x:c>
+      <x:c r="K8" s="31" t="str">
+        <x:v>recipts/photo_7_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
+      <x:c r="A9" s="31" t="str">
+        <x:v>TX0087</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>ایلیا اصغریان دهکردی</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>ایلیا اصغریان دهکردی</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="str">
+        <x:v>Course not specified</x:v>
+      </x:c>
+      <x:c r="E9" s="31" t="str">
+        <x:v>1405/07/01</x:v>
+      </x:c>
+      <x:c r="F9" s="31" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="G9" s="35" t="n">
+        <x:v>2600000</x:v>
+      </x:c>
+      <x:c r="H9" s="36" t="str">
+        <x:v>6676</x:v>
+      </x:c>
+      <x:c r="I9" s="31" t="str">
+        <x:v>Exact normalized recipient name; Blu-to-Blu transfer to IBAN. Card supplied by user, not printed on receipt.</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="str">
+        <x:v>Receipt and user confirmation</x:v>
+      </x:c>
+      <x:c r="K9" s="31" t="str">
+        <x:v>recipts/photo_8_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="29"/>
+      <x:c r="B10" s="29"/>
+      <x:c r="C10" s="29"/>
+      <x:c r="D10" s="29"/>
+      <x:c r="E10" s="29"/>
+      <x:c r="F10" s="29"/>
+      <x:c r="G10" s="29"/>
+      <x:c r="H10" s="29"/>
+      <x:c r="I10" s="29"/>
+      <x:c r="J10" s="29"/>
+      <x:c r="K10" s="29"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="29"/>
+      <x:c r="B11" s="29"/>
+      <x:c r="C11" s="29"/>
+      <x:c r="D11" s="29"/>
+      <x:c r="E11" s="29"/>
+      <x:c r="F11" s="29"/>
+      <x:c r="G11" s="29"/>
+      <x:c r="H11" s="29"/>
+      <x:c r="I11" s="29"/>
+      <x:c r="J11" s="29"/>
+      <x:c r="K11" s="29"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="32" t="str">
+        <x:v>Sixth instructor payment: not yet identified; already-recorded folder payments must not be duplicated.</x:v>
+      </x:c>
+      <x:c r="B12" s="32"/>
+      <x:c r="C12" s="32"/>
+      <x:c r="D12" s="32"/>
+      <x:c r="E12" s="32"/>
+      <x:c r="F12" s="32"/>
+      <x:c r="G12" s="29"/>
+      <x:c r="H12" s="29"/>
+      <x:c r="I12" s="29"/>
+      <x:c r="J12" s="29"/>
+      <x:c r="K12" s="29"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="32"/>
+      <x:c r="B13" s="32"/>
+      <x:c r="C13" s="32"/>
+      <x:c r="D13" s="32"/>
+      <x:c r="E13" s="32"/>
+      <x:c r="F13" s="32"/>
+      <x:c r="G13" s="29"/>
+      <x:c r="H13" s="29"/>
+      <x:c r="I13" s="29"/>
+      <x:c r="J13" s="29"/>
+      <x:c r="K13" s="29"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="32"/>
+      <x:c r="B14" s="32"/>
+      <x:c r="C14" s="32"/>
+      <x:c r="D14" s="32"/>
+      <x:c r="E14" s="32"/>
+      <x:c r="F14" s="32"/>
+      <x:c r="G14" s="29"/>
+      <x:c r="H14" s="29"/>
+      <x:c r="I14" s="29"/>
+      <x:c r="J14" s="29"/>
+      <x:c r="K14" s="29"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A12:F14"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree2b4ec7ce2d4059"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFEDF2F7"/>
@@ -52027,30 +55119,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="32"/>
-      <x:c r="B1" s="32"/>
-      <x:c r="C1" s="32"/>
-      <x:c r="D1" s="32"/>
-      <x:c r="E1" s="32"/>
-      <x:c r="F1" s="32"/>
-    </x:row>
-    <x:row r="2" ht="33.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A2" s="33" t="str">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+      <x:c r="C1" s="33"/>
+      <x:c r="D1" s="33"/>
+      <x:c r="E1" s="33"/>
+      <x:c r="F1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
         <x:v>Original ledger rows reconciled to evidence</x:v>
       </x:c>
-      <x:c r="B2" s="32"/>
-      <x:c r="C2" s="32"/>
-      <x:c r="D2" s="32"/>
-      <x:c r="E2" s="32"/>
-      <x:c r="F2" s="32"/>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="32"/>
-      <x:c r="B3" s="32"/>
-      <x:c r="C3" s="32"/>
-      <x:c r="D3" s="32"/>
-      <x:c r="E3" s="32"/>
-      <x:c r="F3" s="32"/>
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -52079,7 +55171,7 @@
       <x:c r="B5" s="31" t="str">
         <x:v>B3</x:v>
       </x:c>
-      <x:c r="C5" s="34" t="n">
+      <x:c r="C5" s="35" t="n">
         <x:v>33642000</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
@@ -52099,7 +55191,7 @@
       <x:c r="B6" s="31" t="str">
         <x:v>D2</x:v>
       </x:c>
-      <x:c r="C6" s="34" t="n">
+      <x:c r="C6" s="35" t="n">
         <x:v>3500000</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
@@ -52119,7 +55211,7 @@
       <x:c r="B7" s="31" t="str">
         <x:v>D3</x:v>
       </x:c>
-      <x:c r="C7" s="34" t="n">
+      <x:c r="C7" s="35" t="n">
         <x:v>3000000</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
@@ -52139,7 +55231,7 @@
       <x:c r="B8" s="31" t="str">
         <x:v>D4</x:v>
       </x:c>
-      <x:c r="C8" s="34" t="n">
+      <x:c r="C8" s="35" t="n">
         <x:v>3700000</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
@@ -52159,7 +55251,7 @@
       <x:c r="B9" s="31" t="str">
         <x:v>D5</x:v>
       </x:c>
-      <x:c r="C9" s="34" t="n">
+      <x:c r="C9" s="35" t="n">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
@@ -52179,7 +55271,7 @@
       <x:c r="B10" s="31" t="str">
         <x:v>D6</x:v>
       </x:c>
-      <x:c r="C10" s="34" t="n">
+      <x:c r="C10" s="35" t="n">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
@@ -52199,7 +55291,7 @@
       <x:c r="B11" s="31" t="str">
         <x:v>D7</x:v>
       </x:c>
-      <x:c r="C11" s="34" t="n">
+      <x:c r="C11" s="35" t="n">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
@@ -52219,7 +55311,7 @@
       <x:c r="B12" s="31" t="str">
         <x:v>D8</x:v>
       </x:c>
-      <x:c r="C12" s="34" t="n">
+      <x:c r="C12" s="35" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
@@ -52239,7 +55331,7 @@
       <x:c r="B13" s="31" t="str">
         <x:v>D9</x:v>
       </x:c>
-      <x:c r="C13" s="34" t="n">
+      <x:c r="C13" s="35" t="n">
         <x:v>400000</x:v>
       </x:c>
       <x:c r="D13" s="31" t="str">
@@ -52259,7 +55351,7 @@
       <x:c r="B14" s="31" t="str">
         <x:v>D10</x:v>
       </x:c>
-      <x:c r="C14" s="34" t="n">
+      <x:c r="C14" s="35" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D14" s="31" t="str">
@@ -52279,7 +55371,7 @@
       <x:c r="B15" s="31" t="str">
         <x:v>D11</x:v>
       </x:c>
-      <x:c r="C15" s="34" t="n">
+      <x:c r="C15" s="35" t="n">
         <x:v>750000</x:v>
       </x:c>
       <x:c r="D15" s="31" t="str">
@@ -52299,7 +55391,7 @@
       <x:c r="B16" s="31" t="str">
         <x:v>D12</x:v>
       </x:c>
-      <x:c r="C16" s="34" t="n">
+      <x:c r="C16" s="35" t="n">
         <x:v>400000</x:v>
       </x:c>
       <x:c r="D16" s="31" t="str">
@@ -52319,7 +55411,7 @@
       <x:c r="B17" s="31" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="C17" s="34" t="n">
+      <x:c r="C17" s="35" t="n">
         <x:v>4920000</x:v>
       </x:c>
       <x:c r="D17" s="31" t="str">
@@ -52339,7 +55431,7 @@
       <x:c r="B18" s="31" t="str">
         <x:v>D15</x:v>
       </x:c>
-      <x:c r="C18" s="34" t="n">
+      <x:c r="C18" s="35" t="n">
         <x:v>100000</x:v>
       </x:c>
       <x:c r="D18" s="31" t="str">
@@ -52359,7 +55451,7 @@
       <x:c r="B19" s="31" t="str">
         <x:v>D16</x:v>
       </x:c>
-      <x:c r="C19" s="34" t="n">
+      <x:c r="C19" s="35" t="n">
         <x:v>2866000</x:v>
       </x:c>
       <x:c r="D19" s="31" t="str">
@@ -52379,7 +55471,7 @@
       <x:c r="B20" s="31" t="str">
         <x:v>D17</x:v>
       </x:c>
-      <x:c r="C20" s="34" t="n">
+      <x:c r="C20" s="35" t="n">
         <x:v>189000</x:v>
       </x:c>
       <x:c r="D20" s="31" t="str">
@@ -52399,7 +55491,7 @@
       <x:c r="B21" s="31" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="C21" s="34" t="n">
+      <x:c r="C21" s="35" t="n">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D21" s="31" t="str">
@@ -52419,7 +55511,7 @@
       <x:c r="B22" s="31" t="str">
         <x:v>D19</x:v>
       </x:c>
-      <x:c r="C22" s="34" t="n">
+      <x:c r="C22" s="35" t="n">
         <x:v>90000</x:v>
       </x:c>
       <x:c r="D22" s="31" t="str">
@@ -52439,7 +55531,7 @@
       <x:c r="B23" s="31" t="str">
         <x:v>D20</x:v>
       </x:c>
-      <x:c r="C23" s="34" t="n">
+      <x:c r="C23" s="35" t="n">
         <x:v>1052375</x:v>
       </x:c>
       <x:c r="D23" s="31" t="str">
@@ -52459,7 +55551,7 @@
       <x:c r="B24" s="31" t="str">
         <x:v>D21</x:v>
       </x:c>
-      <x:c r="C24" s="34" t="n">
+      <x:c r="C24" s="35" t="n">
         <x:v>790000</x:v>
       </x:c>
       <x:c r="D24" s="31" t="str">
@@ -52479,7 +55571,7 @@
       <x:c r="B25" s="31" t="str">
         <x:v>D22</x:v>
       </x:c>
-      <x:c r="C25" s="34" t="n">
+      <x:c r="C25" s="35" t="n">
         <x:v>912850</x:v>
       </x:c>
       <x:c r="D25" s="31" t="str">
@@ -52499,7 +55591,7 @@
       <x:c r="B26" s="31" t="str">
         <x:v>D23</x:v>
       </x:c>
-      <x:c r="C26" s="34" t="n">
+      <x:c r="C26" s="35" t="n">
         <x:v>1052375</x:v>
       </x:c>
       <x:c r="D26" s="31" t="str">
@@ -52519,7 +55611,7 @@
       <x:c r="B27" s="31" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="C27" s="34" t="n">
+      <x:c r="C27" s="35" t="n">
         <x:v>11000000</x:v>
       </x:c>
       <x:c r="D27" s="31" t="str">
@@ -52539,7 +55631,7 @@
       <x:c r="B28" s="31" t="str">
         <x:v>D25</x:v>
       </x:c>
-      <x:c r="C28" s="34" t="n">
+      <x:c r="C28" s="35" t="n">
         <x:v>725000</x:v>
       </x:c>
       <x:c r="D28" s="31" t="str">
@@ -52559,7 +55651,7 @@
       <x:c r="B29" s="31" t="str">
         <x:v>D26</x:v>
       </x:c>
-      <x:c r="C29" s="34" t="n">
+      <x:c r="C29" s="35" t="n">
         <x:v>120000</x:v>
       </x:c>
       <x:c r="D29" s="31" t="str">
@@ -52579,7 +55671,7 @@
       <x:c r="B30" s="31" t="str">
         <x:v>D27</x:v>
       </x:c>
-      <x:c r="C30" s="34" t="n">
+      <x:c r="C30" s="35" t="n">
         <x:v>1310000</x:v>
       </x:c>
       <x:c r="D30" s="31" t="str">
@@ -52599,7 +55691,7 @@
       <x:c r="B31" s="31" t="str">
         <x:v>D28</x:v>
       </x:c>
-      <x:c r="C31" s="34" t="n">
+      <x:c r="C31" s="35" t="n">
         <x:v>4344000</x:v>
       </x:c>
       <x:c r="D31" s="31" t="str">
@@ -52619,7 +55711,7 @@
       <x:c r="B32" s="31" t="str">
         <x:v>D29</x:v>
       </x:c>
-      <x:c r="C32" s="34" t="n">
+      <x:c r="C32" s="35" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D32" s="31" t="str">
@@ -52639,7 +55731,7 @@
       <x:c r="B33" s="31" t="str">
         <x:v>D30</x:v>
       </x:c>
-      <x:c r="C33" s="34" t="n">
+      <x:c r="C33" s="35" t="n">
         <x:v>70000</x:v>
       </x:c>
       <x:c r="D33" s="31" t="str">
@@ -52659,7 +55751,7 @@
       <x:c r="B34" s="31" t="str">
         <x:v>D31</x:v>
       </x:c>
-      <x:c r="C34" s="34" t="n">
+      <x:c r="C34" s="35" t="n">
         <x:v>310000</x:v>
       </x:c>
       <x:c r="D34" s="31" t="str">
@@ -52679,7 +55771,7 @@
       <x:c r="B35" s="31" t="str">
         <x:v>D32</x:v>
       </x:c>
-      <x:c r="C35" s="34" t="n">
+      <x:c r="C35" s="35" t="n">
         <x:v>1760000</x:v>
       </x:c>
       <x:c r="D35" s="31" t="str">
@@ -52699,7 +55791,7 @@
       <x:c r="B36" s="31" t="str">
         <x:v>D33</x:v>
       </x:c>
-      <x:c r="C36" s="34" t="n">
+      <x:c r="C36" s="35" t="n">
         <x:v>230000</x:v>
       </x:c>
       <x:c r="D36" s="31" t="str">
@@ -52719,7 +55811,7 @@
       <x:c r="B37" s="31" t="str">
         <x:v>D34</x:v>
       </x:c>
-      <x:c r="C37" s="34" t="n">
+      <x:c r="C37" s="35" t="n">
         <x:v>1226100</x:v>
       </x:c>
       <x:c r="D37" s="31" t="str">
@@ -52739,7 +55831,7 @@
       <x:c r="B38" s="31" t="str">
         <x:v>D35</x:v>
       </x:c>
-      <x:c r="C38" s="34" t="n">
+      <x:c r="C38" s="35" t="n">
         <x:v>2300</x:v>
       </x:c>
       <x:c r="D38" s="31" t="str">
@@ -52759,7 +55851,7 @@
       <x:c r="B39" s="31" t="str">
         <x:v>D36</x:v>
       </x:c>
-      <x:c r="C39" s="34" t="n">
+      <x:c r="C39" s="35" t="n">
         <x:v>1300</x:v>
       </x:c>
       <x:c r="D39" s="31" t="str">
@@ -52779,7 +55871,7 @@
       <x:c r="B40" s="31" t="str">
         <x:v>B38</x:v>
       </x:c>
-      <x:c r="C40" s="34" t="n">
+      <x:c r="C40" s="35" t="n">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="D40" s="31" t="str">
@@ -52799,7 +55891,7 @@
       <x:c r="B41" s="31" t="str">
         <x:v>B39</x:v>
       </x:c>
-      <x:c r="C41" s="34" t="n">
+      <x:c r="C41" s="35" t="n">
         <x:v>7000000</x:v>
       </x:c>
       <x:c r="D41" s="31" t="str">
@@ -52819,7 +55911,7 @@
       <x:c r="B42" s="31" t="str">
         <x:v>B40</x:v>
       </x:c>
-      <x:c r="C42" s="34" t="n">
+      <x:c r="C42" s="35" t="n">
         <x:v>6000000</x:v>
       </x:c>
       <x:c r="D42" s="31" t="str">
@@ -52839,7 +55931,7 @@
       <x:c r="B43" s="31" t="str">
         <x:v>B42</x:v>
       </x:c>
-      <x:c r="C43" s="34" t="n">
+      <x:c r="C43" s="35" t="n">
         <x:v>15790000</x:v>
       </x:c>
       <x:c r="D43" s="31" t="str">
@@ -52859,7 +55951,7 @@
       <x:c r="B44" s="31" t="str">
         <x:v>D42</x:v>
       </x:c>
-      <x:c r="C44" s="34" t="n">
+      <x:c r="C44" s="35" t="n">
         <x:v>2137000</x:v>
       </x:c>
       <x:c r="D44" s="31" t="str">
@@ -52879,7 +55971,7 @@
       <x:c r="B45" s="31" t="str">
         <x:v>B43</x:v>
       </x:c>
-      <x:c r="C45" s="34" t="n">
+      <x:c r="C45" s="35" t="n">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D45" s="31" t="str">
@@ -52899,7 +55991,7 @@
       <x:c r="B46" s="31" t="str">
         <x:v>B45</x:v>
       </x:c>
-      <x:c r="C46" s="34" t="n">
+      <x:c r="C46" s="35" t="n">
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="D46" s="31" t="str">
@@ -52919,7 +56011,7 @@
       <x:c r="B47" s="31" t="str">
         <x:v>D45</x:v>
       </x:c>
-      <x:c r="C47" s="34" t="n">
+      <x:c r="C47" s="35" t="n">
         <x:v>5000000</x:v>
       </x:c>
       <x:c r="D47" s="31" t="str">
@@ -52933,14 +56025,17 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raae17b0ad18a4f48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdd9538190054bb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFEDF2F7"/>
@@ -53001,7 +56096,7 @@
       <x:c r="X1" s="1"/>
       <x:c r="Y1" s="1"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
         <x:v>Association transaction ledger | all amounts in toman</x:v>
       </x:c>
@@ -54716,7 +57811,7 @@
         <x:v>-790000</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
+    <x:row r="26" ht="24" hidden="0" customHeight="1">
       <x:c r="A26" s="8" t="str">
         <x:v>TX0022</x:v>
       </x:c>
@@ -54776,10 +57871,11 @@
         <x:v>Same tracking ID, time and balance as TX0021.</x:v>
       </x:c>
       <x:c r="U26" s="31" t="str">
-        <x:v>Excluded.</x:v>
+        <x:v>Excluded. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified.</x:v>
       </x:c>
       <x:c r="V26" s="31" t="str">
-        <x:v>recipts/photo_1_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_1_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W26" s="13" t="n">
         <x:f>IF(AND(N26="Supported",E26="Receipt",ISNUMBER(H26)),H26,0)</x:f>
@@ -56332,7 +59428,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="15" hidden="0" customHeight="1">
+    <x:row r="47" ht="36" hidden="0" customHeight="1">
       <x:c r="A47" s="8" t="str">
         <x:v>TX0043</x:v>
       </x:c>
@@ -56370,13 +59466,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M47" s="8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N47" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O47" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P47" s="8" t="str">
         <x:v>SHAHR-8966</x:v>
@@ -56386,14 +59482,13 @@
         <x:v>406547</x:v>
       </x:c>
       <x:c r="S47" s="8"/>
-      <x:c r="T47" s="31" t="str">
-        <x:v>Association account debit with no purpose and no ledger row.</x:v>
-      </x:c>
+      <x:c r="T47" s="31" t="str"/>
       <x:c r="U47" s="31" t="str">
-        <x:v>Balance after: 121,745,270 rial.</x:v>
+        <x:v>Balance after: 121,745,270 rial. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown. Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V47" s="31" t="str">
-        <x:v>recipts/photo_4_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_4_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W47" s="13" t="n">
         <x:f>IF(AND(N47="Supported",E47="Receipt",ISNUMBER(H47)),H47,0)</x:f>
@@ -56401,11 +59496,11 @@
       </x:c>
       <x:c r="X47" s="13" t="n">
         <x:f>IF(AND(N47="Supported",E47="Payment",ISNUMBER(H47)),H47,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1020000</x:v>
       </x:c>
       <x:c r="Y47" s="13" t="n">
         <x:f>W47-X47</x:f>
-        <x:v>0</x:v>
+        <x:v>-1020000</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="24" hidden="0" customHeight="1">
@@ -57673,7 +60768,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="15" hidden="0" customHeight="1">
+    <x:row r="65" ht="36" hidden="0" customHeight="1">
       <x:c r="A65" s="8" t="str">
         <x:v>TX0061</x:v>
       </x:c>
@@ -57687,7 +60782,7 @@
         <x:v>1404/12</x:v>
       </x:c>
       <x:c r="E65" s="8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Payment</x:v>
       </x:c>
       <x:c r="F65" s="11" t="n">
         <x:v>18012200</x:v>
@@ -57702,7 +60797,7 @@
         <x:v>Card 6221061239419676 (owner unknown)</x:v>
       </x:c>
       <x:c r="J65" s="31" t="str">
-        <x:v>Transfer from association card, purpose and payee unknown</x:v>
+        <x:v>Association payment, purpose and payee allocation pending</x:v>
       </x:c>
       <x:c r="K65" s="31" t="str">
         <x:v>انتقال از کارت انجمن، بابت نامشخص</x:v>
@@ -57711,13 +60806,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M65" s="8" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N65" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O65" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P65" s="8" t="str">
         <x:v>SHAHR-8966</x:v>
@@ -57725,14 +60820,13 @@
       <x:c r="Q65" s="8" t="str"/>
       <x:c r="R65" s="8"/>
       <x:c r="S65" s="8"/>
-      <x:c r="T65" s="31" t="str">
-        <x:v>Could be an expense or an internal transfer to the custodian.</x:v>
-      </x:c>
+      <x:c r="T65" s="31" t="str"/>
       <x:c r="U65" s="31" t="str">
-        <x:v>Balance after: 12,262,895 rial.</x:v>
+        <x:v>Balance after: 12,262,895 rial. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown. Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V65" s="31" t="str">
-        <x:v>recipts/photo_6_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_6_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W65" s="13" t="n">
         <x:f>IF(AND(N65="Supported",E65="Receipt",ISNUMBER(H65)),H65,0)</x:f>
@@ -57740,11 +60834,11 @@
       </x:c>
       <x:c r="X65" s="13" t="n">
         <x:f>IF(AND(N65="Supported",E65="Payment",ISNUMBER(H65)),H65,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1801220</x:v>
       </x:c>
       <x:c r="Y65" s="13" t="n">
         <x:f>W65-X65</x:f>
-        <x:v>0</x:v>
+        <x:v>-1801220</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -58743,7 +61837,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="36" hidden="0" customHeight="1">
+    <x:row r="79" ht="60" hidden="0" customHeight="1">
       <x:c r="A79" s="8" t="str">
         <x:v>TX0075</x:v>
       </x:c>
@@ -58781,13 +61875,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M79" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N79" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O79" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P79" s="8" t="str">
         <x:v>SHAHR-2167</x:v>
@@ -58797,14 +61891,13 @@
         <x:v>187300</x:v>
       </x:c>
       <x:c r="S79" s="8"/>
-      <x:c r="T79" s="31" t="str">
-        <x:v>No purpose and no ledger row. Second card on the same deposit.</x:v>
-      </x:c>
+      <x:c r="T79" s="31" t="str"/>
       <x:c r="U79" s="31" t="str">
-        <x:v>Balance after: 260,305,702 rial. The debit is on deposit 400816808774, the same deposit as SHAHR-8966, using a second card (…2167). The cash_account label 'SHAHR-2167' must not be read as a separate account. Card ownership is unconfirmed.</x:v>
+        <x:v>Balance after: 260,305,702 rial. The debit is on deposit 400816808774, the same deposit as SHAHR-8966, using a second card (…2167). The cash_account label 'SHAHR-2167' must not be read as a separate account. Card ownership is unconfirmed. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V79" s="31" t="str">
-        <x:v>recipts/photo_3_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_3_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W79" s="13" t="n">
         <x:f>IF(AND(N79="Supported",E79="Receipt",ISNUMBER(H79)),H79,0)</x:f>
@@ -58812,14 +61905,14 @@
       </x:c>
       <x:c r="X79" s="13" t="n">
         <x:f>IF(AND(N79="Supported",E79="Payment",ISNUMBER(H79)),H79,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>6337000</x:v>
       </x:c>
       <x:c r="Y79" s="13" t="n">
         <x:f>W79-X79</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="15" hidden="0" customHeight="1">
+        <x:v>-6337000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="36" hidden="0" customHeight="1">
       <x:c r="A80" s="8" t="str">
         <x:v>TX0076</x:v>
       </x:c>
@@ -58857,13 +61950,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M80" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N80" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O80" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P80" s="8" t="str">
         <x:v>SHAHR-2167</x:v>
@@ -58873,14 +61966,13 @@
         <x:v>308839</x:v>
       </x:c>
       <x:c r="S80" s="8"/>
-      <x:c r="T80" s="31" t="str">
-        <x:v>Purpose unknown.</x:v>
-      </x:c>
+      <x:c r="T80" s="31" t="str"/>
       <x:c r="U80" s="31" t="str">
-        <x:v>Balance 217,675,702 rial.</x:v>
+        <x:v>Balance 217,675,702 rial. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V80" s="31" t="str">
-        <x:v>recipts/photo_2_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_2_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W80" s="13" t="n">
         <x:f>IF(AND(N80="Supported",E80="Receipt",ISNUMBER(H80)),H80,0)</x:f>
@@ -58888,14 +61980,14 @@
       </x:c>
       <x:c r="X80" s="13" t="n">
         <x:f>IF(AND(N80="Supported",E80="Payment",ISNUMBER(H80)),H80,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="Y80" s="13" t="n">
         <x:f>W80-X80</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="15" hidden="0" customHeight="1">
+        <x:v>-1100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="36" hidden="0" customHeight="1">
       <x:c r="A81" s="8" t="str">
         <x:v>TX0077</x:v>
       </x:c>
@@ -58933,13 +62025,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M81" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N81" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O81" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P81" s="8" t="str">
         <x:v>SHAHR-2167</x:v>
@@ -58949,14 +62041,13 @@
         <x:v>666086</x:v>
       </x:c>
       <x:c r="S81" s="8"/>
-      <x:c r="T81" s="31" t="str">
-        <x:v>Purpose unknown.</x:v>
-      </x:c>
+      <x:c r="T81" s="31" t="str"/>
       <x:c r="U81" s="31" t="str">
-        <x:v>Balance chain consistent: 204,475,702 rial.</x:v>
+        <x:v>Balance chain consistent: 204,475,702 rial. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V81" s="31" t="str">
-        <x:v>recipts/photo_5_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_5_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W81" s="13" t="n">
         <x:f>IF(AND(N81="Supported",E81="Receipt",ISNUMBER(H81)),H81,0)</x:f>
@@ -58964,14 +62055,14 @@
       </x:c>
       <x:c r="X81" s="13" t="n">
         <x:f>IF(AND(N81="Supported",E81="Payment",ISNUMBER(H81)),H81,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1320000</x:v>
       </x:c>
       <x:c r="Y81" s="13" t="n">
         <x:f>W81-X81</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="15" hidden="0" customHeight="1">
+        <x:v>-1320000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="36" hidden="0" customHeight="1">
       <x:c r="A82" s="8" t="str">
         <x:v>TX0078</x:v>
       </x:c>
@@ -59009,13 +62100,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M82" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N82" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O82" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P82" s="8" t="str">
         <x:v>SHAHR-2167</x:v>
@@ -59025,14 +62116,13 @@
         <x:v>008584</x:v>
       </x:c>
       <x:c r="S82" s="8"/>
-      <x:c r="T82" s="31" t="str">
-        <x:v>Purpose unknown.</x:v>
-      </x:c>
+      <x:c r="T82" s="31" t="str"/>
       <x:c r="U82" s="31" t="str">
-        <x:v>Balance 191,475,702 rial.</x:v>
+        <x:v>Balance 191,475,702 rial. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V82" s="31" t="str">
-        <x:v>recipts/photo_8_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_8_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W82" s="13" t="n">
         <x:f>IF(AND(N82="Supported",E82="Receipt",ISNUMBER(H82)),H82,0)</x:f>
@@ -59040,14 +62130,14 @@
       </x:c>
       <x:c r="X82" s="13" t="n">
         <x:f>IF(AND(N82="Supported",E82="Payment",ISNUMBER(H82)),H82,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1300000</x:v>
       </x:c>
       <x:c r="Y82" s="13" t="n">
         <x:f>W82-X82</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="15" hidden="0" customHeight="1">
+        <x:v>-1300000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="36" hidden="0" customHeight="1">
       <x:c r="A83" s="8" t="str">
         <x:v>TX0079</x:v>
       </x:c>
@@ -59085,13 +62175,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M83" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N83" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O83" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P83" s="8" t="str">
         <x:v>SHAHR-2167</x:v>
@@ -59101,14 +62191,13 @@
         <x:v>972094</x:v>
       </x:c>
       <x:c r="S83" s="8"/>
-      <x:c r="T83" s="31" t="str">
-        <x:v>Purpose unknown.</x:v>
-      </x:c>
+      <x:c r="T83" s="31" t="str"/>
       <x:c r="U83" s="31" t="str">
-        <x:v>Balance 179,875,702 rial.</x:v>
+        <x:v>Balance 179,875,702 rial. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V83" s="31" t="str">
-        <x:v>recipts/photo_7_2026-10-10_14-07-27.jpg</x:v>
+        <x:v>recipts/photo_7_2026-10-10_14-07-27.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W83" s="13" t="n">
         <x:f>IF(AND(N83="Supported",E83="Receipt",ISNUMBER(H83)),H83,0)</x:f>
@@ -59116,14 +62205,14 @@
       </x:c>
       <x:c r="X83" s="13" t="n">
         <x:f>IF(AND(N83="Supported",E83="Payment",ISNUMBER(H83)),H83,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1160000</x:v>
       </x:c>
       <x:c r="Y83" s="13" t="n">
         <x:f>W83-X83</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="15" hidden="0" customHeight="1">
+        <x:v>-1160000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="24" hidden="0" customHeight="1">
       <x:c r="A84" s="8" t="str">
         <x:v>TX0080</x:v>
       </x:c>
@@ -59161,13 +62250,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M84" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N84" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O84" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P84" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59177,12 +62266,13 @@
         <x:v>14054456800606</x:v>
       </x:c>
       <x:c r="S84" s="8"/>
-      <x:c r="T84" s="31" t="str">
-        <x:v>Custodian Blu account; association versus personal funds not established.</x:v>
-      </x:c>
-      <x:c r="U84" s="31" t="str"/>
+      <x:c r="T84" s="31" t="str"/>
+      <x:c r="U84" s="31" t="str">
+        <x:v> User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
+      </x:c>
       <x:c r="V84" s="31" t="str">
-        <x:v>recipts/photo_5_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_5_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W84" s="13" t="n">
         <x:f>IF(AND(N84="Supported",E84="Receipt",ISNUMBER(H84)),H84,0)</x:f>
@@ -59190,14 +62280,14 @@
       </x:c>
       <x:c r="X84" s="13" t="n">
         <x:f>IF(AND(N84="Supported",E84="Payment",ISNUMBER(H84)),H84,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>450000</x:v>
       </x:c>
       <x:c r="Y84" s="13" t="n">
         <x:f>W84-X84</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="15" hidden="0" customHeight="1">
+        <x:v>-450000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="48" hidden="0" customHeight="1">
       <x:c r="A85" s="8" t="str">
         <x:v>TX0081</x:v>
       </x:c>
@@ -59235,13 +62325,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M85" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N85" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O85" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P85" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59251,12 +62341,13 @@
         <x:v>233888</x:v>
       </x:c>
       <x:c r="S85" s="8"/>
-      <x:c r="T85" s="31" t="str">
-        <x:v>Source card …5780 differs from the other Blu card; custody unknown.</x:v>
-      </x:c>
-      <x:c r="U85" s="31" t="str"/>
+      <x:c r="T85" s="31" t="str"/>
+      <x:c r="U85" s="31" t="str">
+        <x:v> User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Source identification: masked source card ending 5780. Association attribution is user-attested; no balance reconciliation is implied. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
+      </x:c>
       <x:c r="V85" s="31" t="str">
-        <x:v>recipts/photo_4_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_4_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W85" s="13" t="n">
         <x:f>IF(AND(N85="Supported",E85="Receipt",ISNUMBER(H85)),H85,0)</x:f>
@@ -59264,11 +62355,11 @@
       </x:c>
       <x:c r="X85" s="13" t="n">
         <x:f>IF(AND(N85="Supported",E85="Payment",ISNUMBER(H85)),H85,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>4500000</x:v>
       </x:c>
       <x:c r="Y85" s="13" t="n">
         <x:f>W85-X85</x:f>
-        <x:v>0</x:v>
+        <x:v>-4500000</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -59345,7 +62436,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="24" hidden="0" customHeight="1">
+    <x:row r="87" ht="48" hidden="0" customHeight="1">
       <x:c r="A87" s="8" t="str">
         <x:v>TX0083</x:v>
       </x:c>
@@ -59374,22 +62465,22 @@
         <x:v>زهرا صالح کوشالی</x:v>
       </x:c>
       <x:c r="J87" s="31" t="str">
-        <x:v>Pol transfer, provisional receipt</x:v>
+        <x:v>Summer School 1405 instructor fee: Course not specified</x:v>
       </x:c>
       <x:c r="K87" s="31" t="str">
-        <x:v>انتقال پل (رسید غیرنهایی)</x:v>
+        <x:v>حق تدریس مدرسه تابستانه ۱۴۰۵ — زهرا صالح کوشالی</x:v>
       </x:c>
       <x:c r="L87" s="8" t="str">
-        <x:v>Unclassified</x:v>
+        <x:v>Teaching</x:v>
       </x:c>
       <x:c r="M87" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Summer School 1405</x:v>
       </x:c>
       <x:c r="N87" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O87" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P87" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59399,14 +62490,13 @@
         <x:v>140506301533582360563628293194</x:v>
       </x:c>
       <x:c r="S87" s="8"/>
-      <x:c r="T87" s="31" t="str">
-        <x:v>Provisional receipt; purpose and custody unknown.</x:v>
-      </x:c>
+      <x:c r="T87" s="31" t="str"/>
       <x:c r="U87" s="31" t="str">
-        <x:v>1405/06/30 = 2026-09-21, which is a Monday and matches the printed weekday 'دوشنبه'. There is no weekday conflict. The OCR's 2026-09-22 was a conversion error.</x:v>
+        <x:v>1405/06/30 = 2026-09-21, which is a Monday and matches the printed weekday 'دوشنبه'. There is no weekday conflict. The OCR's 2026-09-22 was a conversion error. User confirms all recipts/ documents represent association expenses. Purpose specifically classified from user confirmation. Original image is a provisional transfer screen; completion is accepted from user confirmation, not independently proven by the image.</x:v>
       </x:c>
       <x:c r="V87" s="31" t="str">
-        <x:v>recipts/photo_1_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_1_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W87" s="13" t="n">
         <x:f>IF(AND(N87="Supported",E87="Receipt",ISNUMBER(H87)),H87,0)</x:f>
@@ -59414,14 +62504,14 @@
       </x:c>
       <x:c r="X87" s="13" t="n">
         <x:f>IF(AND(N87="Supported",E87="Payment",ISNUMBER(H87)),H87,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="Y87" s="13" t="n">
         <x:f>W87-X87</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" ht="15" hidden="0" customHeight="1">
+        <x:v>-600000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="48" hidden="0" customHeight="1">
       <x:c r="A88" s="8" t="str">
         <x:v>TX0084</x:v>
       </x:c>
@@ -59450,22 +62540,22 @@
         <x:v>رضا فرهادی</x:v>
       </x:c>
       <x:c r="J88" s="31" t="str">
-        <x:v>Pol transfer, provisional</x:v>
+        <x:v>Summer School 1405 instructor fee: Course not specified</x:v>
       </x:c>
       <x:c r="K88" s="31" t="str">
-        <x:v>انتقال پل (غیرنهایی)</x:v>
+        <x:v>حق تدریس مدرسه تابستانه ۱۴۰۵ — رضا فرهادی</x:v>
       </x:c>
       <x:c r="L88" s="8" t="str">
-        <x:v>Unclassified</x:v>
+        <x:v>Teaching</x:v>
       </x:c>
       <x:c r="M88" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Summer School 1405</x:v>
       </x:c>
       <x:c r="N88" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O88" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P88" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59475,14 +62565,13 @@
         <x:v>140506301534578220563979207732</x:v>
       </x:c>
       <x:c r="S88" s="8"/>
-      <x:c r="T88" s="31" t="str">
-        <x:v>Provisional; purpose and custody unknown.</x:v>
-      </x:c>
+      <x:c r="T88" s="31" t="str"/>
       <x:c r="U88" s="31" t="str">
-        <x:v>1405/06/30 = Monday 2026-09-21, consistent with the receipt. Provisional ('این رسید نهایی نیست').</x:v>
+        <x:v>1405/06/30 = Monday 2026-09-21, consistent with the receipt. Provisional ('این رسید نهایی نیست'). User confirms all recipts/ documents represent association expenses. Purpose specifically classified from user confirmation. Original image is a provisional transfer screen; completion is accepted from user confirmation, not independently proven by the image.</x:v>
       </x:c>
       <x:c r="V88" s="31" t="str">
-        <x:v>recipts/photo_2_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_2_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W88" s="13" t="n">
         <x:f>IF(AND(N88="Supported",E88="Receipt",ISNUMBER(H88)),H88,0)</x:f>
@@ -59490,14 +62579,14 @@
       </x:c>
       <x:c r="X88" s="13" t="n">
         <x:f>IF(AND(N88="Supported",E88="Payment",ISNUMBER(H88)),H88,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="Y88" s="13" t="n">
         <x:f>W88-X88</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="15" hidden="0" customHeight="1">
+        <x:v>-1200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="36" hidden="0" customHeight="1">
       <x:c r="A89" s="8" t="str">
         <x:v>TX0085</x:v>
       </x:c>
@@ -59523,25 +62612,25 @@
         <x:v>2400000</x:v>
       </x:c>
       <x:c r="I89" s="8" t="str">
-        <x:v>علیرضا کچویی محقق یعقوبی</x:v>
+        <x:v>ابوالفضل احمدی (paid to علیرضا کچویی محقق یعقوبی)</x:v>
       </x:c>
       <x:c r="J89" s="31" t="str">
-        <x:v>Blu-to-Saman transfer</x:v>
+        <x:v>Summer School 1405 instructor fee: LaTeX and API</x:v>
       </x:c>
       <x:c r="K89" s="31" t="str">
-        <x:v>انتقال بلو به سامان</x:v>
+        <x:v>حق تدریس مدرسه تابستانه ۱۴۰۵ — ابوالفضل احمدی</x:v>
       </x:c>
       <x:c r="L89" s="8" t="str">
-        <x:v>Unclassified</x:v>
+        <x:v>Teaching</x:v>
       </x:c>
       <x:c r="M89" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Summer School 1405</x:v>
       </x:c>
       <x:c r="N89" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O89" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P89" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59551,12 +62640,13 @@
         <x:v>14055256207674</x:v>
       </x:c>
       <x:c r="S89" s="8"/>
-      <x:c r="T89" s="31" t="str">
-        <x:v>Purpose and custody unknown.</x:v>
-      </x:c>
-      <x:c r="U89" s="31" t="str"/>
+      <x:c r="T89" s="31" t="str"/>
+      <x:c r="U89" s="31" t="str">
+        <x:v> User confirms all recipts/ documents represent association expenses. Purpose specifically classified from user confirmation. Instructor beneficiary: Abolfazl Ahmadi; bank account payee: Alireza Kachooei Mohaghegh Yaghoubi. Explicit user-confirmed relationship.</x:v>
+      </x:c>
       <x:c r="V89" s="31" t="str">
-        <x:v>recipts/photo_3_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_3_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W89" s="13" t="n">
         <x:f>IF(AND(N89="Supported",E89="Receipt",ISNUMBER(H89)),H89,0)</x:f>
@@ -59564,14 +62654,14 @@
       </x:c>
       <x:c r="X89" s="13" t="n">
         <x:f>IF(AND(N89="Supported",E89="Payment",ISNUMBER(H89)),H89,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>2400000</x:v>
       </x:c>
       <x:c r="Y89" s="13" t="n">
         <x:f>W89-X89</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="15" hidden="0" customHeight="1">
+        <x:v>-2400000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="24" hidden="0" customHeight="1">
       <x:c r="A90" s="8" t="str">
         <x:v>TX0086</x:v>
       </x:c>
@@ -59600,22 +62690,22 @@
         <x:v>بهاره خویش‌خواه</x:v>
       </x:c>
       <x:c r="J90" s="31" t="str">
-        <x:v>Paya transfer</x:v>
+        <x:v>Summer School 1405 instructor fee: Physical simulation with Python</x:v>
       </x:c>
       <x:c r="K90" s="31" t="str">
-        <x:v>انتقال پایا</x:v>
+        <x:v>حق تدریس مدرسه تابستانه ۱۴۰۵ — بهاره خویش خواه</x:v>
       </x:c>
       <x:c r="L90" s="8" t="str">
-        <x:v>Unclassified</x:v>
+        <x:v>Teaching</x:v>
       </x:c>
       <x:c r="M90" s="8" t="str">
-        <x:v>Unknown (possibly Intro Event 1405)</x:v>
+        <x:v>Summer School 1405</x:v>
       </x:c>
       <x:c r="N90" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O90" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P90" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59625,12 +62715,13 @@
         <x:v>140507010562889372</x:v>
       </x:c>
       <x:c r="S90" s="8"/>
-      <x:c r="T90" s="31" t="str">
-        <x:v>Purpose and custody unknown.</x:v>
-      </x:c>
-      <x:c r="U90" s="31" t="str"/>
+      <x:c r="T90" s="31" t="str"/>
+      <x:c r="U90" s="31" t="str">
+        <x:v> User confirms all recipts/ documents represent association expenses. Purpose specifically classified from user confirmation.</x:v>
+      </x:c>
       <x:c r="V90" s="31" t="str">
-        <x:v>recipts/photo_7_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_7_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W90" s="13" t="n">
         <x:f>IF(AND(N90="Supported",E90="Receipt",ISNUMBER(H90)),H90,0)</x:f>
@@ -59638,14 +62729,14 @@
       </x:c>
       <x:c r="X90" s="13" t="n">
         <x:f>IF(AND(N90="Supported",E90="Payment",ISNUMBER(H90)),H90,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="Y90" s="13" t="n">
         <x:f>W90-X90</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="15" hidden="0" customHeight="1">
+        <x:v>-4700000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="24" hidden="0" customHeight="1">
       <x:c r="A91" s="8" t="str">
         <x:v>TX0087</x:v>
       </x:c>
@@ -59674,22 +62765,22 @@
         <x:v>ایلیا اصغریان دهکردی</x:v>
       </x:c>
       <x:c r="J91" s="31" t="str">
-        <x:v>Blu-to-Blu transfer</x:v>
+        <x:v>Summer School 1405 instructor fee: Course not specified</x:v>
       </x:c>
       <x:c r="K91" s="31" t="str">
-        <x:v>انتقال بلو به بلو</x:v>
+        <x:v>حق تدریس مدرسه تابستانه ۱۴۰۵ — ایلیا اصغریان دهکردی</x:v>
       </x:c>
       <x:c r="L91" s="8" t="str">
-        <x:v>Unclassified</x:v>
+        <x:v>Teaching</x:v>
       </x:c>
       <x:c r="M91" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Summer School 1405</x:v>
       </x:c>
       <x:c r="N91" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O91" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P91" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59699,12 +62790,13 @@
         <x:v>14055311988732</x:v>
       </x:c>
       <x:c r="S91" s="8"/>
-      <x:c r="T91" s="31" t="str">
-        <x:v>Purpose and custody unknown. The payee name appears in the 1404 course lists.</x:v>
-      </x:c>
-      <x:c r="U91" s="31" t="str"/>
+      <x:c r="T91" s="31" t="str"/>
+      <x:c r="U91" s="31" t="str">
+        <x:v> User confirms all recipts/ documents represent association expenses. Purpose specifically classified from user confirmation.</x:v>
+      </x:c>
       <x:c r="V91" s="31" t="str">
-        <x:v>recipts/photo_8_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_8_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W91" s="13" t="n">
         <x:f>IF(AND(N91="Supported",E91="Receipt",ISNUMBER(H91)),H91,0)</x:f>
@@ -59712,14 +62804,14 @@
       </x:c>
       <x:c r="X91" s="13" t="n">
         <x:f>IF(AND(N91="Supported",E91="Payment",ISNUMBER(H91)),H91,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>2600000</x:v>
       </x:c>
       <x:c r="Y91" s="13" t="n">
         <x:f>W91-X91</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" ht="15" hidden="0" customHeight="1">
+        <x:v>-2600000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="36" hidden="0" customHeight="1">
       <x:c r="A92" s="8" t="str">
         <x:v>TX0088</x:v>
       </x:c>
@@ -59748,22 +62840,22 @@
         <x:v>زهرا امیری</x:v>
       </x:c>
       <x:c r="J92" s="31" t="str">
-        <x:v>Pol transfer; possibly design (prior poster payee), provisional</x:v>
+        <x:v>Sticker packs for introduction event</x:v>
       </x:c>
       <x:c r="K92" s="31" t="str">
-        <x:v>انتقال پل؛ احتمالاً طراحی (استنباطی)</x:v>
+        <x:v>خرید بسته‌های استیکر برای رویداد معرفی</x:v>
       </x:c>
       <x:c r="L92" s="8" t="str">
-        <x:v>Unclassified</x:v>
+        <x:v>Supplies</x:v>
       </x:c>
       <x:c r="M92" s="8" t="str">
-        <x:v>Unknown (possibly Intro Event 1405)</x:v>
+        <x:v>Intro Event 1405</x:v>
       </x:c>
       <x:c r="N92" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O92" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P92" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59773,12 +62865,13 @@
         <x:v>140507010417015540563175074696</x:v>
       </x:c>
       <x:c r="S92" s="8"/>
-      <x:c r="T92" s="31" t="str">
-        <x:v>Provisional; purpose inferred only.</x:v>
-      </x:c>
-      <x:c r="U92" s="31" t="str"/>
+      <x:c r="T92" s="31" t="str"/>
+      <x:c r="U92" s="31" t="str">
+        <x:v> User confirms all recipts/ documents represent association expenses. Purpose specifically classified from user confirmation. Original image is a provisional transfer screen; completion is accepted from user confirmation, not independently proven by the image. User confirms sticker packs; not teaching fees or design fee.</x:v>
+      </x:c>
       <x:c r="V92" s="31" t="str">
-        <x:v>recipts/photo_6_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_6_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W92" s="13" t="n">
         <x:f>IF(AND(N92="Supported",E92="Receipt",ISNUMBER(H92)),H92,0)</x:f>
@@ -59786,14 +62879,14 @@
       </x:c>
       <x:c r="X92" s="13" t="n">
         <x:f>IF(AND(N92="Supported",E92="Payment",ISNUMBER(H92)),H92,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>950000</x:v>
       </x:c>
       <x:c r="Y92" s="13" t="n">
         <x:f>W92-X92</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="15" hidden="0" customHeight="1">
+        <x:v>-950000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="48" hidden="0" customHeight="1">
       <x:c r="A93" s="8" t="str">
         <x:v>TX0089</x:v>
       </x:c>
@@ -59822,7 +62915,7 @@
         <x:v>یاران دریان لوکس گیشا</x:v>
       </x:c>
       <x:c r="J93" s="31" t="str">
-        <x:v>Invoice: 190 milk drinks and cakes, buyer Hassan Shiri</x:v>
+        <x:v>Food and beverage purchase, settlement confirmed by user</x:v>
       </x:c>
       <x:c r="K93" s="31" t="str">
         <x:v>فاکتور ۱۹۰ قلم شیرکاکائو و کیک به نام حسن شیری</x:v>
@@ -59831,13 +62924,13 @@
         <x:v>Hospitality</x:v>
       </x:c>
       <x:c r="M93" s="8" t="str">
-        <x:v>Unknown (possibly Intro Event 1405, 1405/07/02)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N93" s="8" t="str">
-        <x:v>Invoice only</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O93" s="8" t="str">
-        <x:v>Invoice</x:v>
+        <x:v>Invoice and user payment confirmation</x:v>
       </x:c>
       <x:c r="P93" s="8" t="str">
         <x:v>UNKNOWN</x:v>
@@ -59845,12 +62938,13 @@
       <x:c r="Q93" s="8" t="str"/>
       <x:c r="R93" s="8"/>
       <x:c r="S93" s="8"/>
-      <x:c r="T93" s="31" t="str">
-        <x:v>Customer balance equals the total, so unpaid at issue. Line sum is 100,100,000 vs total 99,879,000.</x:v>
-      </x:c>
-      <x:c r="U93" s="31" t="str"/>
+      <x:c r="T93" s="31" t="str"/>
+      <x:c r="U93" s="31" t="str">
+        <x:v>Payment attested by user; payment method/account not independently evidenced. Invoice line amounts total 100,100,000 rial versus printed total 99,879,000 (221,000 rial unexplained). Recorded at printed 9,987,900 toman. Original customer balance is retained; user confirms settlement. Prior project label: Unknown (possibly Intro Event 1405, 1405/07/02). Project not specifically confirmed; retained as Unassigned.</x:v>
+      </x:c>
       <x:c r="V93" s="31" t="str">
-        <x:v>recipts/photo_2026-10-10_12-16-28.jpg</x:v>
+        <x:v>recipts/photo_2026-10-10_12-16-28.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W93" s="13" t="n">
         <x:f>IF(AND(N93="Supported",E93="Receipt",ISNUMBER(H93)),H93,0)</x:f>
@@ -59858,14 +62952,14 @@
       </x:c>
       <x:c r="X93" s="13" t="n">
         <x:f>IF(AND(N93="Supported",E93="Payment",ISNUMBER(H93)),H93,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>9987900</x:v>
       </x:c>
       <x:c r="Y93" s="13" t="n">
         <x:f>W93-X93</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" ht="15" hidden="0" customHeight="1">
+        <x:v>-9987900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="48" hidden="0" customHeight="1">
       <x:c r="A94" s="8" t="str">
         <x:v>TX0090</x:v>
       </x:c>
@@ -59903,13 +62997,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M94" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N94" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O94" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P94" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59919,14 +63013,13 @@
         <x:v>487065</x:v>
       </x:c>
       <x:c r="S94" s="8"/>
-      <x:c r="T94" s="31" t="str">
-        <x:v>Largest unexplained outflow. Purpose and custody unknown.</x:v>
-      </x:c>
+      <x:c r="T94" s="31" t="str"/>
       <x:c r="U94" s="31" t="str">
-        <x:v>Reference 487026636208.</x:v>
+        <x:v>Reference 487026636208. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Source identification: masked source card ending 6947. Association attribution is user-attested; no balance reconciliation is implied. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V94" s="31" t="str">
-        <x:v>recipts/photo_10_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_10_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W94" s="13" t="n">
         <x:f>IF(AND(N94="Supported",E94="Receipt",ISNUMBER(H94)),H94,0)</x:f>
@@ -59934,14 +63027,14 @@
       </x:c>
       <x:c r="X94" s="13" t="n">
         <x:f>IF(AND(N94="Supported",E94="Payment",ISNUMBER(H94)),H94,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>13900000</x:v>
       </x:c>
       <x:c r="Y94" s="13" t="n">
         <x:f>W94-X94</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="15" hidden="0" customHeight="1">
+        <x:v>-13900000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="48" hidden="0" customHeight="1">
       <x:c r="A95" s="8" t="str">
         <x:v>TX0091</x:v>
       </x:c>
@@ -59979,13 +63072,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M95" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N95" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O95" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P95" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -59993,14 +63086,13 @@
       <x:c r="Q95" s="8" t="str"/>
       <x:c r="R95" s="8"/>
       <x:c r="S95" s="8"/>
-      <x:c r="T95" s="31" t="str">
-        <x:v>Account holder and goods unknown.</x:v>
-      </x:c>
+      <x:c r="T95" s="31" t="str"/>
       <x:c r="U95" s="31" t="str">
-        <x:v>Balance after: 16,921,310 rial.</x:v>
+        <x:v>Balance after: 16,921,310 rial. User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Source identification: holder not shown. Association attribution is user-attested; no balance reconciliation is implied. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
       </x:c>
       <x:c r="V95" s="31" t="str">
-        <x:v>recipts/photo_11_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_11_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W95" s="13" t="n">
         <x:f>IF(AND(N95="Supported",E95="Receipt",ISNUMBER(H95)),H95,0)</x:f>
@@ -60008,14 +63100,14 @@
       </x:c>
       <x:c r="X95" s="13" t="n">
         <x:f>IF(AND(N95="Supported",E95="Payment",ISNUMBER(H95)),H95,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>2332250</x:v>
       </x:c>
       <x:c r="Y95" s="13" t="n">
         <x:f>W95-X95</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="15" hidden="0" customHeight="1">
+        <x:v>-2332250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="48" hidden="0" customHeight="1">
       <x:c r="A96" s="8" t="str">
         <x:v>TX0092</x:v>
       </x:c>
@@ -60053,13 +63145,13 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="M96" s="8" t="str">
-        <x:v>Unknown (1405)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="N96" s="8" t="str">
-        <x:v>Review</x:v>
+        <x:v>Supported</x:v>
       </x:c>
       <x:c r="O96" s="8" t="str">
-        <x:v>Receipt only</x:v>
+        <x:v>Receipt and user confirmation</x:v>
       </x:c>
       <x:c r="P96" s="8" t="str">
         <x:v>BLU-CUSTODIAN</x:v>
@@ -60069,12 +63161,13 @@
         <x:v>981431</x:v>
       </x:c>
       <x:c r="S96" s="8"/>
-      <x:c r="T96" s="31" t="str">
-        <x:v>Purpose and custody unknown.</x:v>
-      </x:c>
-      <x:c r="U96" s="31" t="str"/>
+      <x:c r="T96" s="31" t="str"/>
+      <x:c r="U96" s="31" t="str">
+        <x:v> User confirms all recipts/ documents represent association expenses. Purpose is retained as unclassified unless specifically identified. Source identification: masked source card ending 6947. Association attribution is user-attested; no balance reconciliation is implied. Prior project label: Unknown (1405). Project not specifically confirmed; retained as Unassigned.</x:v>
+      </x:c>
       <x:c r="V96" s="31" t="str">
-        <x:v>recipts/photo_12_2026-10-10_11-09-04.jpg</x:v>
+        <x:v>recipts/photo_12_2026-10-10_11-09-04.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="W96" s="13" t="n">
         <x:f>IF(AND(N96="Supported",E96="Receipt",ISNUMBER(H96)),H96,0)</x:f>
@@ -60082,11 +63175,11 @@
       </x:c>
       <x:c r="X96" s="13" t="n">
         <x:f>IF(AND(N96="Supported",E96="Payment",ISNUMBER(H96)),H96,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>305000</x:v>
       </x:c>
       <x:c r="Y96" s="13" t="n">
         <x:f>W96-X96</x:f>
-        <x:v>0</x:v>
+        <x:v>-305000</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -60305,6 +63398,9 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:conditionalFormatting sqref="N5:N99">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Review"/>
   </x:conditionalFormatting>
@@ -60318,12 +63414,12 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5c9b8f9333a473f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ab8608d7634931"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFEDF2F7"/>
@@ -60344,45 +63440,45 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="32"/>
-      <x:c r="B1" s="32"/>
-      <x:c r="C1" s="32"/>
-      <x:c r="D1" s="32"/>
-      <x:c r="E1" s="32"/>
-      <x:c r="F1" s="32"/>
-      <x:c r="G1" s="32"/>
-      <x:c r="H1" s="32"/>
-      <x:c r="I1" s="32"/>
-      <x:c r="J1" s="32"/>
-      <x:c r="K1" s="32"/>
-    </x:row>
-    <x:row r="2" ht="84" hidden="0" customHeight="1">
-      <x:c r="A2" s="33" t="str">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+      <x:c r="C1" s="33"/>
+      <x:c r="D1" s="33"/>
+      <x:c r="E1" s="33"/>
+      <x:c r="F1" s="33"/>
+      <x:c r="G1" s="33"/>
+      <x:c r="H1" s="33"/>
+      <x:c r="I1" s="33"/>
+      <x:c r="J1" s="33"/>
+      <x:c r="K1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
         <x:v>Supplier invoice and payment matching register</x:v>
       </x:c>
-      <x:c r="B2" s="32"/>
-      <x:c r="C2" s="32"/>
-      <x:c r="D2" s="32"/>
-      <x:c r="E2" s="32"/>
-      <x:c r="F2" s="32"/>
-      <x:c r="G2" s="32"/>
-      <x:c r="H2" s="32"/>
-      <x:c r="I2" s="32"/>
-      <x:c r="J2" s="32"/>
-      <x:c r="K2" s="32"/>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
+      <x:c r="G2" s="33"/>
+      <x:c r="H2" s="33"/>
+      <x:c r="I2" s="33"/>
+      <x:c r="J2" s="33"/>
+      <x:c r="K2" s="33"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="32"/>
-      <x:c r="B3" s="32"/>
-      <x:c r="C3" s="32"/>
-      <x:c r="D3" s="32"/>
-      <x:c r="E3" s="32"/>
-      <x:c r="F3" s="32"/>
-      <x:c r="G3" s="32"/>
-      <x:c r="H3" s="32"/>
-      <x:c r="I3" s="32"/>
-      <x:c r="J3" s="32"/>
-      <x:c r="K3" s="32"/>
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
+      <x:c r="H3" s="33"/>
+      <x:c r="I3" s="33"/>
+      <x:c r="J3" s="33"/>
+      <x:c r="K3" s="33"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -60433,10 +63529,10 @@
         <x:v>Sony NP-FV50 battery, invoice 15628595</x:v>
       </x:c>
       <x:c r="E5" s="31"/>
-      <x:c r="F5" s="34" t="n">
+      <x:c r="F5" s="35" t="n">
         <x:v>696000</x:v>
       </x:c>
-      <x:c r="G5" s="34" t="n">
+      <x:c r="G5" s="35" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="31" t="str">
@@ -60466,10 +63562,10 @@
         <x:v>Shipping and insurance, invoice 12050044</x:v>
       </x:c>
       <x:c r="E6" s="31"/>
-      <x:c r="F6" s="34" t="n">
+      <x:c r="F6" s="35" t="n">
         <x:v>29000</x:v>
       </x:c>
-      <x:c r="G6" s="34" t="n">
+      <x:c r="G6" s="35" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
@@ -60499,10 +63595,10 @@
         <x:v>4 balloon glue, invoice 29449</x:v>
       </x:c>
       <x:c r="E7" s="31"/>
-      <x:c r="F7" s="34" t="n">
+      <x:c r="F7" s="35" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="G7" s="34"/>
+      <x:c r="G7" s="35"/>
       <x:c r="H7" s="31" t="str">
         <x:v>TX0037</x:v>
       </x:c>
@@ -60531,10 +63627,10 @@
         <x:v>Balloons, pump, thread, foils; invoice 2935/29350</x:v>
       </x:c>
       <x:c r="E8" s="31"/>
-      <x:c r="F8" s="34" t="n">
+      <x:c r="F8" s="35" t="n">
         <x:v>1310000</x:v>
       </x:c>
-      <x:c r="G8" s="34"/>
+      <x:c r="G8" s="35"/>
       <x:c r="H8" s="31" t="str">
         <x:v>TX0038</x:v>
       </x:c>
@@ -60561,8 +63657,8 @@
         <x:v>Freshman prizes: holders, spinners, bow ties</x:v>
       </x:c>
       <x:c r="E9" s="31"/>
-      <x:c r="F9" s="34"/>
-      <x:c r="G9" s="34"/>
+      <x:c r="F9" s="35"/>
+      <x:c r="G9" s="35"/>
       <x:c r="H9" s="31" t="str">
         <x:v>TX0033</x:v>
       </x:c>
@@ -60590,10 +63686,10 @@
         <x:v>USB flash 32G and earphones</x:v>
       </x:c>
       <x:c r="E10" s="31"/>
-      <x:c r="F10" s="34" t="n">
+      <x:c r="F10" s="35" t="n">
         <x:v>1500000</x:v>
       </x:c>
-      <x:c r="G10" s="34"/>
+      <x:c r="G10" s="35"/>
       <x:c r="H10" s="31" t="str">
         <x:v>TX0034</x:v>
       </x:c>
@@ -60621,10 +63717,10 @@
         <x:v>Pineapple pie and pastry order</x:v>
       </x:c>
       <x:c r="E11" s="31"/>
-      <x:c r="F11" s="34" t="n">
+      <x:c r="F11" s="35" t="n">
         <x:v>1052375</x:v>
       </x:c>
-      <x:c r="G11" s="34"/>
+      <x:c r="G11" s="35"/>
       <x:c r="H11" s="31" t="str">
         <x:v>TX0024</x:v>
       </x:c>
@@ -60652,10 +63748,10 @@
         <x:v>French chocolate cream pastry</x:v>
       </x:c>
       <x:c r="E12" s="31"/>
-      <x:c r="F12" s="34" t="n">
+      <x:c r="F12" s="35" t="n">
         <x:v>912850</x:v>
       </x:c>
-      <x:c r="G12" s="34"/>
+      <x:c r="G12" s="35"/>
       <x:c r="H12" s="31" t="str">
         <x:v>TX0023</x:v>
       </x:c>
@@ -60681,10 +63777,10 @@
         <x:v>7 × 2kg pomegranates</x:v>
       </x:c>
       <x:c r="E13" s="31"/>
-      <x:c r="F13" s="34" t="n">
+      <x:c r="F13" s="35" t="n">
         <x:v>1664700</x:v>
       </x:c>
-      <x:c r="G13" s="34"/>
+      <x:c r="G13" s="35"/>
       <x:c r="H13" s="31" t="str"/>
       <x:c r="I13" s="31" t="str">
         <x:v>Unmatched invoice</x:v>
@@ -60710,10 +63806,10 @@
         <x:v>Jelly powder and cherry syrup</x:v>
       </x:c>
       <x:c r="E14" s="31"/>
-      <x:c r="F14" s="34" t="n">
+      <x:c r="F14" s="35" t="n">
         <x:v>2150000</x:v>
       </x:c>
-      <x:c r="G14" s="34" t="n">
+      <x:c r="G14" s="35" t="n">
         <x:v>195454.5</x:v>
       </x:c>
       <x:c r="H14" s="31" t="str">
@@ -60744,10 +63840,10 @@
         <x:v>Snack receipts C1-C8 (eight slips)</x:v>
       </x:c>
       <x:c r="E15" s="31"/>
-      <x:c r="F15" s="34" t="n">
+      <x:c r="F15" s="35" t="n">
         <x:v>1306700</x:v>
       </x:c>
-      <x:c r="G15" s="34"/>
+      <x:c r="G15" s="35"/>
       <x:c r="H15" s="31" t="str">
         <x:v>TX0064, TX0065, TX0066, TX0067, TX0068, TX0069, TX0072, TX0073</x:v>
       </x:c>
@@ -60775,10 +63871,10 @@
         <x:v>99 Mozmoz snacks</x:v>
       </x:c>
       <x:c r="E16" s="31"/>
-      <x:c r="F16" s="34" t="n">
+      <x:c r="F16" s="35" t="n">
         <x:v>1916640</x:v>
       </x:c>
-      <x:c r="G16" s="34" t="n">
+      <x:c r="G16" s="35" t="n">
         <x:v>174240</x:v>
       </x:c>
       <x:c r="H16" s="31" t="str">
@@ -60808,10 +63904,10 @@
         <x:v>Gala chocolate</x:v>
       </x:c>
       <x:c r="E17" s="31"/>
-      <x:c r="F17" s="34" t="n">
+      <x:c r="F17" s="35" t="n">
         <x:v>135800</x:v>
       </x:c>
-      <x:c r="G17" s="34" t="n">
+      <x:c r="G17" s="35" t="n">
         <x:v>12345.4</x:v>
       </x:c>
       <x:c r="H17" s="31" t="str">
@@ -60839,10 +63935,10 @@
         <x:v>Handwritten, likely chocolate cookies</x:v>
       </x:c>
       <x:c r="E18" s="31"/>
-      <x:c r="F18" s="34" t="n">
+      <x:c r="F18" s="35" t="n">
         <x:v>495000</x:v>
       </x:c>
-      <x:c r="G18" s="34"/>
+      <x:c r="G18" s="35"/>
       <x:c r="H18" s="31" t="str"/>
       <x:c r="I18" s="31" t="str">
         <x:v>Unmatched invoice</x:v>
@@ -60868,10 +63964,10 @@
         <x:v>Skyroom licence + recording, invoice 61150</x:v>
       </x:c>
       <x:c r="E19" s="31"/>
-      <x:c r="F19" s="34" t="n">
+      <x:c r="F19" s="35" t="n">
         <x:v>4257000</x:v>
       </x:c>
-      <x:c r="G19" s="34" t="n">
+      <x:c r="G19" s="35" t="n">
         <x:v>387000</x:v>
       </x:c>
       <x:c r="H19" s="31" t="str"/>
@@ -60885,7 +63981,7 @@
         <x:v>Buyer Hassan Shiri.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
+    <x:row r="20" ht="24" hidden="0" customHeight="1">
       <x:c r="A20" s="31" t="str">
         <x:v>INV016</x:v>
       </x:c>
@@ -60899,30 +63995,36 @@
         <x:v>190 dairy drinks and cakes, order 165826</x:v>
       </x:c>
       <x:c r="E20" s="31"/>
-      <x:c r="F20" s="34" t="n">
+      <x:c r="F20" s="35" t="n">
         <x:v>9987900</x:v>
       </x:c>
-      <x:c r="G20" s="34"/>
-      <x:c r="H20" s="31" t="str"/>
+      <x:c r="G20" s="35"/>
+      <x:c r="H20" s="31" t="str">
+        <x:v>TX0089</x:v>
+      </x:c>
       <x:c r="I20" s="31" t="str">
-        <x:v>Unmatched invoice</x:v>
+        <x:v>Matched payment</x:v>
       </x:c>
       <x:c r="J20" s="31" t="str">
-        <x:v>recipts/photo_2026-10-10_12-16-28.jpg</x:v>
+        <x:v>recipts/photo_2026-10-10_12-16-28.jpg
+reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
       </x:c>
       <x:c r="K20" s="31" t="str">
-        <x:v>Unpaid at issue.</x:v>
+        <x:v>Unpaid at issue. User explicitly confirms this folder document is a settled association expense. Matched to TX0089 based on attestation; no separate bank transfer is supplied.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf14341be696145df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44849797a5ce4847"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFEDF2F7"/>
@@ -60940,36 +64042,36 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="32"/>
-      <x:c r="B1" s="32"/>
-      <x:c r="C1" s="32"/>
-      <x:c r="D1" s="32"/>
-      <x:c r="E1" s="32"/>
-      <x:c r="F1" s="32"/>
-      <x:c r="G1" s="32"/>
-      <x:c r="H1" s="32"/>
-    </x:row>
-    <x:row r="2" ht="67.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A2" s="33" t="str">
+      <x:c r="A1" s="33"/>
+      <x:c r="B1" s="33"/>
+      <x:c r="C1" s="33"/>
+      <x:c r="D1" s="33"/>
+      <x:c r="E1" s="33"/>
+      <x:c r="F1" s="33"/>
+      <x:c r="G1" s="33"/>
+      <x:c r="H1" s="33"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="34" t="str">
         <x:v>Reconciliation issues and required follow-up</x:v>
       </x:c>
-      <x:c r="B2" s="32"/>
-      <x:c r="C2" s="32"/>
-      <x:c r="D2" s="32"/>
-      <x:c r="E2" s="32"/>
-      <x:c r="F2" s="32"/>
-      <x:c r="G2" s="32"/>
-      <x:c r="H2" s="32"/>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
+      <x:c r="G2" s="33"/>
+      <x:c r="H2" s="33"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="32"/>
-      <x:c r="B3" s="32"/>
-      <x:c r="C3" s="32"/>
-      <x:c r="D3" s="32"/>
-      <x:c r="E3" s="32"/>
-      <x:c r="F3" s="32"/>
-      <x:c r="G3" s="32"/>
-      <x:c r="H3" s="32"/>
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
+      <x:c r="H3" s="33"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -61010,7 +64112,7 @@
       <x:c r="D5" s="31" t="str">
         <x:v>Only fragments are available: receipts, SMS and screenshots. There is no opening balance, and balance snapshots conflict (230,203,965 rial on 1404/05/02; 22,953,913 rial on 1404/07/20; '560,800,163' on 1404/07/22; 22,765,000 in message52; 29,200 in message86). The 560,800,163 and 565,800,163 rial snapshots are mutually consistent with a 5,000,000 rial deposit; their relation to the earlier 22,953,913 snapshot remains unexplained. On 1404/05/03 the balance drop of 9,614,400 rial is 7,394,600 smaller than recorded intervening debits of 17,009,000 rial, requiring inflows or other explanation.</x:v>
       </x:c>
-      <x:c r="E5" s="34"/>
+      <x:c r="E5" s="35"/>
       <x:c r="F5" s="31" t="str"/>
       <x:c r="G5" s="31" t="str">
         <x:v>Obtain full Shahr 400816808774, Sepah 3001254062925 and Blu statements.</x:v>
@@ -61024,22 +64126,22 @@
         <x:v>ISS002</x:v>
       </x:c>
       <x:c r="B6" s="31" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>Commingled custodian Blu account outflows in 1405</x:v>
+        <x:v>Allocation details for user-confirmed association payments</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>Eleven Blu transfers and purchases by Hassan Shiri totalling 33,937,250 toman have no stated purpose. The source accounts are not established as association accounts.</x:v>
-      </x:c>
-      <x:c r="E6" s="34" t="n">
+        <x:v>User confirms all eleven Blu outflows totaling 33,937,250 are association expenses. Five identified Summer School 1405 fees total 11,500,000; sticker packs cost 950,000. Remaining 21,487,250 requires purpose/project allocation, not income/expense-direction confirmation.</x:v>
+      </x:c>
+      <x:c r="E6" s="35" t="n">
         <x:v>33937250</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
         <x:v>TX0080, TX0081, TX0083, TX0084, TX0085, TX0086, TX0087, TX0088, TX0090, TX0091, TX0092</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Custodian to annotate each payment and declare which funds are association funds.</x:v>
+        <x:v>Identify remaining project/category allocations and the sixth Summer School instructor payment. Preserve user attestation separately from bank evidence.</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
         <x:v>recipts/photo_10_2026-10-10_11-09-04.jpg</x:v>
@@ -61053,19 +64155,19 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="C7" s="31" t="str">
-        <x:v>Unexplained 1405 debits on association Shahr deposit</x:v>
+        <x:v>User-confirmed Shahr expenses and bank-balance gaps</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>Five card purchases on card …2167 (1405/05/21-22), plus 1404/09/02 and 1404/12/09 debits. There is also an undocumented 31,630,000 rial drop between the 1405/05/21 and 1405/05/22 balances.</x:v>
-      </x:c>
-      <x:c r="E7" s="34" t="n">
+        <x:v>User confirms seven Shahr-folder outflows totaling 14,038,220 are association expenses, including TX0061 previously unclassified in direction. Merchant/project allocation remains pending. The unlogged balance movement remains unexplained.</x:v>
+      </x:c>
+      <x:c r="E7" s="35" t="n">
         <x:v>14038220</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
         <x:v>TX0075, TX0076, TX0077, TX0078, TX0079, TX0043, TX0061</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Identify merchants and purpose. Confirm whether card …2167 belongs to the association.</x:v>
+        <x:v>Assign purposes/projects to merchant payments and obtain complete statements to explain the 31,630,000 rial balance gap.</x:v>
       </x:c>
       <x:c r="H7" s="31" t="str">
         <x:v>recipts/photo_3_2026-10-10_14-07-27.jpg</x:v>
@@ -61082,9 +64184,9 @@
         <x:v>Intro Event 1405 bridge: 27,235,000 gross vs 23,000,000 ledger</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>The platform report shows gross sales of 27,235,000. The ledger records 23,000,000 with a 5,000,000 gathering. No settlement deposit exists, and invoices for Skyroom (4,257,000) and catering (9,987,900) are unpaid or unmatched.</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="n">
+        <x:v>Platform gross sales 27,235,000 vs original-ledger receipts 23,000,000 remain unreconciled. Skyroom invoice 4,257,000 remains unmatched. Food invoice 9,987,900 is now user-confirmed paid (TX0089); sticker purchase 950,000 belongs to this event (TX0088). No new registration receipts are inferred.</x:v>
+      </x:c>
+      <x:c r="E8" s="35" t="n">
         <x:v>4235000</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
@@ -61111,7 +64213,7 @@
       <x:c r="D9" s="31" t="str">
         <x:v>17,650,000 without a unit. As rial (1,765,000 toman) it equals ledger M3 net. Treated as an internal transfer.</x:v>
       </x:c>
-      <x:c r="E9" s="34"/>
+      <x:c r="E9" s="35"/>
       <x:c r="F9" s="31" t="str">
         <x:v>TX0018, TX0014</x:v>
       </x:c>
@@ -61135,7 +64237,7 @@
       <x:c r="D10" s="31" t="str">
         <x:v>مجموع D23 duplicates the D20 pastry (1,052,375). D12 likely duplicates the D9 ad (400,000).</x:v>
       </x:c>
-      <x:c r="E10" s="34" t="n">
+      <x:c r="E10" s="35" t="n">
         <x:v>1452375</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
@@ -61149,7 +64251,7 @@
 Anjoman accounting.xlsx#مجموع!D12</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
       <x:c r="A11" s="31" t="str">
         <x:v>ISS007</x:v>
       </x:c>
@@ -61160,9 +64262,9 @@
         <x:v>Cash shabash direction unresolved</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>message111 reads '300000 cash shabash for the party'. The ledger treats it as an expense (D29), but it could be cash received.</x:v>
-      </x:c>
-      <x:c r="E11" s="34" t="n">
+        <x:v>message111 reads '300000 cash shabash for the party'. The ledger treats it as an expense (D29), but it could be cash received. This Telegram/workbook item is outside recipts/ and is not resolved by the folder-wide expense confirmation.</x:v>
+      </x:c>
+      <x:c r="E11" s="35" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
@@ -61188,7 +64290,7 @@
       <x:c r="D12" s="31" t="str">
         <x:v>Parnian reimbursement 4,050,000 is absent from the original ledger. Printed purchases total 3,359,139.9, or 3,180,139.9 excluding possible C6 duplicate. Including invoice-only Ribar 495,000 gives 3,854,139.9 or 3,675,139.9. These are provisional documentation gaps, not confirmed overpayment. Hossein reimbursement is undocumented. Bardia claims vs payment need a separate bridge.</x:v>
       </x:c>
-      <x:c r="E12" s="34" t="n">
+      <x:c r="E12" s="35" t="n">
         <x:v>4050000</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
@@ -61214,7 +64316,7 @@
       <x:c r="D13" s="31" t="str">
         <x:v>The SMS withdrawal is 100,037,800 in an unprinted unit (10,003,780 toman if rial). Message120 describes expense payments or transfers, not income. It remains unconverted and may overlap recorded expenses. Deposit lines are explicitly rial: 150,000, 500,000 and 1,000,000 toman; they do not sum to the treasurer total 15,790,000. Balances imply unlogged movements.</x:v>
       </x:c>
-      <x:c r="E13" s="34"/>
+      <x:c r="E13" s="35"/>
       <x:c r="F13" s="31" t="str">
         <x:v>TX0049, TX0047</x:v>
       </x:c>
@@ -61238,7 +64340,7 @@
       <x:c r="D14" s="31" t="str">
         <x:v>The receipt shows 235,000; the ledger and message show 230,000.</x:v>
       </x:c>
-      <x:c r="E14" s="34" t="n">
+      <x:c r="E14" s="35" t="n">
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F14" s="31" t="str">
@@ -61264,7 +64366,7 @@
       <x:c r="D15" s="31" t="str">
         <x:v>Transfer fee 900, Dina Zali 180,000, Parnian 4,050,000. The poster print of 13,000 is unmatched.</x:v>
       </x:c>
-      <x:c r="E15" s="34" t="n">
+      <x:c r="E15" s="35" t="n">
         <x:v>4230900</x:v>
       </x:c>
       <x:c r="F15" s="31" t="str">
@@ -61288,7 +64390,7 @@
       <x:c r="D16" s="31" t="str">
         <x:v>Refined تطبیق!B7 is circular (=B6-B7; should be B5-B6). TX-00002 counterparty is wrong. TX-00044 is marked confirmed with no payment. The مرداد sheet omits D10-D12. Sohrab's fee does not follow the 100k rounding rule (2,934→3,000).</x:v>
       </x:c>
-      <x:c r="E16" s="34"/>
+      <x:c r="E16" s="35"/>
       <x:c r="F16" s="31" t="str">
         <x:v>TX0001, TX0002, TX0082</x:v>
       </x:c>
@@ -61312,7 +64414,7 @@
       <x:c r="D17" s="31" t="str">
         <x:v>Moghimi's 10m receipt has no date. The forward header is 1404/08/28 but the ledger month is آذر.</x:v>
       </x:c>
-      <x:c r="E17" s="34" t="n">
+      <x:c r="E17" s="35" t="n">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="F17" s="31" t="str">
@@ -61338,7 +64440,7 @@
       <x:c r="D18" s="31" t="str">
         <x:v>Course reports label 11,601, 12,261 and 9,781 as toman. The printed-unit total is 33,643 toman. A possible thousand-toman scale would total 33,643,000, versus the ledger 33,642,000; that scale is unconfirmed and is used only as a comparison, not additional revenue. Reports contain student phone numbers.</x:v>
       </x:c>
-      <x:c r="E18" s="34" t="n">
+      <x:c r="E18" s="35" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F18" s="31" t="str">
@@ -61351,2680 +64453,37 @@
         <x:v>telegram export/files/report_Python.txt</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" ht="24" hidden="0" customHeight="1">
+      <x:c r="A19" s="31" t="str">
+        <x:v>ISS015</x:v>
+      </x:c>
+      <x:c r="B19" s="31" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="str">
+        <x:v>Sixth Summer School 1405 instructor payment not identified</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="str">
+        <x:v>User states six folder receipts are instructor payments. Five are matched by recipient-name evidence and explicit clarification: TX0083-87, total 11,500,000. TX0088 is explicitly sticker packs, not an instructor fee. The sixth remains unmatched among already recorded folder expenses.</x:v>
+      </x:c>
+      <x:c r="E19" s="35"/>
+      <x:c r="F19" s="31" t="str">
+        <x:v>TX0083, TX0084, TX0085, TX0086, TX0087</x:v>
+      </x:c>
+      <x:c r="G19" s="31" t="str">
+        <x:v>Provide the sixth instructor/payee name or receipt filename. Do not create an additional payment or infer registration income.</x:v>
+      </x:c>
+      <x:c r="H19" s="31" t="str">
+        <x:v>reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R198b9dda13844d0e"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FFEDF2F7"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="85" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="25" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="110" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="120" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="32"/>
-      <x:c r="B1" s="32"/>
-      <x:c r="C1" s="32"/>
-      <x:c r="D1" s="32"/>
-      <x:c r="E1" s="32"/>
-      <x:c r="F1" s="32"/>
-      <x:c r="G1" s="32"/>
-      <x:c r="H1" s="32"/>
-      <x:c r="I1" s="32"/>
-      <x:c r="J1" s="32"/>
-      <x:c r="K1" s="32"/>
-    </x:row>
-    <x:row r="2" ht="67.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A2" s="33" t="str">
-        <x:v>Source inventory and extraction coverage</x:v>
-      </x:c>
-      <x:c r="B2" s="32"/>
-      <x:c r="C2" s="32"/>
-      <x:c r="D2" s="32"/>
-      <x:c r="E2" s="32"/>
-      <x:c r="F2" s="32"/>
-      <x:c r="G2" s="32"/>
-      <x:c r="H2" s="32"/>
-      <x:c r="I2" s="32"/>
-      <x:c r="J2" s="32"/>
-      <x:c r="K2" s="32"/>
-    </x:row>
-    <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="32"/>
-      <x:c r="B3" s="32"/>
-      <x:c r="C3" s="32"/>
-      <x:c r="D3" s="32"/>
-      <x:c r="E3" s="32"/>
-      <x:c r="F3" s="32"/>
-      <x:c r="G3" s="32"/>
-      <x:c r="H3" s="32"/>
-      <x:c r="I3" s="32"/>
-      <x:c r="J3" s="32"/>
-      <x:c r="K3" s="32"/>
-    </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="7" t="str">
-        <x:v>Source ID</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>Repository file</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>File type</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="str">
-        <x:v>Bytes</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="str">
-        <x:v>SHA-256</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="str">
-        <x:v>Read status</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="str">
-        <x:v>Ledger IDs</x:v>
-      </x:c>
-      <x:c r="H4" s="7" t="str">
-        <x:v>Message IDs</x:v>
-      </x:c>
-      <x:c r="I4" s="7" t="str">
-        <x:v>Treatment</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="K4" s="7" t="str">
-        <x:v>GitHub source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="31" t="str">
-        <x:v>SRC001</x:v>
-      </x:c>
-      <x:c r="B5" s="31" t="str">
-        <x:v>Anjoman accounting - refined.xlsx</x:v>
-      </x:c>
-      <x:c r="C5" s="31" t="str">
-        <x:v>xlsx</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
-        <x:v>63212</x:v>
-      </x:c>
-      <x:c r="E5" s="31" t="str">
-        <x:v>d77c540aba056a0bce5abaef9ac974fbf1f91ead2f0ea55d7ac1bc96b94a2228</x:v>
-      </x:c>
-      <x:c r="F5" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G5" s="31" t="str"/>
-      <x:c r="H5" s="31" t="str"/>
-      <x:c r="I5" s="31" t="str">
-        <x:v>Context only</x:v>
-      </x:c>
-      <x:c r="J5" s="31" t="str">
-        <x:v>Derived copy of مجموع plus TX-00044..48 proposals. Errors flagged in ISS012.</x:v>
-      </x:c>
-      <x:c r="K5" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/Anjoman%20accounting%20-%20refined.xlsx</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
-      <x:c r="A6" s="31" t="str">
-        <x:v>SRC002</x:v>
-      </x:c>
-      <x:c r="B6" s="31" t="str">
-        <x:v>Anjoman accounting.xlsx</x:v>
-      </x:c>
-      <x:c r="C6" s="31" t="str">
-        <x:v>xlsx</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
-        <x:v>130028</x:v>
-      </x:c>
-      <x:c r="E6" s="31" t="str">
-        <x:v>5701b246ebee5bd5db7fc022de097f47c34354e420bb59f08f4f2fc74a0bfcf0</x:v>
-      </x:c>
-      <x:c r="F6" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G6" s="31" t="str">
-        <x:v>TX0001, TX0013, TX0014, TX0016, TX0017, TX0045, TX0093, TX0095</x:v>
-      </x:c>
-      <x:c r="H6" s="31" t="str"/>
-      <x:c r="I6" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J6" s="31" t="str">
-        <x:v>Every مجموع row is mapped in original_ledger_reconciliation. The مرداد and شهریور sheets are subsets.</x:v>
-      </x:c>
-      <x:c r="K6" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/Anjoman%20accounting.xlsx</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="31" t="str">
-        <x:v>SRC003</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>invoice-61150.pdf</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>pdf</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
-        <x:v>153863</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>06626a709e2a23bc59d3a5185c64e0a85b64e59ccf244cbb3b0867344bc07b57</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>TX0082</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str"/>
-      <x:c r="I7" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J7" s="31" t="str">
-        <x:v>Invoice only.</x:v>
-      </x:c>
-      <x:c r="K7" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/invoice-61150.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="31" t="str">
-        <x:v>SRC004</x:v>
-      </x:c>
-      <x:c r="B8" s="31" t="str">
-        <x:v>physics_intro full report.pdf</x:v>
-      </x:c>
-      <x:c r="C8" s="31" t="str">
-        <x:v>pdf</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
-        <x:v>52198</x:v>
-      </x:c>
-      <x:c r="E8" s="31" t="str">
-        <x:v>993061f6f022016308bbd6585c6ae0e8a2b67575c39f21e740659cc25da7dc70</x:v>
-      </x:c>
-      <x:c r="F8" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G8" s="31" t="str">
-        <x:v>TX0094</x:v>
-      </x:c>
-      <x:c r="H8" s="31" t="str"/>
-      <x:c r="I8" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J8" s="31" t="str">
-        <x:v>Summary only.</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/physics_intro%20full%20report.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="31" t="str">
-        <x:v>SRC005</x:v>
-      </x:c>
-      <x:c r="B9" s="31" t="str">
-        <x:v>recipts/photo_10_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C9" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
-        <x:v>49752</x:v>
-      </x:c>
-      <x:c r="E9" s="31" t="str">
-        <x:v>b424f88e66186c7fdfcd19043e65ade1aef245c80f81328c53bd4c1354047ea3</x:v>
-      </x:c>
-      <x:c r="F9" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G9" s="31" t="str">
-        <x:v>TX0090</x:v>
-      </x:c>
-      <x:c r="H9" s="31" t="str"/>
-      <x:c r="I9" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J9" s="31" t="str"/>
-      <x:c r="K9" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_10_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="31" t="str">
-        <x:v>SRC006</x:v>
-      </x:c>
-      <x:c r="B10" s="31" t="str">
-        <x:v>recipts/photo_11_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C10" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
-        <x:v>31986</x:v>
-      </x:c>
-      <x:c r="E10" s="31" t="str">
-        <x:v>4b6a665eaaa0ff0a14e2f665cd7ef1480d78c90efa576fa0f1cf910698baacc6</x:v>
-      </x:c>
-      <x:c r="F10" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G10" s="31" t="str">
-        <x:v>TX0091</x:v>
-      </x:c>
-      <x:c r="H10" s="31" t="str"/>
-      <x:c r="I10" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J10" s="31" t="str"/>
-      <x:c r="K10" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_11_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="31" t="str">
-        <x:v>SRC007</x:v>
-      </x:c>
-      <x:c r="B11" s="31" t="str">
-        <x:v>recipts/photo_12_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C11" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
-        <x:v>50026</x:v>
-      </x:c>
-      <x:c r="E11" s="31" t="str">
-        <x:v>77e952d643e05bc03bdd136daa677561a5610e8049fb8d8aedfc24280909d917</x:v>
-      </x:c>
-      <x:c r="F11" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G11" s="31" t="str">
-        <x:v>TX0092</x:v>
-      </x:c>
-      <x:c r="H11" s="31" t="str"/>
-      <x:c r="I11" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J11" s="31" t="str"/>
-      <x:c r="K11" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_12_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="31" t="str">
-        <x:v>SRC008</x:v>
-      </x:c>
-      <x:c r="B12" s="31" t="str">
-        <x:v>recipts/photo_1_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C12" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
-        <x:v>58923</x:v>
-      </x:c>
-      <x:c r="E12" s="31" t="str">
-        <x:v>9b398cb3fd79cacf08994828e10209d3739b9ec072ff9dbdb29e456ad1a29262</x:v>
-      </x:c>
-      <x:c r="F12" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G12" s="31" t="str">
-        <x:v>TX0083</x:v>
-      </x:c>
-      <x:c r="H12" s="31" t="str"/>
-      <x:c r="I12" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J12" s="31" t="str"/>
-      <x:c r="K12" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_1_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="31" t="str">
-        <x:v>SRC009</x:v>
-      </x:c>
-      <x:c r="B13" s="31" t="str">
-        <x:v>recipts/photo_1_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C13" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
-        <x:v>44693</x:v>
-      </x:c>
-      <x:c r="E13" s="31" t="str">
-        <x:v>a50d13d6abcf5b4aacd05fa7fa773b5c01a6d2739577691d719c1bf334433b52</x:v>
-      </x:c>
-      <x:c r="F13" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G13" s="31" t="str">
-        <x:v>TX0022</x:v>
-      </x:c>
-      <x:c r="H13" s="31" t="str"/>
-      <x:c r="I13" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J13" s="31" t="str">
-        <x:v>Duplicate of photo_16.</x:v>
-      </x:c>
-      <x:c r="K13" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_1_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="31" t="str">
-        <x:v>SRC010</x:v>
-      </x:c>
-      <x:c r="B14" s="31" t="str">
-        <x:v>recipts/photo_2026-10-10_12-16-28.jpg</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
-        <x:v>160143</x:v>
-      </x:c>
-      <x:c r="E14" s="31" t="str">
-        <x:v>99a77eab001c2f3c72a639a7ec75b0a97bb90c5e5e244a8cf575d61107bedcc9</x:v>
-      </x:c>
-      <x:c r="F14" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G14" s="31" t="str">
-        <x:v>TX0089</x:v>
-      </x:c>
-      <x:c r="H14" s="31" t="str"/>
-      <x:c r="I14" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J14" s="31" t="str">
-        <x:v>Invoice only.</x:v>
-      </x:c>
-      <x:c r="K14" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_2026-10-10_12-16-28.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="31" t="str">
-        <x:v>SRC011</x:v>
-      </x:c>
-      <x:c r="B15" s="31" t="str">
-        <x:v>recipts/photo_2_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C15" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
-        <x:v>57944</x:v>
-      </x:c>
-      <x:c r="E15" s="31" t="str">
-        <x:v>5b8abe4d9a9d270a1a5cb0583fbb4ff555d551b16023d63343affe459769150f</x:v>
-      </x:c>
-      <x:c r="F15" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G15" s="31" t="str">
-        <x:v>TX0084</x:v>
-      </x:c>
-      <x:c r="H15" s="31" t="str"/>
-      <x:c r="I15" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="str"/>
-      <x:c r="K15" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_2_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="31" t="str">
-        <x:v>SRC012</x:v>
-      </x:c>
-      <x:c r="B16" s="31" t="str">
-        <x:v>recipts/photo_2_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
-        <x:v>39945</x:v>
-      </x:c>
-      <x:c r="E16" s="31" t="str">
-        <x:v>6f9a6e2d264b36faa78b41d76c6a1448122e4a243a95c361fd1281ae2bc47e4a</x:v>
-      </x:c>
-      <x:c r="F16" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G16" s="31" t="str">
-        <x:v>TX0076</x:v>
-      </x:c>
-      <x:c r="H16" s="31" t="str"/>
-      <x:c r="I16" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="str"/>
-      <x:c r="K16" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_2_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="31" t="str">
-        <x:v>SRC013</x:v>
-      </x:c>
-      <x:c r="B17" s="31" t="str">
-        <x:v>recipts/photo_3_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
-        <x:v>48603</x:v>
-      </x:c>
-      <x:c r="E17" s="31" t="str">
-        <x:v>5e9f3828411eb9b655e40edf6506756897d37de7bd8a35ea38c9eee80d9742c0</x:v>
-      </x:c>
-      <x:c r="F17" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G17" s="31" t="str">
-        <x:v>TX0085</x:v>
-      </x:c>
-      <x:c r="H17" s="31" t="str"/>
-      <x:c r="I17" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J17" s="31" t="str"/>
-      <x:c r="K17" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_3_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="31" t="str">
-        <x:v>SRC014</x:v>
-      </x:c>
-      <x:c r="B18" s="31" t="str">
-        <x:v>recipts/photo_3_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
-        <x:v>45037</x:v>
-      </x:c>
-      <x:c r="E18" s="31" t="str">
-        <x:v>89cfe54d6ab70d44461da04c4318c4b7a11f78947d9a61bda0e7266fbcc3bdab</x:v>
-      </x:c>
-      <x:c r="F18" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G18" s="31" t="str">
-        <x:v>TX0075</x:v>
-      </x:c>
-      <x:c r="H18" s="31" t="str"/>
-      <x:c r="I18" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="str"/>
-      <x:c r="K18" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_3_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="31" t="str">
-        <x:v>SRC015</x:v>
-      </x:c>
-      <x:c r="B19" s="31" t="str">
-        <x:v>recipts/photo_4_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C19" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
-        <x:v>49704</x:v>
-      </x:c>
-      <x:c r="E19" s="31" t="str">
-        <x:v>da2ff247cc7b5f3f295635d3052d3d599eebc0806a657613e584d1cce0639769</x:v>
-      </x:c>
-      <x:c r="F19" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G19" s="31" t="str">
-        <x:v>TX0081</x:v>
-      </x:c>
-      <x:c r="H19" s="31" t="str"/>
-      <x:c r="I19" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J19" s="31" t="str"/>
-      <x:c r="K19" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_4_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="31" t="str">
-        <x:v>SRC016</x:v>
-      </x:c>
-      <x:c r="B20" s="31" t="str">
-        <x:v>recipts/photo_4_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C20" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
-        <x:v>44990</x:v>
-      </x:c>
-      <x:c r="E20" s="31" t="str">
-        <x:v>44a438cc79650702edcbab92c8d1b6d5bc74008f068089c928f463f0657d2162</x:v>
-      </x:c>
-      <x:c r="F20" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G20" s="31" t="str">
-        <x:v>TX0043</x:v>
-      </x:c>
-      <x:c r="H20" s="31" t="str"/>
-      <x:c r="I20" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="str"/>
-      <x:c r="K20" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_4_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="31" t="str">
-        <x:v>SRC017</x:v>
-      </x:c>
-      <x:c r="B21" s="31" t="str">
-        <x:v>recipts/photo_5_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C21" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
-        <x:v>49513</x:v>
-      </x:c>
-      <x:c r="E21" s="31" t="str">
-        <x:v>556c6c35f9ce9e0fb5845f3b0d5b9a1b2696d7e1377af7f4c39d6a23e4360af2</x:v>
-      </x:c>
-      <x:c r="F21" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G21" s="31" t="str">
-        <x:v>TX0080</x:v>
-      </x:c>
-      <x:c r="H21" s="31" t="str"/>
-      <x:c r="I21" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="str"/>
-      <x:c r="K21" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_5_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="31" t="str">
-        <x:v>SRC018</x:v>
-      </x:c>
-      <x:c r="B22" s="31" t="str">
-        <x:v>recipts/photo_5_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C22" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
-        <x:v>39739</x:v>
-      </x:c>
-      <x:c r="E22" s="31" t="str">
-        <x:v>63f59a169b5a2bb5dd1bc0587d75173d88da586a0b9b30cbe7effcd5b676c67c</x:v>
-      </x:c>
-      <x:c r="F22" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G22" s="31" t="str">
-        <x:v>TX0077</x:v>
-      </x:c>
-      <x:c r="H22" s="31" t="str"/>
-      <x:c r="I22" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="str"/>
-      <x:c r="K22" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_5_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="31" t="str">
-        <x:v>SRC019</x:v>
-      </x:c>
-      <x:c r="B23" s="31" t="str">
-        <x:v>recipts/photo_6_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C23" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
-        <x:v>57246</x:v>
-      </x:c>
-      <x:c r="E23" s="31" t="str">
-        <x:v>3e2419ef0ccbe67c3e775ffb4f32e97152e3923bab3c3760071727253938e142</x:v>
-      </x:c>
-      <x:c r="F23" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G23" s="31" t="str">
-        <x:v>TX0088</x:v>
-      </x:c>
-      <x:c r="H23" s="31" t="str"/>
-      <x:c r="I23" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J23" s="31" t="str"/>
-      <x:c r="K23" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_6_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="31" t="str">
-        <x:v>SRC020</x:v>
-      </x:c>
-      <x:c r="B24" s="31" t="str">
-        <x:v>recipts/photo_6_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C24" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
-        <x:v>41211</x:v>
-      </x:c>
-      <x:c r="E24" s="31" t="str">
-        <x:v>2a51ef05147371b78e220f491a2c3e82578cb8a9cc8a65128cd503f3f2eaf183</x:v>
-      </x:c>
-      <x:c r="F24" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G24" s="31" t="str">
-        <x:v>TX0061</x:v>
-      </x:c>
-      <x:c r="H24" s="31" t="str"/>
-      <x:c r="I24" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="str"/>
-      <x:c r="K24" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_6_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="31" t="str">
-        <x:v>SRC021</x:v>
-      </x:c>
-      <x:c r="B25" s="31" t="str">
-        <x:v>recipts/photo_7_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C25" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
-        <x:v>49510</x:v>
-      </x:c>
-      <x:c r="E25" s="31" t="str">
-        <x:v>805ebbd2b231c7cf1c2858b5a056938b59dd5c7ccaed44d74c4edc20f4b57ce2</x:v>
-      </x:c>
-      <x:c r="F25" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G25" s="31" t="str">
-        <x:v>TX0086</x:v>
-      </x:c>
-      <x:c r="H25" s="31" t="str"/>
-      <x:c r="I25" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J25" s="31" t="str"/>
-      <x:c r="K25" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_7_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="31" t="str">
-        <x:v>SRC022</x:v>
-      </x:c>
-      <x:c r="B26" s="31" t="str">
-        <x:v>recipts/photo_7_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C26" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
-        <x:v>44918</x:v>
-      </x:c>
-      <x:c r="E26" s="31" t="str">
-        <x:v>1bfe3e9b9076ece14313b068bc35b4b58c247e5b9fbf0c8ac9d9161c5a1eab10</x:v>
-      </x:c>
-      <x:c r="F26" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G26" s="31" t="str">
-        <x:v>TX0079</x:v>
-      </x:c>
-      <x:c r="H26" s="31" t="str"/>
-      <x:c r="I26" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="str"/>
-      <x:c r="K26" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_7_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="31" t="str">
-        <x:v>SRC023</x:v>
-      </x:c>
-      <x:c r="B27" s="31" t="str">
-        <x:v>recipts/photo_8_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-      <x:c r="C27" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
-        <x:v>48893</x:v>
-      </x:c>
-      <x:c r="E27" s="31" t="str">
-        <x:v>75fee797d13ddb85ea935721b36fb145c6c9fe6b2ea11406f10a551c57acac32</x:v>
-      </x:c>
-      <x:c r="F27" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G27" s="31" t="str">
-        <x:v>TX0087</x:v>
-      </x:c>
-      <x:c r="H27" s="31" t="str"/>
-      <x:c r="I27" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="str"/>
-      <x:c r="K27" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_8_2026-10-10_11-09-04.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="31" t="str">
-        <x:v>SRC024</x:v>
-      </x:c>
-      <x:c r="B28" s="31" t="str">
-        <x:v>recipts/photo_8_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-      <x:c r="C28" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D28" s="31" t="n">
-        <x:v>39907</x:v>
-      </x:c>
-      <x:c r="E28" s="31" t="str">
-        <x:v>ae9fe7eccdae6bf86a1de9ecb8dc330494dec3835c76a1f55a0dd695297689b8</x:v>
-      </x:c>
-      <x:c r="F28" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G28" s="31" t="str">
-        <x:v>TX0078</x:v>
-      </x:c>
-      <x:c r="H28" s="31" t="str"/>
-      <x:c r="I28" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="str"/>
-      <x:c r="K28" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/recipts/photo_8_2026-10-10_14-07-27.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="24" hidden="0" customHeight="1">
-      <x:c r="A29" s="31" t="str">
-        <x:v>SRC025</x:v>
-      </x:c>
-      <x:c r="B29" s="31" t="str">
-        <x:v>telegram export/files/CamScanner 13-05-2026 12.43 (1).pdf</x:v>
-      </x:c>
-      <x:c r="C29" s="31" t="str">
-        <x:v>pdf</x:v>
-      </x:c>
-      <x:c r="D29" s="31" t="n">
-        <x:v>7377808</x:v>
-      </x:c>
-      <x:c r="E29" s="31" t="str">
-        <x:v>6710c8248b7f8f3fb3ccc8ef74c9e5f017aa69fcd6c02fb1e5e4f8d33d134b2b</x:v>
-      </x:c>
-      <x:c r="F29" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G29" s="31" t="str">
-        <x:v>TX0064, TX0065, TX0066, TX0067, TX0068, TX0069, TX0070, TX0071, TX0072, TX0073, TX0074</x:v>
-      </x:c>
-      <x:c r="H29" s="31" t="str">
-        <x:v>message124</x:v>
-      </x:c>
-      <x:c r="I29" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J29" s="31" t="str">
-        <x:v>11 pages = scan_pages_01-03, 04-06, 07-09, 10-11. Independent page review used.</x:v>
-      </x:c>
-      <x:c r="K29" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/CamScanner%2013-05-2026%2012.43%20(1).pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="31" t="str">
-        <x:v>SRC026</x:v>
-      </x:c>
-      <x:c r="B30" s="31" t="str">
-        <x:v>telegram export/files/dk-file-2025-10-16-14-43-08.pdf</x:v>
-      </x:c>
-      <x:c r="C30" s="31" t="str">
-        <x:v>pdf</x:v>
-      </x:c>
-      <x:c r="D30" s="31" t="n">
-        <x:v>326283</x:v>
-      </x:c>
-      <x:c r="E30" s="31" t="str">
-        <x:v>6e8ce528a639e8464eeb696a426eea1e00398cec8ff5e910340153fd01552139</x:v>
-      </x:c>
-      <x:c r="F30" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G30" s="31" t="str">
-        <x:v>TX0032</x:v>
-      </x:c>
-      <x:c r="H30" s="31" t="str">
-        <x:v>message66</x:v>
-      </x:c>
-      <x:c r="I30" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J30" s="31" t="str">
-        <x:v>INV001/002.</x:v>
-      </x:c>
-      <x:c r="K30" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/dk-file-2025-10-16-14-43-08.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="31" t="str">
-        <x:v>SRC027</x:v>
-      </x:c>
-      <x:c r="B31" s="31" t="str">
-        <x:v>telegram export/files/report_LaTeX.txt</x:v>
-      </x:c>
-      <x:c r="C31" s="31" t="str">
-        <x:v>txt</x:v>
-      </x:c>
-      <x:c r="D31" s="31" t="n">
-        <x:v>6858</x:v>
-      </x:c>
-      <x:c r="E31" s="31" t="str">
-        <x:v>31bbba72112289413c94d94087af8adf90da26ee8f61c7340c3042896a931038</x:v>
-      </x:c>
-      <x:c r="F31" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G31" s="31" t="str">
-        <x:v>TX0001</x:v>
-      </x:c>
-      <x:c r="H31" s="31" t="str">
-        <x:v>message7</x:v>
-      </x:c>
-      <x:c r="I31" s="31" t="str">
-        <x:v>Context only</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="str">
-        <x:v>Allocation control.</x:v>
-      </x:c>
-      <x:c r="K31" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/report_LaTeX.txt</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="31" t="str">
-        <x:v>SRC028</x:v>
-      </x:c>
-      <x:c r="B32" s="31" t="str">
-        <x:v>telegram export/files/report_Mathematica.txt</x:v>
-      </x:c>
-      <x:c r="C32" s="31" t="str">
-        <x:v>txt</x:v>
-      </x:c>
-      <x:c r="D32" s="31" t="n">
-        <x:v>5711</x:v>
-      </x:c>
-      <x:c r="E32" s="31" t="str">
-        <x:v>63b8607b7119b6c9b55fc9d03c59faa2b7722b6d12fd9ec43f51827b9048224b</x:v>
-      </x:c>
-      <x:c r="F32" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G32" s="31" t="str">
-        <x:v>TX0001</x:v>
-      </x:c>
-      <x:c r="H32" s="31" t="str">
-        <x:v>message8</x:v>
-      </x:c>
-      <x:c r="I32" s="31" t="str">
-        <x:v>Context only</x:v>
-      </x:c>
-      <x:c r="J32" s="31" t="str">
-        <x:v>Allocation control.</x:v>
-      </x:c>
-      <x:c r="K32" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/report_Mathematica.txt</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="31" t="str">
-        <x:v>SRC029</x:v>
-      </x:c>
-      <x:c r="B33" s="31" t="str">
-        <x:v>telegram export/files/report_Python.txt</x:v>
-      </x:c>
-      <x:c r="C33" s="31" t="str">
-        <x:v>txt</x:v>
-      </x:c>
-      <x:c r="D33" s="31" t="n">
-        <x:v>6285</x:v>
-      </x:c>
-      <x:c r="E33" s="31" t="str">
-        <x:v>8ff96f7277fc07553a6ac271872413e31de240ec23f25984e53ebd6202e8e6b6</x:v>
-      </x:c>
-      <x:c r="F33" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G33" s="31" t="str">
-        <x:v>TX0001</x:v>
-      </x:c>
-      <x:c r="H33" s="31" t="str">
-        <x:v>message6</x:v>
-      </x:c>
-      <x:c r="I33" s="31" t="str">
-        <x:v>Context only</x:v>
-      </x:c>
-      <x:c r="J33" s="31" t="str">
-        <x:v>Allocation control; contains personal data.</x:v>
-      </x:c>
-      <x:c r="K33" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/files/report_Python.txt</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="36" hidden="0" customHeight="1">
-      <x:c r="A34" s="31" t="str">
-        <x:v>SRC030</x:v>
-      </x:c>
-      <x:c r="B34" s="31" t="str">
-        <x:v>telegram export/messages.html</x:v>
-      </x:c>
-      <x:c r="C34" s="31" t="str">
-        <x:v>html</x:v>
-      </x:c>
-      <x:c r="D34" s="31" t="n">
-        <x:v>116651</x:v>
-      </x:c>
-      <x:c r="E34" s="31" t="str">
-        <x:v>4ac19a5c1db97672da0893539fa00e862d2f986c2b12a577bfe816891b24e7e4</x:v>
-      </x:c>
-      <x:c r="F34" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G34" s="31" t="str">
-        <x:v>TX0008, TX0018, TX0029, TX0030, TX0035, TX0036, TX0039, TX0040, TX0041, TX0047, TX0048, TX0049, TX0058</x:v>
-      </x:c>
-      <x:c r="H34" s="31" t="str"/>
-      <x:c r="I34" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J34" s="31" t="str">
-        <x:v>All financial messages were mapped. Non-financial chat is context only (commitments in project_notes).</x:v>
-      </x:c>
-      <x:c r="K34" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/messages.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="15" hidden="0" customHeight="1">
-      <x:c r="A35" s="31" t="str">
-        <x:v>SRC031</x:v>
-      </x:c>
-      <x:c r="B35" s="31" t="str">
-        <x:v>telegram export/photos/photo_10@15-08-2025_18-28-22.jpg</x:v>
-      </x:c>
-      <x:c r="C35" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D35" s="31" t="n">
-        <x:v>74672</x:v>
-      </x:c>
-      <x:c r="E35" s="31" t="str">
-        <x:v>28455c00bd0229cddc0b8874a8b025fc25700f4e553b6c67bdfc9082b2cad0b7</x:v>
-      </x:c>
-      <x:c r="F35" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G35" s="31" t="str">
-        <x:v>TX0012</x:v>
-      </x:c>
-      <x:c r="H35" s="31" t="str">
-        <x:v>message47</x:v>
-      </x:c>
-      <x:c r="I35" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J35" s="31" t="str"/>
-      <x:c r="K35" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_10%4015-08-2025_18-28-22.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="15" hidden="0" customHeight="1">
-      <x:c r="A36" s="31" t="str">
-        <x:v>SRC032</x:v>
-      </x:c>
-      <x:c r="B36" s="31" t="str">
-        <x:v>telegram export/photos/photo_11@04-09-2025_14-05-56.jpg</x:v>
-      </x:c>
-      <x:c r="C36" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D36" s="31" t="n">
-        <x:v>56585</x:v>
-      </x:c>
-      <x:c r="E36" s="31" t="str">
-        <x:v>dba6c9549b471a9a2d016b29b57970c53eedf21a4f80e3a841478cf04784555e</x:v>
-      </x:c>
-      <x:c r="F36" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G36" s="31" t="str">
-        <x:v>TX0015</x:v>
-      </x:c>
-      <x:c r="H36" s="31" t="str">
-        <x:v>message48</x:v>
-      </x:c>
-      <x:c r="I36" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J36" s="31" t="str"/>
-      <x:c r="K36" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_11%4004-09-2025_14-05-56.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="15" hidden="0" customHeight="1">
-      <x:c r="A37" s="31" t="str">
-        <x:v>SRC033</x:v>
-      </x:c>
-      <x:c r="B37" s="31" t="str">
-        <x:v>telegram export/photos/photo_12@01-10-2025_18-02-44.jpg</x:v>
-      </x:c>
-      <x:c r="C37" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D37" s="31" t="n">
-        <x:v>48640</x:v>
-      </x:c>
-      <x:c r="E37" s="31" t="str">
-        <x:v>6295ac27d8bc4463d51132d3a86a8e01dc37946b107ee50d0c77ceffe9470b4c</x:v>
-      </x:c>
-      <x:c r="F37" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G37" s="31" t="str">
-        <x:v>TX0018</x:v>
-      </x:c>
-      <x:c r="H37" s="31" t="str">
-        <x:v>message51</x:v>
-      </x:c>
-      <x:c r="I37" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J37" s="31" t="str"/>
-      <x:c r="K37" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_12%4001-10-2025_18-02-44.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="15" hidden="0" customHeight="1">
-      <x:c r="A38" s="31" t="str">
-        <x:v>SRC034</x:v>
-      </x:c>
-      <x:c r="B38" s="31" t="str">
-        <x:v>telegram export/photos/photo_13@12-10-2025_10-24-38.jpg</x:v>
-      </x:c>
-      <x:c r="C38" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D38" s="31" t="n">
-        <x:v>66592</x:v>
-      </x:c>
-      <x:c r="E38" s="31" t="str">
-        <x:v>6d79bcdee6b1e2fb274811a327e44deb472e519ef16ca2cb2633fddb9da7e083</x:v>
-      </x:c>
-      <x:c r="F38" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G38" s="31" t="str">
-        <x:v>TX0020</x:v>
-      </x:c>
-      <x:c r="H38" s="31" t="str">
-        <x:v>message61</x:v>
-      </x:c>
-      <x:c r="I38" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J38" s="31" t="str"/>
-      <x:c r="K38" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_13%4012-10-2025_10-24-38.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="31" t="str">
-        <x:v>SRC035</x:v>
-      </x:c>
-      <x:c r="B39" s="31" t="str">
-        <x:v>telegram export/photos/photo_14@15-10-2025_14-18-25.jpg</x:v>
-      </x:c>
-      <x:c r="C39" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D39" s="31" t="n">
-        <x:v>69226</x:v>
-      </x:c>
-      <x:c r="E39" s="31" t="str">
-        <x:v>b214b33a77c58bb0428ba09719496e21696b82ae4055292c9711694e4e16fd3b</x:v>
-      </x:c>
-      <x:c r="F39" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G39" s="31" t="str">
-        <x:v>TX0024</x:v>
-      </x:c>
-      <x:c r="H39" s="31" t="str">
-        <x:v>message62</x:v>
-      </x:c>
-      <x:c r="I39" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J39" s="31" t="str"/>
-      <x:c r="K39" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_14%4015-10-2025_14-18-25.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="15" hidden="0" customHeight="1">
-      <x:c r="A40" s="31" t="str">
-        <x:v>SRC036</x:v>
-      </x:c>
-      <x:c r="B40" s="31" t="str">
-        <x:v>telegram export/photos/photo_15@15-10-2025_14-18-25.jpg</x:v>
-      </x:c>
-      <x:c r="C40" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D40" s="31" t="n">
-        <x:v>64998</x:v>
-      </x:c>
-      <x:c r="E40" s="31" t="str">
-        <x:v>f31ffa6bdd2395d18e073911daffc69b21952eaef6f5b1d6bcf7beacb8193f96</x:v>
-      </x:c>
-      <x:c r="F40" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G40" s="31" t="str">
-        <x:v>TX0019</x:v>
-      </x:c>
-      <x:c r="H40" s="31" t="str">
-        <x:v>message63</x:v>
-      </x:c>
-      <x:c r="I40" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J40" s="31" t="str"/>
-      <x:c r="K40" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_15%4015-10-2025_14-18-25.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="15" hidden="0" customHeight="1">
-      <x:c r="A41" s="31" t="str">
-        <x:v>SRC037</x:v>
-      </x:c>
-      <x:c r="B41" s="31" t="str">
-        <x:v>telegram export/photos/photo_16@15-10-2025_14-18-26.jpg</x:v>
-      </x:c>
-      <x:c r="C41" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D41" s="31" t="n">
-        <x:v>68536</x:v>
-      </x:c>
-      <x:c r="E41" s="31" t="str">
-        <x:v>28db8e201da1e5584cadcf90b8a007d7293f769983b96c5cee2f7e2e3fd3fa83</x:v>
-      </x:c>
-      <x:c r="F41" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G41" s="31" t="str">
-        <x:v>TX0021</x:v>
-      </x:c>
-      <x:c r="H41" s="31" t="str">
-        <x:v>message64</x:v>
-      </x:c>
-      <x:c r="I41" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J41" s="31" t="str"/>
-      <x:c r="K41" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_16%4015-10-2025_14-18-26.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="15" hidden="0" customHeight="1">
-      <x:c r="A42" s="31" t="str">
-        <x:v>SRC038</x:v>
-      </x:c>
-      <x:c r="B42" s="31" t="str">
-        <x:v>telegram export/photos/photo_17@15-10-2025_14-18-26.jpg</x:v>
-      </x:c>
-      <x:c r="C42" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D42" s="31" t="n">
-        <x:v>68859</x:v>
-      </x:c>
-      <x:c r="E42" s="31" t="str">
-        <x:v>ed8841b0f4a343d505b7aecc8f250fbe6f41fbcf2dcf64ca77e75a72fcf51b2b</x:v>
-      </x:c>
-      <x:c r="F42" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G42" s="31" t="str">
-        <x:v>TX0023</x:v>
-      </x:c>
-      <x:c r="H42" s="31" t="str">
-        <x:v>message65</x:v>
-      </x:c>
-      <x:c r="I42" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J42" s="31" t="str"/>
-      <x:c r="K42" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_17%4015-10-2025_14-18-26.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="15" hidden="0" customHeight="1">
-      <x:c r="A43" s="31" t="str">
-        <x:v>SRC039</x:v>
-      </x:c>
-      <x:c r="B43" s="31" t="str">
-        <x:v>telegram export/photos/photo_18@28-10-2025_01-53-01.jpg</x:v>
-      </x:c>
-      <x:c r="C43" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D43" s="31" t="n">
-        <x:v>69491</x:v>
-      </x:c>
-      <x:c r="E43" s="31" t="str">
-        <x:v>52872081d1c4fc01e8f48c9cae4df8a96c78c269d03384ab89a398a382fda9e2</x:v>
-      </x:c>
-      <x:c r="F43" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G43" s="31" t="str">
-        <x:v>TX0027</x:v>
-      </x:c>
-      <x:c r="H43" s="31" t="str">
-        <x:v>message67</x:v>
-      </x:c>
-      <x:c r="I43" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J43" s="31" t="str"/>
-      <x:c r="K43" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_18%4028-10-2025_01-53-01.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="31" t="str">
-        <x:v>SRC040</x:v>
-      </x:c>
-      <x:c r="B44" s="31" t="str">
-        <x:v>telegram export/photos/photo_19@28-10-2025_01-58-07.jpg</x:v>
-      </x:c>
-      <x:c r="C44" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D44" s="31" t="n">
-        <x:v>65290</x:v>
-      </x:c>
-      <x:c r="E44" s="31" t="str">
-        <x:v>6406d711ff22151beab2efc5ad32dff29634b42c4df6d6c1de3e76cff738b2ca</x:v>
-      </x:c>
-      <x:c r="F44" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G44" s="31" t="str">
-        <x:v>TX0032</x:v>
-      </x:c>
-      <x:c r="H44" s="31" t="str">
-        <x:v>message69</x:v>
-      </x:c>
-      <x:c r="I44" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J44" s="31" t="str"/>
-      <x:c r="K44" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_19%4028-10-2025_01-58-07.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="15" hidden="0" customHeight="1">
-      <x:c r="A45" s="31" t="str">
-        <x:v>SRC041</x:v>
-      </x:c>
-      <x:c r="B45" s="31" t="str">
-        <x:v>telegram export/photos/photo_1@24-07-2025_21-00-16.jpg</x:v>
-      </x:c>
-      <x:c r="C45" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D45" s="31" t="n">
-        <x:v>73477</x:v>
-      </x:c>
-      <x:c r="E45" s="31" t="str">
-        <x:v>79265bb04e6428f336712238ba43edcc9065f4a4313a8b75c7f937a113c99ce2</x:v>
-      </x:c>
-      <x:c r="F45" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G45" s="31" t="str">
-        <x:v>TX0002</x:v>
-      </x:c>
-      <x:c r="H45" s="31" t="str">
-        <x:v>message25</x:v>
-      </x:c>
-      <x:c r="I45" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J45" s="31" t="str"/>
-      <x:c r="K45" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_1%4024-07-2025_21-00-16.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="15" hidden="0" customHeight="1">
-      <x:c r="A46" s="31" t="str">
-        <x:v>SRC042</x:v>
-      </x:c>
-      <x:c r="B46" s="31" t="str">
-        <x:v>telegram export/photos/photo_20@28-10-2025_22-07-57.jpg</x:v>
-      </x:c>
-      <x:c r="C46" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D46" s="31" t="n">
-        <x:v>145202</x:v>
-      </x:c>
-      <x:c r="E46" s="31" t="str">
-        <x:v>18a41c8ef151421d6a8438c0c292c313bd9d69817efed89507abf1bb0e852e6b</x:v>
-      </x:c>
-      <x:c r="F46" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G46" s="31" t="str">
-        <x:v>TX0026</x:v>
-      </x:c>
-      <x:c r="H46" s="31" t="str">
-        <x:v>message71</x:v>
-      </x:c>
-      <x:c r="I46" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J46" s="31" t="str"/>
-      <x:c r="K46" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_20%4028-10-2025_22-07-57.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="15" hidden="0" customHeight="1">
-      <x:c r="A47" s="31" t="str">
-        <x:v>SRC043</x:v>
-      </x:c>
-      <x:c r="B47" s="31" t="str">
-        <x:v>telegram export/photos/photo_21@09-11-2025_23-16-09.jpg</x:v>
-      </x:c>
-      <x:c r="C47" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D47" s="31" t="n">
-        <x:v>89073</x:v>
-      </x:c>
-      <x:c r="E47" s="31" t="str">
-        <x:v>430d605cb4bf4e4aaaf901e209b69c43c2d82946451612543b40ef112ba1fe22</x:v>
-      </x:c>
-      <x:c r="F47" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G47" s="31" t="str">
-        <x:v>TX0037</x:v>
-      </x:c>
-      <x:c r="H47" s="31" t="str">
-        <x:v>message90</x:v>
-      </x:c>
-      <x:c r="I47" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J47" s="31" t="str">
-        <x:v>INV003.</x:v>
-      </x:c>
-      <x:c r="K47" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_21%4009-11-2025_23-16-09.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="15" hidden="0" customHeight="1">
-      <x:c r="A48" s="31" t="str">
-        <x:v>SRC044</x:v>
-      </x:c>
-      <x:c r="B48" s="31" t="str">
-        <x:v>telegram export/photos/photo_22@09-11-2025_23-16-15.jpg</x:v>
-      </x:c>
-      <x:c r="C48" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D48" s="31" t="n">
-        <x:v>84952</x:v>
-      </x:c>
-      <x:c r="E48" s="31" t="str">
-        <x:v>64e9c8107140b08a348e146533350e8bd264e2f59b1f09ade0e80ba76639f360</x:v>
-      </x:c>
-      <x:c r="F48" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G48" s="31" t="str">
-        <x:v>TX0038</x:v>
-      </x:c>
-      <x:c r="H48" s="31" t="str">
-        <x:v>message91</x:v>
-      </x:c>
-      <x:c r="I48" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J48" s="31" t="str">
-        <x:v>INV004.</x:v>
-      </x:c>
-      <x:c r="K48" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_22%4009-11-2025_23-16-15.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="31" t="str">
-        <x:v>SRC045</x:v>
-      </x:c>
-      <x:c r="B49" s="31" t="str">
-        <x:v>telegram export/photos/photo_23@14-11-2025_04-07-19.jpg</x:v>
-      </x:c>
-      <x:c r="C49" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D49" s="31" t="n">
-        <x:v>65632</x:v>
-      </x:c>
-      <x:c r="E49" s="31" t="str">
-        <x:v>7003f7a94da98c211e78490a0c98ad1e5681266cb40708889b8d9b8cb66f3455</x:v>
-      </x:c>
-      <x:c r="F49" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G49" s="31" t="str">
-        <x:v>TX0037</x:v>
-      </x:c>
-      <x:c r="H49" s="31" t="str">
-        <x:v>message99</x:v>
-      </x:c>
-      <x:c r="I49" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J49" s="31" t="str"/>
-      <x:c r="K49" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_23%4014-11-2025_04-07-19.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="31" t="str">
-        <x:v>SRC046</x:v>
-      </x:c>
-      <x:c r="B50" s="31" t="str">
-        <x:v>telegram export/photos/photo_24@14-11-2025_04-07-19.jpg</x:v>
-      </x:c>
-      <x:c r="C50" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D50" s="31" t="n">
-        <x:v>66823</x:v>
-      </x:c>
-      <x:c r="E50" s="31" t="str">
-        <x:v>2944f175b5256a669c1a6407a09eecb566d715c37dd54b80eed0cee2ae943f0c</x:v>
-      </x:c>
-      <x:c r="F50" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G50" s="31" t="str">
-        <x:v>TX0038</x:v>
-      </x:c>
-      <x:c r="H50" s="31" t="str">
-        <x:v>message100</x:v>
-      </x:c>
-      <x:c r="I50" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J50" s="31" t="str"/>
-      <x:c r="K50" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_24%4014-11-2025_04-07-19.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="15" hidden="0" customHeight="1">
-      <x:c r="A51" s="31" t="str">
-        <x:v>SRC047</x:v>
-      </x:c>
-      <x:c r="B51" s="31" t="str">
-        <x:v>telegram export/photos/photo_25@19-11-2025_11-46-31.jpg</x:v>
-      </x:c>
-      <x:c r="C51" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D51" s="31" t="n">
-        <x:v>18253</x:v>
-      </x:c>
-      <x:c r="E51" s="31" t="str">
-        <x:v>5c7d3623f81cfec1c847235a9e6124fc4d7090687911db318684c83dc455de7f</x:v>
-      </x:c>
-      <x:c r="F51" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G51" s="31" t="str">
-        <x:v>TX0044</x:v>
-      </x:c>
-      <x:c r="H51" s="31" t="str">
-        <x:v>message102</x:v>
-      </x:c>
-      <x:c r="I51" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J51" s="31" t="str"/>
-      <x:c r="K51" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_25%4019-11-2025_11-46-31.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="15" hidden="0" customHeight="1">
-      <x:c r="A52" s="31" t="str">
-        <x:v>SRC048</x:v>
-      </x:c>
-      <x:c r="B52" s="31" t="str">
-        <x:v>telegram export/photos/photo_26@21-12-2025_05-36-21.jpg</x:v>
-      </x:c>
-      <x:c r="C52" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D52" s="31" t="n">
-        <x:v>35321</x:v>
-      </x:c>
-      <x:c r="E52" s="31" t="str">
-        <x:v>a7ff8727fc0c461dc0be5e4bbc9c6c1409720229eae30931e3ae85f417819512</x:v>
-      </x:c>
-      <x:c r="F52" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G52" s="31" t="str">
-        <x:v>TX0046</x:v>
-      </x:c>
-      <x:c r="H52" s="31" t="str">
-        <x:v>message112</x:v>
-      </x:c>
-      <x:c r="I52" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J52" s="31" t="str"/>
-      <x:c r="K52" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_26%4021-12-2025_05-36-21.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="15" hidden="0" customHeight="1">
-      <x:c r="A53" s="31" t="str">
-        <x:v>SRC049</x:v>
-      </x:c>
-      <x:c r="B53" s="31" t="str">
-        <x:v>telegram export/photos/photo_27@17-05-2026_19-45-07.jpg</x:v>
-      </x:c>
-      <x:c r="C53" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D53" s="31" t="n">
-        <x:v>71982</x:v>
-      </x:c>
-      <x:c r="E53" s="31" t="str">
-        <x:v>e0e7050e5e9b2018e96723ae4831b7cdcbf4f3d79406e74efb72a47e928fe9e5</x:v>
-      </x:c>
-      <x:c r="F53" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G53" s="31" t="str">
-        <x:v>TX0063</x:v>
-      </x:c>
-      <x:c r="H53" s="31" t="str">
-        <x:v>message125</x:v>
-      </x:c>
-      <x:c r="I53" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J53" s="31" t="str"/>
-      <x:c r="K53" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_27%4017-05-2026_19-45-07.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="31" t="str">
-        <x:v>SRC050</x:v>
-      </x:c>
-      <x:c r="B54" s="31" t="str">
-        <x:v>telegram export/photos/photo_28@17-05-2026_19-45-07.jpg</x:v>
-      </x:c>
-      <x:c r="C54" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D54" s="31" t="n">
-        <x:v>72527</x:v>
-      </x:c>
-      <x:c r="E54" s="31" t="str">
-        <x:v>a79a95c1f0e5d599fc42a26df85ffafea142c9cc7caa622a0a1b3e9d5b7dae31</x:v>
-      </x:c>
-      <x:c r="F54" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G54" s="31" t="str">
-        <x:v>TX0062</x:v>
-      </x:c>
-      <x:c r="H54" s="31" t="str">
-        <x:v>message126</x:v>
-      </x:c>
-      <x:c r="I54" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J54" s="31" t="str"/>
-      <x:c r="K54" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_28%4017-05-2026_19-45-07.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="31" t="str">
-        <x:v>SRC051</x:v>
-      </x:c>
-      <x:c r="B55" s="31" t="str">
-        <x:v>telegram export/photos/photo_29@27-06-2026_18-24-14.jpg</x:v>
-      </x:c>
-      <x:c r="C55" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D55" s="31" t="n">
-        <x:v>89975</x:v>
-      </x:c>
-      <x:c r="E55" s="31" t="str">
-        <x:v>fdfebe75ba5891f2dbc84e11ef7625558452b73f3ce3b50b63d9c1745a4385b5</x:v>
-      </x:c>
-      <x:c r="F55" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G55" s="31" t="str">
-        <x:v>TX0038</x:v>
-      </x:c>
-      <x:c r="H55" s="31" t="str">
-        <x:v>message142</x:v>
-      </x:c>
-      <x:c r="I55" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J55" s="31" t="str">
-        <x:v>Second photo of INV004.</x:v>
-      </x:c>
-      <x:c r="K55" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_29%4027-06-2026_18-24-14.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="15" hidden="0" customHeight="1">
-      <x:c r="A56" s="31" t="str">
-        <x:v>SRC052</x:v>
-      </x:c>
-      <x:c r="B56" s="31" t="str">
-        <x:v>telegram export/photos/photo_2@24-07-2025_21-00-17.jpg</x:v>
-      </x:c>
-      <x:c r="C56" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D56" s="31" t="n">
-        <x:v>74772</x:v>
-      </x:c>
-      <x:c r="E56" s="31" t="str">
-        <x:v>9d1cc7913277237d5bf999452661d8ab00c1add42d2751e54bfa96521f756b17</x:v>
-      </x:c>
-      <x:c r="F56" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G56" s="31" t="str">
-        <x:v>TX0003</x:v>
-      </x:c>
-      <x:c r="H56" s="31" t="str">
-        <x:v>message26</x:v>
-      </x:c>
-      <x:c r="I56" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J56" s="31" t="str"/>
-      <x:c r="K56" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_2%4024-07-2025_21-00-17.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="15" hidden="0" customHeight="1">
-      <x:c r="A57" s="31" t="str">
-        <x:v>SRC053</x:v>
-      </x:c>
-      <x:c r="B57" s="31" t="str">
-        <x:v>telegram export/photos/photo_30@27-06-2026_18-24-31.jpg</x:v>
-      </x:c>
-      <x:c r="C57" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D57" s="31" t="n">
-        <x:v>114397</x:v>
-      </x:c>
-      <x:c r="E57" s="31" t="str">
-        <x:v>f5569b998adf63c1cebcb144277502c32db8088ce75d731cd3a7d98be3b2c669</x:v>
-      </x:c>
-      <x:c r="F57" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G57" s="31" t="str">
-        <x:v>TX0037</x:v>
-      </x:c>
-      <x:c r="H57" s="31" t="str">
-        <x:v>message143</x:v>
-      </x:c>
-      <x:c r="I57" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J57" s="31" t="str">
-        <x:v>Second photo of INV003.</x:v>
-      </x:c>
-      <x:c r="K57" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_30%4027-06-2026_18-24-31.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="15" hidden="0" customHeight="1">
-      <x:c r="A58" s="31" t="str">
-        <x:v>SRC054</x:v>
-      </x:c>
-      <x:c r="B58" s="31" t="str">
-        <x:v>telegram export/photos/photo_31@27-06-2026_18-24-39.jpg</x:v>
-      </x:c>
-      <x:c r="C58" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D58" s="31" t="n">
-        <x:v>51950</x:v>
-      </x:c>
-      <x:c r="E58" s="31" t="str">
-        <x:v>5e693fc6f8303f5ee512c9ec9b3eadec3f3d7319b2c2f969e9875baca06d790b</x:v>
-      </x:c>
-      <x:c r="F58" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G58" s="31" t="str">
-        <x:v>TX0028</x:v>
-      </x:c>
-      <x:c r="H58" s="31" t="str">
-        <x:v>message144</x:v>
-      </x:c>
-      <x:c r="I58" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J58" s="31" t="str"/>
-      <x:c r="K58" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_31%4027-06-2026_18-24-39.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="15" hidden="0" customHeight="1">
-      <x:c r="A59" s="31" t="str">
-        <x:v>SRC055</x:v>
-      </x:c>
-      <x:c r="B59" s="31" t="str">
-        <x:v>telegram export/photos/photo_32@27-06-2026_18-24-52.jpg</x:v>
-      </x:c>
-      <x:c r="C59" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D59" s="31" t="n">
-        <x:v>66516</x:v>
-      </x:c>
-      <x:c r="E59" s="31" t="str">
-        <x:v>7628c00e8636b2fb53053ed1feaab9c04fbc27a578e143dd6f1f16a64d6e00e3</x:v>
-      </x:c>
-      <x:c r="F59" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G59" s="31" t="str">
-        <x:v>TX0042</x:v>
-      </x:c>
-      <x:c r="H59" s="31" t="str">
-        <x:v>message145</x:v>
-      </x:c>
-      <x:c r="I59" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J59" s="31" t="str"/>
-      <x:c r="K59" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_32%4027-06-2026_18-24-52.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="15" hidden="0" customHeight="1">
-      <x:c r="A60" s="31" t="str">
-        <x:v>SRC056</x:v>
-      </x:c>
-      <x:c r="B60" s="31" t="str">
-        <x:v>telegram export/photos/photo_33@27-06-2026_18-25-49.jpg</x:v>
-      </x:c>
-      <x:c r="C60" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D60" s="31" t="n">
-        <x:v>69981</x:v>
-      </x:c>
-      <x:c r="E60" s="31" t="str">
-        <x:v>a0ebad23be285a1e51b629326f6f3a8dab9f52662632f4ef6194fea9855b2267</x:v>
-      </x:c>
-      <x:c r="F60" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G60" s="31" t="str">
-        <x:v>TX0033</x:v>
-      </x:c>
-      <x:c r="H60" s="31" t="str">
-        <x:v>message146</x:v>
-      </x:c>
-      <x:c r="I60" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J60" s="31" t="str"/>
-      <x:c r="K60" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_33%4027-06-2026_18-25-49.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="15" hidden="0" customHeight="1">
-      <x:c r="A61" s="31" t="str">
-        <x:v>SRC057</x:v>
-      </x:c>
-      <x:c r="B61" s="31" t="str">
-        <x:v>telegram export/photos/photo_34@27-06-2026_18-26-03.jpg</x:v>
-      </x:c>
-      <x:c r="C61" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D61" s="31" t="n">
-        <x:v>162060</x:v>
-      </x:c>
-      <x:c r="E61" s="31" t="str">
-        <x:v>d7091b678efb3e0f2e1da6270bff602fc8d5dd14fd758484945206f09aec6835</x:v>
-      </x:c>
-      <x:c r="F61" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G61" s="31" t="str">
-        <x:v>TX0033</x:v>
-      </x:c>
-      <x:c r="H61" s="31" t="str">
-        <x:v>message147</x:v>
-      </x:c>
-      <x:c r="I61" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J61" s="31" t="str">
-        <x:v>INV005, uncertain.</x:v>
-      </x:c>
-      <x:c r="K61" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_34%4027-06-2026_18-26-03.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="15" hidden="0" customHeight="1">
-      <x:c r="A62" s="31" t="str">
-        <x:v>SRC058</x:v>
-      </x:c>
-      <x:c r="B62" s="31" t="str">
-        <x:v>telegram export/photos/photo_35@27-06-2026_18-26-22.jpg</x:v>
-      </x:c>
-      <x:c r="C62" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D62" s="31" t="n">
-        <x:v>168669</x:v>
-      </x:c>
-      <x:c r="E62" s="31" t="str">
-        <x:v>df1dad972da0ba8c3da2b76b90ccdd5c9ae6c42488b2b0f50e3eb232ab177028</x:v>
-      </x:c>
-      <x:c r="F62" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G62" s="31" t="str">
-        <x:v>TX0034</x:v>
-      </x:c>
-      <x:c r="H62" s="31" t="str">
-        <x:v>message148</x:v>
-      </x:c>
-      <x:c r="I62" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J62" s="31" t="str"/>
-      <x:c r="K62" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_35%4027-06-2026_18-26-22.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="15" hidden="0" customHeight="1">
-      <x:c r="A63" s="31" t="str">
-        <x:v>SRC059</x:v>
-      </x:c>
-      <x:c r="B63" s="31" t="str">
-        <x:v>telegram export/photos/photo_36@27-06-2026_18-26-45.jpg</x:v>
-      </x:c>
-      <x:c r="C63" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D63" s="31" t="n">
-        <x:v>56182</x:v>
-      </x:c>
-      <x:c r="E63" s="31" t="str">
-        <x:v>c76783f3ab2aa8dfafe81fe1d3273e3a70b017cbb8e04ee0aebf20c7896fd8a6</x:v>
-      </x:c>
-      <x:c r="F63" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G63" s="31" t="str">
-        <x:v>TX0024</x:v>
-      </x:c>
-      <x:c r="H63" s="31" t="str">
-        <x:v>message149</x:v>
-      </x:c>
-      <x:c r="I63" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J63" s="31" t="str">
-        <x:v>Same purchase as photo_14.</x:v>
-      </x:c>
-      <x:c r="K63" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_36%4027-06-2026_18-26-45.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="31" t="str">
-        <x:v>SRC060</x:v>
-      </x:c>
-      <x:c r="B64" s="31" t="str">
-        <x:v>telegram export/photos/photo_37@27-06-2026_18-27-12.jpg</x:v>
-      </x:c>
-      <x:c r="C64" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D64" s="31" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E64" s="31" t="str">
-        <x:v>9a1f8890689207a4000e3fe0fc271e522bb56ace944c1646ccf84577b88f9405</x:v>
-      </x:c>
-      <x:c r="F64" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G64" s="31" t="str">
-        <x:v>TX0023</x:v>
-      </x:c>
-      <x:c r="H64" s="31" t="str">
-        <x:v>message150</x:v>
-      </x:c>
-      <x:c r="I64" s="31" t="str">
-        <x:v>Reconciled</x:v>
-      </x:c>
-      <x:c r="J64" s="31" t="str">
-        <x:v>Same purchase as photo_17.</x:v>
-      </x:c>
-      <x:c r="K64" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_37%4027-06-2026_18-27-12.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="15" hidden="0" customHeight="1">
-      <x:c r="A65" s="31" t="str">
-        <x:v>SRC061</x:v>
-      </x:c>
-      <x:c r="B65" s="31" t="str">
-        <x:v>telegram export/photos/photo_38@27-06-2026_18-27-25.jpg</x:v>
-      </x:c>
-      <x:c r="C65" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D65" s="31" t="n">
-        <x:v>41070</x:v>
-      </x:c>
-      <x:c r="E65" s="31" t="str">
-        <x:v>e8a6c9ba9556546fa4abbc8e152e35df08dcc2c6669884f9dc12679882029c3e</x:v>
-      </x:c>
-      <x:c r="F65" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G65" s="31" t="str">
-        <x:v>TX0060</x:v>
-      </x:c>
-      <x:c r="H65" s="31" t="str">
-        <x:v>message151</x:v>
-      </x:c>
-      <x:c r="I65" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J65" s="31" t="str"/>
-      <x:c r="K65" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_38%4027-06-2026_18-27-25.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="15" hidden="0" customHeight="1">
-      <x:c r="A66" s="31" t="str">
-        <x:v>SRC062</x:v>
-      </x:c>
-      <x:c r="B66" s="31" t="str">
-        <x:v>telegram export/photos/photo_39@27-06-2026_18-29-10.jpg</x:v>
-      </x:c>
-      <x:c r="C66" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D66" s="31" t="n">
-        <x:v>62596</x:v>
-      </x:c>
-      <x:c r="E66" s="31" t="str">
-        <x:v>2cc0dda007136a8eb626cca071cf976fa2faea1a3ec9461e2f9e61d426d539da</x:v>
-      </x:c>
-      <x:c r="F66" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G66" s="31" t="str">
-        <x:v>TX0059</x:v>
-      </x:c>
-      <x:c r="H66" s="31" t="str">
-        <x:v>message152</x:v>
-      </x:c>
-      <x:c r="I66" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J66" s="31" t="str"/>
-      <x:c r="K66" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_39%4027-06-2026_18-29-10.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="15" hidden="0" customHeight="1">
-      <x:c r="A67" s="31" t="str">
-        <x:v>SRC063</x:v>
-      </x:c>
-      <x:c r="B67" s="31" t="str">
-        <x:v>telegram export/photos/photo_3@24-07-2025_21-02-51.jpg</x:v>
-      </x:c>
-      <x:c r="C67" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D67" s="31" t="n">
-        <x:v>71647</x:v>
-      </x:c>
-      <x:c r="E67" s="31" t="str">
-        <x:v>3a30db869e1f6a6c63f03739af4268b7b0405346be7199ac5e26f23dc73806fc</x:v>
-      </x:c>
-      <x:c r="F67" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G67" s="31" t="str">
-        <x:v>TX0004</x:v>
-      </x:c>
-      <x:c r="H67" s="31" t="str">
-        <x:v>message27</x:v>
-      </x:c>
-      <x:c r="I67" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J67" s="31" t="str"/>
-      <x:c r="K67" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_3%4024-07-2025_21-02-51.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="15" hidden="0" customHeight="1">
-      <x:c r="A68" s="31" t="str">
-        <x:v>SRC064</x:v>
-      </x:c>
-      <x:c r="B68" s="31" t="str">
-        <x:v>telegram export/photos/photo_40@27-06-2026_18-31-08.jpg</x:v>
-      </x:c>
-      <x:c r="C68" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D68" s="31" t="n">
-        <x:v>59578</x:v>
-      </x:c>
-      <x:c r="E68" s="31" t="str">
-        <x:v>8e9cb970ead01179e35ef3181ee0017987b3e8de78c03c3bb37fc20f4f3ef402</x:v>
-      </x:c>
-      <x:c r="F68" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G68" s="31" t="str">
-        <x:v>TX0031</x:v>
-      </x:c>
-      <x:c r="H68" s="31" t="str">
-        <x:v>message153</x:v>
-      </x:c>
-      <x:c r="I68" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J68" s="31" t="str"/>
-      <x:c r="K68" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_40%4027-06-2026_18-31-08.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="15" hidden="0" customHeight="1">
-      <x:c r="A69" s="31" t="str">
-        <x:v>SRC065</x:v>
-      </x:c>
-      <x:c r="B69" s="31" t="str">
-        <x:v>telegram export/photos/photo_41@27-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-      <x:c r="C69" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D69" s="31" t="n">
-        <x:v>77996</x:v>
-      </x:c>
-      <x:c r="E69" s="31" t="str">
-        <x:v>78ad7571d728263883b5dc1bb9cd22848b5c2e67370643caa12c8c8935da2b20</x:v>
-      </x:c>
-      <x:c r="F69" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G69" s="31" t="str">
-        <x:v>TX0053</x:v>
-      </x:c>
-      <x:c r="H69" s="31" t="str">
-        <x:v>message155</x:v>
-      </x:c>
-      <x:c r="I69" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J69" s="31" t="str"/>
-      <x:c r="K69" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_41%4027-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="15" hidden="0" customHeight="1">
-      <x:c r="A70" s="31" t="str">
-        <x:v>SRC066</x:v>
-      </x:c>
-      <x:c r="B70" s="31" t="str">
-        <x:v>telegram export/photos/photo_42@27-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-      <x:c r="C70" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D70" s="31" t="n">
-        <x:v>77238</x:v>
-      </x:c>
-      <x:c r="E70" s="31" t="str">
-        <x:v>94ca1e41dc1aa15b41dd5ec0b9bb664d54733c8559fe9e348d1adc782f316712</x:v>
-      </x:c>
-      <x:c r="F70" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G70" s="31" t="str">
-        <x:v>TX0052</x:v>
-      </x:c>
-      <x:c r="H70" s="31" t="str">
-        <x:v>message156</x:v>
-      </x:c>
-      <x:c r="I70" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J70" s="31" t="str"/>
-      <x:c r="K70" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_42%4027-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="15" hidden="0" customHeight="1">
-      <x:c r="A71" s="31" t="str">
-        <x:v>SRC067</x:v>
-      </x:c>
-      <x:c r="B71" s="31" t="str">
-        <x:v>telegram export/photos/photo_43@27-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-      <x:c r="C71" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D71" s="31" t="n">
-        <x:v>85618</x:v>
-      </x:c>
-      <x:c r="E71" s="31" t="str">
-        <x:v>35428512edee92243496c3104d792d4fd07c6d43257d697c19937ccfa0a98517</x:v>
-      </x:c>
-      <x:c r="F71" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G71" s="31" t="str">
-        <x:v>TX0054</x:v>
-      </x:c>
-      <x:c r="H71" s="31" t="str">
-        <x:v>message157</x:v>
-      </x:c>
-      <x:c r="I71" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J71" s="31" t="str"/>
-      <x:c r="K71" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_43%4027-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="15" hidden="0" customHeight="1">
-      <x:c r="A72" s="31" t="str">
-        <x:v>SRC068</x:v>
-      </x:c>
-      <x:c r="B72" s="31" t="str">
-        <x:v>telegram export/photos/photo_44@27-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-      <x:c r="C72" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D72" s="31" t="n">
-        <x:v>85772</x:v>
-      </x:c>
-      <x:c r="E72" s="31" t="str">
-        <x:v>552ed592df76565fdf834836abf1da6c4b9784e66039b1efaa36e162e69d855b</x:v>
-      </x:c>
-      <x:c r="F72" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G72" s="31" t="str">
-        <x:v>TX0055</x:v>
-      </x:c>
-      <x:c r="H72" s="31" t="str">
-        <x:v>message158</x:v>
-      </x:c>
-      <x:c r="I72" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J72" s="31" t="str"/>
-      <x:c r="K72" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_44%4027-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="15" hidden="0" customHeight="1">
-      <x:c r="A73" s="31" t="str">
-        <x:v>SRC069</x:v>
-      </x:c>
-      <x:c r="B73" s="31" t="str">
-        <x:v>telegram export/photos/photo_45@27-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-      <x:c r="C73" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D73" s="31" t="n">
-        <x:v>65390</x:v>
-      </x:c>
-      <x:c r="E73" s="31" t="str">
-        <x:v>d3cd5d400ad26b008c54a467ede8e780c9606b0a9a460d51c2e11bf69ede9a39</x:v>
-      </x:c>
-      <x:c r="F73" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G73" s="31" t="str">
-        <x:v>TX0050</x:v>
-      </x:c>
-      <x:c r="H73" s="31" t="str">
-        <x:v>message159</x:v>
-      </x:c>
-      <x:c r="I73" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J73" s="31" t="str"/>
-      <x:c r="K73" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_45%4027-06-2026_18-36-09.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="15" hidden="0" customHeight="1">
-      <x:c r="A74" s="31" t="str">
-        <x:v>SRC070</x:v>
-      </x:c>
-      <x:c r="B74" s="31" t="str">
-        <x:v>telegram export/photos/photo_46@27-06-2026_18-38-52.jpg</x:v>
-      </x:c>
-      <x:c r="C74" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D74" s="31" t="n">
-        <x:v>145310</x:v>
-      </x:c>
-      <x:c r="E74" s="31" t="str">
-        <x:v>22c0f55d35b72f746c979bd91c0f23f9862ff7f5a4851ab2293686a796fab727</x:v>
-      </x:c>
-      <x:c r="F74" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G74" s="31" t="str">
-        <x:v>TX0056</x:v>
-      </x:c>
-      <x:c r="H74" s="31" t="str">
-        <x:v>message161</x:v>
-      </x:c>
-      <x:c r="I74" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J74" s="31" t="str"/>
-      <x:c r="K74" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_46%4027-06-2026_18-38-52.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="15" hidden="0" customHeight="1">
-      <x:c r="A75" s="31" t="str">
-        <x:v>SRC071</x:v>
-      </x:c>
-      <x:c r="B75" s="31" t="str">
-        <x:v>telegram export/photos/photo_47@27-06-2026_18-43-30.jpg</x:v>
-      </x:c>
-      <x:c r="C75" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D75" s="31" t="n">
-        <x:v>145095</x:v>
-      </x:c>
-      <x:c r="E75" s="31" t="str">
-        <x:v>65c4560d70bc56c79da398701f9c98c8ae2ffada8d71d2c3e111e2e24ae1cd86</x:v>
-      </x:c>
-      <x:c r="F75" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G75" s="31" t="str">
-        <x:v>TX0057</x:v>
-      </x:c>
-      <x:c r="H75" s="31" t="str">
-        <x:v>message164</x:v>
-      </x:c>
-      <x:c r="I75" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J75" s="31" t="str">
-        <x:v>Duplicate image.</x:v>
-      </x:c>
-      <x:c r="K75" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_47%4027-06-2026_18-43-30.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="15" hidden="0" customHeight="1">
-      <x:c r="A76" s="31" t="str">
-        <x:v>SRC072</x:v>
-      </x:c>
-      <x:c r="B76" s="31" t="str">
-        <x:v>telegram export/photos/photo_48@27-06-2026_18-43-30.jpg</x:v>
-      </x:c>
-      <x:c r="C76" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D76" s="31" t="n">
-        <x:v>64244</x:v>
-      </x:c>
-      <x:c r="E76" s="31" t="str">
-        <x:v>20df96b527f0c957a11188d14f66f9281587d18e0b3e31457b0db70daf899449</x:v>
-      </x:c>
-      <x:c r="F76" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G76" s="31" t="str">
-        <x:v>TX0051</x:v>
-      </x:c>
-      <x:c r="H76" s="31" t="str">
-        <x:v>message165</x:v>
-      </x:c>
-      <x:c r="I76" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J76" s="31" t="str">
-        <x:v>Duplicate image.</x:v>
-      </x:c>
-      <x:c r="K76" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_48%4027-06-2026_18-43-30.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="15" hidden="0" customHeight="1">
-      <x:c r="A77" s="31" t="str">
-        <x:v>SRC073</x:v>
-      </x:c>
-      <x:c r="B77" s="31" t="str">
-        <x:v>telegram export/photos/photo_4@25-07-2025_04-04-24.jpg</x:v>
-      </x:c>
-      <x:c r="C77" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D77" s="31" t="n">
-        <x:v>74199</x:v>
-      </x:c>
-      <x:c r="E77" s="31" t="str">
-        <x:v>5034c1ebaa4bd3c07a59eaf0de3840e0ed1486387ba2b1e9c2832c748b3979a7</x:v>
-      </x:c>
-      <x:c r="F77" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G77" s="31" t="str">
-        <x:v>TX0005</x:v>
-      </x:c>
-      <x:c r="H77" s="31" t="str">
-        <x:v>message29</x:v>
-      </x:c>
-      <x:c r="I77" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J77" s="31" t="str"/>
-      <x:c r="K77" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_4%4025-07-2025_04-04-24.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="15" hidden="0" customHeight="1">
-      <x:c r="A78" s="31" t="str">
-        <x:v>SRC074</x:v>
-      </x:c>
-      <x:c r="B78" s="31" t="str">
-        <x:v>telegram export/photos/photo_5@25-07-2025_04-08-41.jpg</x:v>
-      </x:c>
-      <x:c r="C78" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D78" s="31" t="n">
-        <x:v>74870</x:v>
-      </x:c>
-      <x:c r="E78" s="31" t="str">
-        <x:v>097c6be0efefe88b7e213d3f6aba5f4dc6a9e813bd3aed9162a991d6f68aeb4b</x:v>
-      </x:c>
-      <x:c r="F78" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G78" s="31" t="str">
-        <x:v>TX0006</x:v>
-      </x:c>
-      <x:c r="H78" s="31" t="str">
-        <x:v>message30</x:v>
-      </x:c>
-      <x:c r="I78" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J78" s="31" t="str"/>
-      <x:c r="K78" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_5%4025-07-2025_04-08-41.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="15" hidden="0" customHeight="1">
-      <x:c r="A79" s="31" t="str">
-        <x:v>SRC075</x:v>
-      </x:c>
-      <x:c r="B79" s="31" t="str">
-        <x:v>telegram export/photos/photo_6@25-07-2025_15-53-39.jpg</x:v>
-      </x:c>
-      <x:c r="C79" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D79" s="31" t="n">
-        <x:v>74748</x:v>
-      </x:c>
-      <x:c r="E79" s="31" t="str">
-        <x:v>26c18dafda65ecb48d670d908ff9a6c650df2905684e12dc23e64ef7a00a2547</x:v>
-      </x:c>
-      <x:c r="F79" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G79" s="31" t="str">
-        <x:v>TX0007, TX0008</x:v>
-      </x:c>
-      <x:c r="H79" s="31" t="str">
-        <x:v>message31</x:v>
-      </x:c>
-      <x:c r="I79" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J79" s="31" t="str"/>
-      <x:c r="K79" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_6%4025-07-2025_15-53-39.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="15" hidden="0" customHeight="1">
-      <x:c r="A80" s="31" t="str">
-        <x:v>SRC076</x:v>
-      </x:c>
-      <x:c r="B80" s="31" t="str">
-        <x:v>telegram export/photos/photo_7@11-08-2025_15-51-55.jpg</x:v>
-      </x:c>
-      <x:c r="C80" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D80" s="31" t="n">
-        <x:v>71573</x:v>
-      </x:c>
-      <x:c r="E80" s="31" t="str">
-        <x:v>7cea1f63bcc0623f6f084e71e2aeea383f1f5648bfcdf5e8b6785cc5a6ec980d</x:v>
-      </x:c>
-      <x:c r="F80" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G80" s="31" t="str">
-        <x:v>TX0011</x:v>
-      </x:c>
-      <x:c r="H80" s="31" t="str">
-        <x:v>message42</x:v>
-      </x:c>
-      <x:c r="I80" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J80" s="31" t="str"/>
-      <x:c r="K80" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_7%4011-08-2025_15-51-55.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="15" hidden="0" customHeight="1">
-      <x:c r="A81" s="31" t="str">
-        <x:v>SRC077</x:v>
-      </x:c>
-      <x:c r="B81" s="31" t="str">
-        <x:v>telegram export/photos/photo_8@12-08-2025_09-58-34.jpg</x:v>
-      </x:c>
-      <x:c r="C81" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D81" s="31" t="n">
-        <x:v>74246</x:v>
-      </x:c>
-      <x:c r="E81" s="31" t="str">
-        <x:v>644eada63dc0f6deb5768ffcb5bf455d0cda0ea15dd20247a08aedaf6a6c2863</x:v>
-      </x:c>
-      <x:c r="F81" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G81" s="31" t="str">
-        <x:v>TX0009</x:v>
-      </x:c>
-      <x:c r="H81" s="31" t="str">
-        <x:v>message44</x:v>
-      </x:c>
-      <x:c r="I81" s="31" t="str">
-        <x:v>Extracted</x:v>
-      </x:c>
-      <x:c r="J81" s="31" t="str"/>
-      <x:c r="K81" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_8%4012-08-2025_09-58-34.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="15" hidden="0" customHeight="1">
-      <x:c r="A82" s="31" t="str">
-        <x:v>SRC078</x:v>
-      </x:c>
-      <x:c r="B82" s="31" t="str">
-        <x:v>telegram export/photos/photo_9@12-08-2025_09-58-34.jpg</x:v>
-      </x:c>
-      <x:c r="C82" s="31" t="str">
-        <x:v>jpg</x:v>
-      </x:c>
-      <x:c r="D82" s="31" t="n">
-        <x:v>254809</x:v>
-      </x:c>
-      <x:c r="E82" s="31" t="str">
-        <x:v>5c47322f7a512fb80b48f0044a38ac5a9222176efd200637dbdac21211145ca5</x:v>
-      </x:c>
-      <x:c r="F82" s="31" t="str">
-        <x:v>Read</x:v>
-      </x:c>
-      <x:c r="G82" s="31" t="str">
-        <x:v>TX0009</x:v>
-      </x:c>
-      <x:c r="H82" s="31" t="str">
-        <x:v>message46</x:v>
-      </x:c>
-      <x:c r="I82" s="31" t="str">
-        <x:v>Context only</x:v>
-      </x:c>
-      <x:c r="J82" s="31" t="str">
-        <x:v>Ad screenshot; no transaction.</x:v>
-      </x:c>
-      <x:c r="K82" s="31" t="str">
-        <x:v>https://github.com/SireJeff/anjoman-accounting/blob/6a005a29ab910c0599fc061d27ea33fcbf7aa5d7/telegram%20export/photos/photo_9%4012-08-2025_09-58-34.jpg</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08a5715841384b6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9cbf4759baa4eb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Anjoman accounting - refined.xlsx
+++ b/Anjoman accounting - refined.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4a9f4271ec614551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly report" sheetId="2" r:id="R63cce25b3d4c4c0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project report" sheetId="3" r:id="Rb430486f56924b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category report" sheetId="4" r:id="R227ce80cdd234da4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructor payments" sheetId="5" r:id="R101d2ef863814210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original reconciliation" sheetId="6" r:id="R4bfe70809c4e4662"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="7" r:id="Rd5c3ba573aa249db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="8" r:id="R858a50cfac1d461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review items" sheetId="9" r:id="R3518424ddf3d4f0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence register" sheetId="10" r:id="Re33b57dd606547a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram messages" sheetId="11" r:id="R172e6d085a944565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original records" sheetId="12" r:id="Rae202dfdac2b4cb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="13" r:id="R81e80365f50b4c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc1c63eeb9adb4c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly report" sheetId="2" r:id="Ra817098cd0ac4f79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project report" sheetId="3" r:id="R25d0897a8d5b4bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category report" sheetId="4" r:id="Redd5d58e56694769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructor payments" sheetId="5" r:id="R961148af21bf4f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original reconciliation" sheetId="6" r:id="R9a0f560a77024b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="7" r:id="R0de0e650211f489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoices" sheetId="8" r:id="Rbe296708a34d497a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review items" sheetId="9" r:id="R29b050f8b1e4485f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence register" sheetId="10" r:id="R2f7091a5aed54313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram messages" sheetId="11" r:id="R0ae9833c42984309"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original records" sheetId="12" r:id="R6e89d45c901c4f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="13" r:id="R169f3d1f00114fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Website budget" sheetId="14" r:id="R7f4b779fe8c6467e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,12 +26,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <x:numFmt numFmtId="202" formatCode="#,##0"/>
+    <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -79,6 +81,11 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF008000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
   <x:fills count="5">
     <x:fill>
@@ -115,7 +122,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -197,14 +204,46 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -474,7 +513,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R87bb17e6ce894254"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R53c92c6846d5404a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -546,11 +585,23 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="MethodologyTable" displayName="MethodologyTable" ref="A4:B30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:B30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="MethodologyTable" displayName="MethodologyTable" ref="A4:B31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:B31"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Topic"/>
     <x:tableColumn id="2" name="Policy"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="WebsitebudgetTable" displayName="WebsitebudgetTable" ref="A4:C13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:C13"/>
+  <x:tableColumns count="3">
+    <x:tableColumn id="1" name="Measure"/>
+    <x:tableColumn id="2" name="Value"/>
+    <x:tableColumn id="3" name="Basis"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -572,8 +623,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ProjectreportTable" displayName="ProjectreportTable" ref="A4:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:E16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ProjectreportTable" displayName="ProjectreportTable" ref="A4:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:E17"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Project"/>
     <x:tableColumn id="2" name="Receipts (toman)"/>
@@ -586,8 +637,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="CategoryreportTable" displayName="CategoryreportTable" ref="A4:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:E17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="CategoryreportTable" displayName="CategoryreportTable" ref="A4:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:E18"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Category"/>
     <x:tableColumn id="2" name="Receipts (toman)"/>
@@ -635,8 +686,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TransactionsTable" displayName="TransactionsTable" ref="A4:Y99" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:Y99"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TransactionsTable" displayName="TransactionsTable" ref="A4:Y100" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:Y100"/>
   <x:tableColumns count="25">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Gregorian date"/>
@@ -689,8 +740,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="ReviewitemsTable" displayName="ReviewitemsTable" ref="A4:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="ReviewitemsTable" displayName="ReviewitemsTable" ref="A4:H20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H20"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Issue ID"/>
     <x:tableColumn id="2" name="Priority"/>
@@ -941,7 +992,7 @@
         <x:v>Supported cash receipts</x:v>
       </x:c>
       <x:c r="B5" s="19" t="n">
-        <x:f>SUM('Transactions'!$W$5:$W$99)</x:f>
+        <x:f>SUM('Transactions'!$W$5:$W$100)</x:f>
         <x:v>112552000</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
@@ -953,7 +1004,7 @@
         <x:v>Supported cash payments</x:v>
       </x:c>
       <x:c r="B6" s="19" t="n">
-        <x:f>SUM('Transactions'!$X$5:$X$99)</x:f>
+        <x:f>SUM('Transactions'!$X$5:$X$100)</x:f>
         <x:v>99085195</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
@@ -989,7 +1040,7 @@
         <x:v>Receipts awaiting review</x:v>
       </x:c>
       <x:c r="B9" s="19" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$N$5:$N$99,"Review",'Transactions'!$E$5:$E$99,"Receipt")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$N$5:$N$100,"Review",'Transactions'!$E$5:$E$100,"Receipt")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
@@ -1001,8 +1052,8 @@
         <x:v>Payments awaiting review</x:v>
       </x:c>
       <x:c r="B10" s="19" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$N$5:$N$99,"Review",'Transactions'!$E$5:$E$99,"Payment")</x:f>
-        <x:v>8334723.9</x:v>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$N$5:$N$100,"Review",'Transactions'!$E$5:$E$100,"Payment")</x:f>
+        <x:v>11334723.9</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
         <x:v>Excluded from supported totals</x:v>
@@ -1013,7 +1064,7 @@
         <x:v>Unclassified amounts awaiting review</x:v>
       </x:c>
       <x:c r="B11" s="19" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$N$5:$N$99,"Review",'Transactions'!$E$5:$E$99,"Unknown")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$N$5:$N$100,"Review",'Transactions'!$E$5:$E$100,"Unknown")</x:f>
         <x:v>300000</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
@@ -1025,7 +1076,7 @@
         <x:v>Internal transfers</x:v>
       </x:c>
       <x:c r="B12" s="19" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$E$5:$E$99,"Internal transfer",'Transactions'!$N$5:$N$99,"Supported")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$E$5:$E$100,"Internal transfer",'Transactions'!$N$5:$N$100,"Supported")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
@@ -1049,7 +1100,7 @@
         <x:v>Excluded duplicate candidate amounts</x:v>
       </x:c>
       <x:c r="B14" s="19" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$N$5:$N$99,"Duplicate")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$N$5:$N$100,"Duplicate")</x:f>
         <x:v>6129375</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
@@ -1061,7 +1112,7 @@
         <x:v>Supported transaction count</x:v>
       </x:c>
       <x:c r="B15" s="21" t="n">
-        <x:f>COUNTIFS('Transactions'!$N$5:$N$99,"Supported",'Transactions'!$E$5:$E$99,"Receipt")+COUNTIFS('Transactions'!$N$5:$N$99,"Supported",'Transactions'!$E$5:$E$99,"Payment")</x:f>
+        <x:f>COUNTIFS('Transactions'!$N$5:$N$100,"Supported",'Transactions'!$E$5:$E$100,"Receipt")+COUNTIFS('Transactions'!$N$5:$N$100,"Supported",'Transactions'!$E$5:$E$100,"Payment")</x:f>
         <x:v>66</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
@@ -1073,8 +1124,8 @@
         <x:v>Review transaction count</x:v>
       </x:c>
       <x:c r="B16" s="21" t="n">
-        <x:f>COUNTIFS('Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>21</x:v>
+        <x:f>COUNTIFS('Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
         <x:v>Number of ledger records marked Review</x:v>
@@ -1154,7 +1205,7 @@
         <x:v>Former-board handover</x:v>
       </x:c>
       <x:c r="B28" s="30" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,"Opening funds")</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,"Opening funds")</x:f>
         <x:v>11000000</x:v>
       </x:c>
       <x:c r="C28" s="29" t="str">
@@ -1215,6 +1266,53 @@
       </x:c>
       <x:c r="C34" s="29" t="str">
         <x:v>Zahra Amiri payment; excluded from instructor fees</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="27" t="str">
+        <x:v>Association website</x:v>
+      </x:c>
+      <x:c r="B36" s="27" t="str">
+        <x:v>Amount (toman)</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="str">
+        <x:v>Separate from supported cash</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="29" t="str">
+        <x:v>Declared domain purchase</x:v>
+      </x:c>
+      <x:c r="B37" s="30" t="n">
+        <x:f>'Website budget'!B5</x:f>
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="C37" s="29" t="str">
+        <x:v>Date and funding unconfirmed; included in Review only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="29" t="str">
+        <x:v>Three-month VM budget</x:v>
+      </x:c>
+      <x:c r="B38" s="30" t="n">
+        <x:f>'Website budget'!B11</x:f>
+        <x:v>6030048</x:v>
+      </x:c>
+      <x:c r="C38" s="29" t="str">
+        <x:v>92-day estimate; no actual VM payment recorded</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="29" t="str">
+        <x:v>Combined website budget</x:v>
+      </x:c>
+      <x:c r="B39" s="30" t="n">
+        <x:f>'Website budget'!B12</x:f>
+        <x:v>9030048</x:v>
+      </x:c>
+      <x:c r="C39" s="29" t="str">
+        <x:v>Domain plus VM estimate; not a paid total</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1224,7 +1322,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9ed71cc8aab4345"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeb11c1c657f45f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1250,45 +1348,45 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
-      <x:c r="C1" s="33"/>
-      <x:c r="D1" s="33"/>
-      <x:c r="E1" s="33"/>
-      <x:c r="F1" s="33"/>
-      <x:c r="G1" s="33"/>
-      <x:c r="H1" s="33"/>
-      <x:c r="I1" s="33"/>
-      <x:c r="J1" s="33"/>
-      <x:c r="K1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="39"/>
+      <x:c r="I1" s="39"/>
+      <x:c r="J1" s="39"/>
+      <x:c r="K1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Source inventory and extraction coverage</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
-      <x:c r="C2" s="33"/>
-      <x:c r="D2" s="33"/>
-      <x:c r="E2" s="33"/>
-      <x:c r="F2" s="33"/>
-      <x:c r="G2" s="33"/>
-      <x:c r="H2" s="33"/>
-      <x:c r="I2" s="33"/>
-      <x:c r="J2" s="33"/>
-      <x:c r="K2" s="33"/>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="39"/>
+      <x:c r="E2" s="39"/>
+      <x:c r="F2" s="39"/>
+      <x:c r="G2" s="39"/>
+      <x:c r="H2" s="39"/>
+      <x:c r="I2" s="39"/>
+      <x:c r="J2" s="39"/>
+      <x:c r="K2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
-      <x:c r="F3" s="33"/>
-      <x:c r="G3" s="33"/>
-      <x:c r="H3" s="33"/>
-      <x:c r="I3" s="33"/>
-      <x:c r="J3" s="33"/>
-      <x:c r="K3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
+      <x:c r="F3" s="39"/>
+      <x:c r="G3" s="39"/>
+      <x:c r="H3" s="39"/>
+      <x:c r="I3" s="39"/>
+      <x:c r="J3" s="39"/>
+      <x:c r="K3" s="39"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -3897,7 +3995,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R802189b79e394a7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb033ae8a9dc4ec5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3919,33 +4017,33 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
-      <x:c r="C1" s="33"/>
-      <x:c r="D1" s="33"/>
-      <x:c r="E1" s="33"/>
-      <x:c r="F1" s="33"/>
-      <x:c r="G1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Telegram source messages | replies and attachments preserved</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
-      <x:c r="C2" s="33"/>
-      <x:c r="D2" s="33"/>
-      <x:c r="E2" s="33"/>
-      <x:c r="F2" s="33"/>
-      <x:c r="G2" s="33"/>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="39"/>
+      <x:c r="E2" s="39"/>
+      <x:c r="F2" s="39"/>
+      <x:c r="G2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
-      <x:c r="F3" s="33"/>
-      <x:c r="G3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
+      <x:c r="F3" s="39"/>
+      <x:c r="G3" s="39"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -7571,7 +7669,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f60271f93344373"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c0ae5c88bb348bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7591,27 +7689,27 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
-      <x:c r="C1" s="33"/>
-      <x:c r="D1" s="33"/>
-      <x:c r="E1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+      <x:c r="E1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Original workbook cells | unchanged source snapshots</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
-      <x:c r="C2" s="33"/>
-      <x:c r="D2" s="33"/>
-      <x:c r="E2" s="33"/>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="39"/>
+      <x:c r="E2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -53440,7 +53538,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729c94d5ac7a42bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a32414ed50c48cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53457,18 +53555,18 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Accounting basis, definitions and refresh instructions</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
+      <x:c r="B2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -53684,6 +53782,14 @@
       </x:c>
       <x:c r="B30" s="31" t="str">
         <x:v>User-confirmation revision: all recipts/ images are association expenses. Provisional transfers and the photographed invoice are treated as settled only on explicit user attestation; their original source limitations remain visible. The folder duplicate is retained and excluded. Five Summer School 1405 payments are identified; the sixth is not inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="24" hidden="0" customHeight="1">
+      <x:c r="A31" s="31" t="str">
+        <x:v>Policy 13</x:v>
+      </x:c>
+      <x:c r="B31" s="31" t="str">
+        <x:v>Website costs: the domain is a user-declared 3,000,000 toman expense with unknown purchase date and funding source, held outside cutoff supported cash totals. The VM is a 92-day budget at 655,440 rial per day; projections are not actual payments.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -53692,7 +53798,328 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00da56e4d26f4d9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96fbe383ba93417b"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFEDF2F7"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="105" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="29"/>
+      <x:c r="E1" s="29"/>
+    </x:row>
+    <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="40" t="str">
+        <x:v>Association website: declared domain expense and VM forecast</x:v>
+      </x:c>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="29"/>
+      <x:c r="E2" s="29"/>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="29"/>
+      <x:c r="E3" s="29"/>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="7" t="str">
+        <x:v>Measure</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>Basis</x:v>
+      </x:c>
+      <x:c r="D4" s="29"/>
+      <x:c r="E4" s="29"/>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="31" t="str">
+        <x:v>Declared domain cost (toman)</x:v>
+      </x:c>
+      <x:c r="B5" s="41" t="n">
+        <x:f>'Transactions'!H100</x:f>
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>User-declared purchase; date and funding unknown; TX0096 excluded from supported cash</x:v>
+      </x:c>
+      <x:c r="D5" s="29"/>
+      <x:c r="E5" s="29"/>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="31" t="str">
+        <x:v>Daily VM rate (rial)</x:v>
+      </x:c>
+      <x:c r="B6" s="42" t="n">
+        <x:v>655440</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>User quotation; editable rate</x:v>
+      </x:c>
+      <x:c r="D6" s="29"/>
+      <x:c r="E6" s="29"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="31" t="str">
+        <x:v>Daily VM rate (toman)</x:v>
+      </x:c>
+      <x:c r="B7" s="43" t="n">
+        <x:f>IF(ISNUMBER(B6),B6/10,"Unavailable")</x:f>
+        <x:v>65544</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>10 rial = 1 toman</x:v>
+      </x:c>
+      <x:c r="D7" s="29"/>
+      <x:c r="E7" s="29"/>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="31" t="str">
+        <x:v>VM service start</x:v>
+      </x:c>
+      <x:c r="B8" s="44" t="d">
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>1405/05/28 at 22:56 Asia/Tehran</x:v>
+      </x:c>
+      <x:c r="D8" s="29"/>
+      <x:c r="E8" s="29"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="31" t="str">
+        <x:v>Three-month horizon end</x:v>
+      </x:c>
+      <x:c r="B9" s="44" t="d">
+        <x:v>2026-11-19T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>1405/08/28 at 22:56 Asia/Tehran</x:v>
+      </x:c>
+      <x:c r="D9" s="29"/>
+      <x:c r="E9" s="29"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="31" t="str">
+        <x:v>Full billable days</x:v>
+      </x:c>
+      <x:c r="B10" s="45" t="n">
+        <x:f>IF(AND(ISNUMBER(B8),ISNUMBER(B9),B9&gt;=B8),B9-B8,"Unavailable")</x:f>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="str">
+        <x:v>End minus start; start included, horizon end excluded</x:v>
+      </x:c>
+      <x:c r="D10" s="29"/>
+      <x:c r="E10" s="29"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="31" t="str">
+        <x:v>Three-month VM forecast (toman)</x:v>
+      </x:c>
+      <x:c r="B11" s="43" t="n">
+        <x:f>IF(AND(ISNUMBER(B7),ISNUMBER(B10)),B7*B10,"Unavailable")</x:f>
+        <x:v>6030048</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="str">
+        <x:v>Budget estimate; no actual VM payments supplied</x:v>
+      </x:c>
+      <x:c r="D11" s="29"/>
+      <x:c r="E11" s="29"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="31" t="str">
+        <x:v>Domain plus VM budget (toman)</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="n">
+        <x:f>IF(AND(ISNUMBER(B5),ISNUMBER(B11)),B5+B11,"Unavailable")</x:f>
+        <x:v>9030048</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>Declared domain cost plus modelled VM cost; not cash paid</x:v>
+      </x:c>
+      <x:c r="D12" s="29"/>
+      <x:c r="E12" s="29"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="31" t="str">
+        <x:v>Actual VM payments</x:v>
+      </x:c>
+      <x:c r="B13" s="31" t="str">
+        <x:f>"Unavailable"</x:f>
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="str">
+        <x:v>Unknown; excluded from supported payments</x:v>
+      </x:c>
+      <x:c r="D13" s="29"/>
+      <x:c r="E13" s="29"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="29"/>
+      <x:c r="B14" s="29"/>
+      <x:c r="C14" s="29"/>
+      <x:c r="D14" s="29"/>
+      <x:c r="E14" s="29"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="29"/>
+      <x:c r="B15" s="29"/>
+      <x:c r="C15" s="29"/>
+      <x:c r="D15" s="29"/>
+      <x:c r="E15" s="29"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="29"/>
+      <x:c r="B16" s="29"/>
+      <x:c r="C16" s="29"/>
+      <x:c r="D16" s="29"/>
+      <x:c r="E16" s="29"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="38" t="str">
+        <x:v>Jalali service interval</x:v>
+      </x:c>
+      <x:c r="B17" s="38" t="str">
+        <x:v>Start date</x:v>
+      </x:c>
+      <x:c r="C17" s="38" t="str">
+        <x:v>End date</x:v>
+      </x:c>
+      <x:c r="D17" s="38" t="str">
+        <x:v>Days</x:v>
+      </x:c>
+      <x:c r="E17" s="38" t="str">
+        <x:v>VM forecast (toman)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="29" t="str">
+        <x:v>1405/05/28 to 1405/06/28</x:v>
+      </x:c>
+      <x:c r="B18" s="46" t="n">
+        <x:f>B8</x:f>
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C18" s="46" t="d">
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D18" s="47" t="n">
+        <x:f>C18-B18</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="n">
+        <x:f>D18*$B$7</x:f>
+        <x:v>2031864</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="29" t="str">
+        <x:v>1405/06/28 to 1405/07/28</x:v>
+      </x:c>
+      <x:c r="B19" s="46" t="n">
+        <x:f>C18</x:f>
+        <x:v>46284</x:v>
+      </x:c>
+      <x:c r="C19" s="46" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="D19" s="47" t="n">
+        <x:f>C19-B19</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="n">
+        <x:f>D19*$B$7</x:f>
+        <x:v>2031864</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="29" t="str">
+        <x:v>1405/07/28 to 1405/08/28</x:v>
+      </x:c>
+      <x:c r="B20" s="46" t="n">
+        <x:f>C19</x:f>
+        <x:v>46315</x:v>
+      </x:c>
+      <x:c r="C20" s="46" t="n">
+        <x:f>B9</x:f>
+        <x:v>46345</x:v>
+      </x:c>
+      <x:c r="D20" s="47" t="n">
+        <x:f>C20-B20</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="n">
+        <x:f>D20*$B$7</x:f>
+        <x:v>1966320</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="29"/>
+      <x:c r="B21" s="29"/>
+      <x:c r="C21" s="29"/>
+      <x:c r="D21" s="29"/>
+      <x:c r="E21" s="29"/>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="29"/>
+      <x:c r="B22" s="29"/>
+      <x:c r="C22" s="29"/>
+      <x:c r="D22" s="29"/>
+      <x:c r="E22" s="29"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="29" t="str">
+        <x:v>Fixed-rate scenario only. No tax, fees, credits or downtime assumed. Billing statements are required to establish actual VM costs.</x:v>
+      </x:c>
+      <x:c r="B23" s="29"/>
+      <x:c r="C23" s="29"/>
+      <x:c r="D23" s="29"/>
+      <x:c r="E23" s="29"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="29"/>
+      <x:c r="B24" s="29"/>
+      <x:c r="C24" s="29"/>
+      <x:c r="D24" s="29"/>
+      <x:c r="E24" s="29"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="29"/>
+      <x:c r="B25" s="29"/>
+      <x:c r="C25" s="29"/>
+      <x:c r="D25" s="29"/>
+      <x:c r="E25" s="29"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:C2"/>
+    <x:mergeCell ref="A23:E25"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2cec64cd9f748ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53763,11 +54190,11 @@
         <x:v>1404/04</x:v>
       </x:c>
       <x:c r="B5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A5)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A5)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A5)</x:f>
         <x:v>400000</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
@@ -53779,7 +54206,7 @@
         <x:v>-400000</x:v>
       </x:c>
       <x:c r="F5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A5,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A5,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -53788,11 +54215,11 @@
         <x:v>1404/05</x:v>
       </x:c>
       <x:c r="B6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A6)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A6)</x:f>
         <x:v>33642000</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A6)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A6)</x:f>
         <x:v>13250900</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
@@ -53804,7 +54231,7 @@
         <x:v>19991100</x:v>
       </x:c>
       <x:c r="F6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A6,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A6,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>400000</x:v>
       </x:c>
     </x:row>
@@ -53813,11 +54240,11 @@
         <x:v>1404/06</x:v>
       </x:c>
       <x:c r="B7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A7)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A7)</x:f>
         <x:v>4920000</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A7)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A7)</x:f>
         <x:v>3155000</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
@@ -53829,7 +54256,7 @@
         <x:v>21756100</x:v>
       </x:c>
       <x:c r="F7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A7,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A7,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -53838,11 +54265,11 @@
         <x:v>1404/07</x:v>
       </x:c>
       <x:c r="B8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A8)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A8)</x:f>
         <x:v>500000</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A8)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A8)</x:f>
         <x:v>2845225</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
@@ -53854,7 +54281,7 @@
         <x:v>19410875</x:v>
       </x:c>
       <x:c r="F8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A8,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A8,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -53863,11 +54290,11 @@
         <x:v>1404/08</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A9)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A9)</x:f>
         <x:v>11000000</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A9)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A9)</x:f>
         <x:v>10103700</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
@@ -53879,7 +54306,7 @@
         <x:v>20307175</x:v>
       </x:c>
       <x:c r="F9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A9,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A9,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>313000</x:v>
       </x:c>
     </x:row>
@@ -53888,11 +54315,11 @@
         <x:v>1404/09</x:v>
       </x:c>
       <x:c r="B10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A10)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A10)</x:f>
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A10)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A10)</x:f>
         <x:v>1020000</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
@@ -53904,7 +54331,7 @@
         <x:v>42287175</x:v>
       </x:c>
       <x:c r="F10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A10,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A10,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -53913,11 +54340,11 @@
         <x:v>1404/10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A11)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A11)</x:f>
         <x:v>16490000</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A11)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A11)</x:f>
         <x:v>2317000</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
@@ -53929,7 +54356,7 @@
         <x:v>56460175</x:v>
       </x:c>
       <x:c r="F11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A11,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A11,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>7921723.9</x:v>
       </x:c>
     </x:row>
@@ -53938,11 +54365,11 @@
         <x:v>1404/12</x:v>
       </x:c>
       <x:c r="B12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A12)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A12)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A12)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A12)</x:f>
         <x:v>1801220</x:v>
       </x:c>
       <x:c r="D12" s="10" t="n">
@@ -53954,7 +54381,7 @@
         <x:v>54658955</x:v>
       </x:c>
       <x:c r="F12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A12,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A12,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -53963,11 +54390,11 @@
         <x:v>1405/02</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A13)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A13)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A13)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A13)</x:f>
         <x:v>4050000</x:v>
       </x:c>
       <x:c r="D13" s="10" t="n">
@@ -53979,7 +54406,7 @@
         <x:v>50608955</x:v>
       </x:c>
       <x:c r="F13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A13,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A13,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -53988,11 +54415,11 @@
         <x:v>1405/05</x:v>
       </x:c>
       <x:c r="B14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A14)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A14)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A14)</x:f>
         <x:v>11217000</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
@@ -54004,7 +54431,7 @@
         <x:v>39391955</x:v>
       </x:c>
       <x:c r="F14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A14,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A14,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54013,11 +54440,11 @@
         <x:v>1405/06</x:v>
       </x:c>
       <x:c r="B15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A15)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A15)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A15)</x:f>
         <x:v>9150000</x:v>
       </x:c>
       <x:c r="D15" s="10" t="n">
@@ -54029,7 +54456,7 @@
         <x:v>30241955</x:v>
       </x:c>
       <x:c r="F15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A15,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A15,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54038,11 +54465,11 @@
         <x:v>1405/07</x:v>
       </x:c>
       <x:c r="B16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A16)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A16)</x:f>
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="C16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A16)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A16)</x:f>
         <x:v>39775150</x:v>
       </x:c>
       <x:c r="D16" s="10" t="n">
@@ -54054,7 +54481,7 @@
         <x:v>13466805</x:v>
       </x:c>
       <x:c r="F16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A16,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A16,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54063,11 +54490,11 @@
         <x:v>Undated</x:v>
       </x:c>
       <x:c r="B17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$D$5:$D$99,A17)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$D$5:$D$100,A17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$D$5:$D$99,A17)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$D$5:$D$100,A17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="10" t="n">
@@ -54079,8 +54506,8 @@
         <x:v>13466805</x:v>
       </x:c>
       <x:c r="F17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$D$5:$D$99,A17,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>0</x:v>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$D$5:$D$100,A17,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>3000000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -54088,9 +54515,9 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f0135e3e0584163"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a417473ff02407a"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ba6036f48843ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6c81485a7bb4c5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54154,11 +54581,11 @@
         <x:v>Association operations</x:v>
       </x:c>
       <x:c r="B5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A5)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A5)</x:f>
         <x:v>34000000</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A5)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A5)</x:f>
         <x:v>3084700</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
@@ -54166,238 +54593,259 @@
         <x:v>30915300</x:v>
       </x:c>
       <x:c r="E5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A5,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A5,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>13000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
       <x:c r="A6" s="8" t="str">
-        <x:v>Booths 1404</x:v>
+        <x:v>Association website</x:v>
       </x:c>
       <x:c r="B6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A6)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A6)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A6)</x:f>
-        <x:v>1995000</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A6)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
         <x:f>B6-C6</x:f>
-        <x:v>-1995000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A6,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>0</x:v>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A6,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>3000000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
       <x:c r="A7" s="8" t="str">
-        <x:v>Freshman Party 1404</x:v>
+        <x:v>Booths 1404</x:v>
       </x:c>
       <x:c r="B7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A7)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A7)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A7)</x:f>
-        <x:v>5774000</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A7)</x:f>
+        <x:v>1995000</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
         <x:f>B7-C7</x:f>
-        <x:v>-5774000</x:v>
+        <x:v>-1995000</x:v>
       </x:c>
       <x:c r="E7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A7,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>300000</x:v>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A7,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
       <x:c r="A8" s="8" t="str">
-        <x:v>Intro Event 1404</x:v>
+        <x:v>Freshman Party 1404</x:v>
       </x:c>
       <x:c r="B8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A8)</x:f>
-        <x:v>4920000</x:v>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A8)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A8)</x:f>
-        <x:v>3155000</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A8)</x:f>
+        <x:v>5774000</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
         <x:f>B8-C8</x:f>
-        <x:v>1765000</x:v>
+        <x:v>-5774000</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A8,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>0</x:v>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A8,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>300000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="8" t="str">
-        <x:v>Intro Event 1405</x:v>
+        <x:v>Intro Event 1404</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A9)</x:f>
-        <x:v>23000000</x:v>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A9)</x:f>
+        <x:v>4920000</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A9)</x:f>
-        <x:v>5950000</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A9)</x:f>
+        <x:v>3155000</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
         <x:f>B9-C9</x:f>
-        <x:v>17050000</x:v>
+        <x:v>1765000</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A9,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A9,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="8" t="str">
-        <x:v>Professors assembly Mehr</x:v>
+        <x:v>Intro Event 1405</x:v>
       </x:c>
       <x:c r="B10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A10)</x:f>
-        <x:v>500000</x:v>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A10)</x:f>
+        <x:v>23000000</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A10)</x:f>
-        <x:v>1142375</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A10)</x:f>
+        <x:v>5950000</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
         <x:f>B10-C10</x:f>
-        <x:v>-642375</x:v>
+        <x:v>17050000</x:v>
       </x:c>
       <x:c r="E10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A10,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A10,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="8" t="str">
-        <x:v>Summer School 1404</x:v>
+        <x:v>Professors assembly Mehr</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A11)</x:f>
-        <x:v>33642000</x:v>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A11)</x:f>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A11)</x:f>
-        <x:v>12900900</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A11)</x:f>
+        <x:v>1142375</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
         <x:f>B11-C11</x:f>
-        <x:v>20741100</x:v>
+        <x:v>-642375</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A11,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>400000</x:v>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A11,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="8" t="str">
-        <x:v>Summer School 1405</x:v>
+        <x:v>Summer School 1404</x:v>
       </x:c>
       <x:c r="B12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A12)</x:f>
-        <x:v>0</x:v>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A12)</x:f>
+        <x:v>33642000</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A12)</x:f>
-        <x:v>11500000</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A12)</x:f>
+        <x:v>12900900</x:v>
       </x:c>
       <x:c r="D12" s="10" t="n">
         <x:f>B12-C12</x:f>
-        <x:v>-11500000</x:v>
+        <x:v>20741100</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A12,'Transactions'!$N$5:$N$99,"Review")</x:f>
-        <x:v>0</x:v>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A12,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>400000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="8" t="str">
-        <x:v>Tea &amp; Physics society</x:v>
+        <x:v>Summer School 1405</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A13)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A13)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A13)</x:f>
-        <x:v>1702850</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A13)</x:f>
+        <x:v>11500000</x:v>
       </x:c>
       <x:c r="D13" s="10" t="n">
         <x:f>B13-C13</x:f>
-        <x:v>-1702850</x:v>
+        <x:v>-11500000</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A13,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A13,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="8" t="str">
-        <x:v>Unassigned</x:v>
+        <x:v>Tea &amp; Physics society</x:v>
       </x:c>
       <x:c r="B14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A14)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A14)</x:f>
-        <x:v>45513370</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A14)</x:f>
+        <x:v>1702850</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
         <x:f>B14-C14</x:f>
-        <x:v>-45513370</x:v>
+        <x:v>-1702850</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A14,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A14,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
       <x:c r="A15" s="8" t="str">
-        <x:v>Unknown (likely 1405 summer school)</x:v>
+        <x:v>Unassigned</x:v>
       </x:c>
       <x:c r="B15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A15)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A15)</x:f>
-        <x:v>0</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A15)</x:f>
+        <x:v>45513370</x:v>
       </x:c>
       <x:c r="D15" s="10" t="n">
         <x:f>B15-C15</x:f>
-        <x:v>0</x:v>
+        <x:v>-45513370</x:v>
       </x:c>
       <x:c r="E15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A15,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A15,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="8" t="str">
-        <x:v>Yalda 1404</x:v>
+        <x:v>Unknown (likely 1405 summer school)</x:v>
       </x:c>
       <x:c r="B16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$M$5:$M$99,A16)</x:f>
-        <x:v>16490000</x:v>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A16)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$M$5:$M$99,A16)</x:f>
-        <x:v>6367000</x:v>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A16)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="10" t="n">
         <x:f>B16-C16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="10" t="n">
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A16,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="27" customHeight="1">
+      <x:c r="A17" s="8" t="str">
+        <x:v>Yalda 1404</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="n">
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$M$5:$M$100,A17)</x:f>
+        <x:v>16490000</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="n">
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$M$5:$M$100,A17)</x:f>
+        <x:v>6367000</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="n">
+        <x:f>B17-C17</x:f>
         <x:v>10123000</x:v>
       </x:c>
-      <x:c r="E16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$M$5:$M$99,A16,'Transactions'!$N$5:$N$99,"Review")</x:f>
+      <x:c r="E17" s="10" t="n">
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$M$5:$M$100,A17,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>7921723.9</x:v>
       </x:c>
     </x:row>
@@ -54407,7 +54855,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R548e1b0b8dbf4a7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd7d563e0ada4210"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54471,11 +54919,11 @@
         <x:v>Advertising</x:v>
       </x:c>
       <x:c r="B5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A5)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A5)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A5)</x:f>
         <x:v>400000</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
@@ -54483,7 +54931,7 @@
         <x:v>-400000</x:v>
       </x:c>
       <x:c r="E5" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A5,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A5,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>400000</x:v>
       </x:c>
     </x:row>
@@ -54492,11 +54940,11 @@
         <x:v>Bank fees</x:v>
       </x:c>
       <x:c r="B6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A6)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A6)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A6)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A6)</x:f>
         <x:v>900</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
@@ -54504,7 +54952,7 @@
         <x:v>-900</x:v>
       </x:c>
       <x:c r="E6" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A6,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A6,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54513,11 +54961,11 @@
         <x:v>Course fees</x:v>
       </x:c>
       <x:c r="B7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A7)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A7)</x:f>
         <x:v>33642000</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A7)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A7)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
@@ -54525,7 +54973,7 @@
         <x:v>33642000</x:v>
       </x:c>
       <x:c r="E7" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A7,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A7,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54534,11 +54982,11 @@
         <x:v>Donations</x:v>
       </x:c>
       <x:c r="B8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A8)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A8)</x:f>
         <x:v>39990000</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A8)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A8)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
@@ -54546,7 +54994,7 @@
         <x:v>39990000</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A8,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A8,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54555,11 +55003,11 @@
         <x:v>Equipment</x:v>
       </x:c>
       <x:c r="B9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A9)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A9)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A9)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A9)</x:f>
         <x:v>3545000</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
@@ -54567,7 +55015,7 @@
         <x:v>-3545000</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A9,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A9,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54576,11 +55024,11 @@
         <x:v>Events</x:v>
       </x:c>
       <x:c r="B10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A10)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A10)</x:f>
         <x:v>27920000</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A10)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A10)</x:f>
         <x:v>20196000</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
@@ -54588,7 +55036,7 @@
         <x:v>7724000</x:v>
       </x:c>
       <x:c r="E10" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A10,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A10,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>7921723.9</x:v>
       </x:c>
     </x:row>
@@ -54597,11 +55045,11 @@
         <x:v>Hospitality</x:v>
       </x:c>
       <x:c r="B11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A11)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A11)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A11)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A11)</x:f>
         <x:v>12978125</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
@@ -54609,7 +55057,7 @@
         <x:v>-12978125</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A11,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A11,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54618,11 +55066,11 @@
         <x:v>Opening funds</x:v>
       </x:c>
       <x:c r="B12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A12)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A12)</x:f>
         <x:v>11000000</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A12)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A12)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="10" t="n">
@@ -54630,7 +55078,7 @@
         <x:v>11000000</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A12,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A12,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54639,11 +55087,11 @@
         <x:v>Printing</x:v>
       </x:c>
       <x:c r="B13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A13)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A13)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A13)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A13)</x:f>
         <x:v>193600</x:v>
       </x:c>
       <x:c r="D13" s="10" t="n">
@@ -54651,7 +55099,7 @@
         <x:v>-193600</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A13,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A13,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>13000</x:v>
       </x:c>
     </x:row>
@@ -54660,11 +55108,11 @@
         <x:v>Supplies</x:v>
       </x:c>
       <x:c r="B14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A14)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A14)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A14)</x:f>
         <x:v>2246100</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
@@ -54672,7 +55120,7 @@
         <x:v>-2246100</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A14,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A14,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54681,11 +55129,11 @@
         <x:v>Teaching</x:v>
       </x:c>
       <x:c r="B15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A15)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A15)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A15)</x:f>
         <x:v>24000000</x:v>
       </x:c>
       <x:c r="D15" s="10" t="n">
@@ -54693,7 +55141,7 @@
         <x:v>-24000000</x:v>
       </x:c>
       <x:c r="E15" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A15,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A15,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54702,11 +55150,11 @@
         <x:v>Transfers</x:v>
       </x:c>
       <x:c r="B16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A16)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A16)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="10" t="n">
@@ -54714,7 +55162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A16,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A16,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -54723,11 +55171,11 @@
         <x:v>Unclassified</x:v>
       </x:c>
       <x:c r="B17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$W$5:$W$99,'Transactions'!$L$5:$L$99,A17)</x:f>
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$X$5:$X$99,'Transactions'!$L$5:$L$99,A17)</x:f>
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A17)</x:f>
         <x:v>35525470</x:v>
       </x:c>
       <x:c r="D17" s="10" t="n">
@@ -54735,8 +55183,29 @@
         <x:v>-35525470</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
-        <x:f>SUMIFS('Transactions'!$H$5:$H$99,'Transactions'!$L$5:$L$99,A17,'Transactions'!$N$5:$N$99,"Review")</x:f>
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A17,'Transactions'!$N$5:$N$100,"Review")</x:f>
         <x:v>300000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="27" customHeight="1">
+      <x:c r="A18" s="8" t="str">
+        <x:v>Website domain</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="n">
+        <x:f>SUMIFS('Transactions'!$W$5:$W$100,'Transactions'!$L$5:$L$100,A18)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="n">
+        <x:f>SUMIFS('Transactions'!$X$5:$X$100,'Transactions'!$L$5:$L$100,A18)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="n">
+        <x:f>B18-C18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="10" t="n">
+        <x:f>SUMIFS('Transactions'!$H$5:$H$100,'Transactions'!$L$5:$L$100,A18,'Transactions'!$N$5:$N$100,"Review")</x:f>
+        <x:v>3000000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -54745,7 +55214,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0477bb1193294e00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62d2b30e1bc04792"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54771,45 +55240,45 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
-      <x:c r="C1" s="33"/>
-      <x:c r="D1" s="33"/>
-      <x:c r="E1" s="33"/>
-      <x:c r="F1" s="33"/>
-      <x:c r="G1" s="33"/>
-      <x:c r="H1" s="33"/>
-      <x:c r="I1" s="33"/>
-      <x:c r="J1" s="33"/>
-      <x:c r="K1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="39"/>
+      <x:c r="I1" s="39"/>
+      <x:c r="J1" s="39"/>
+      <x:c r="K1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Summer School 1405 instructor payments | five of six identified</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
-      <x:c r="C2" s="33"/>
-      <x:c r="D2" s="33"/>
-      <x:c r="E2" s="33"/>
-      <x:c r="F2" s="33"/>
-      <x:c r="G2" s="33"/>
-      <x:c r="H2" s="33"/>
-      <x:c r="I2" s="33"/>
-      <x:c r="J2" s="33"/>
-      <x:c r="K2" s="33"/>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="39"/>
+      <x:c r="E2" s="39"/>
+      <x:c r="F2" s="39"/>
+      <x:c r="G2" s="39"/>
+      <x:c r="H2" s="39"/>
+      <x:c r="I2" s="39"/>
+      <x:c r="J2" s="39"/>
+      <x:c r="K2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
-      <x:c r="F3" s="33"/>
-      <x:c r="G3" s="33"/>
-      <x:c r="H3" s="33"/>
-      <x:c r="I3" s="33"/>
-      <x:c r="J3" s="33"/>
-      <x:c r="K3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
+      <x:c r="F3" s="39"/>
+      <x:c r="G3" s="39"/>
+      <x:c r="H3" s="39"/>
+      <x:c r="I3" s="39"/>
+      <x:c r="J3" s="39"/>
+      <x:c r="K3" s="39"/>
     </x:row>
     <x:row r="4" ht="24" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -54865,10 +55334,10 @@
       <x:c r="F5" s="31" t="str">
         <x:v>2026-09-21</x:v>
       </x:c>
-      <x:c r="G5" s="35" t="n">
+      <x:c r="G5" s="43" t="n">
         <x:v>600000</x:v>
       </x:c>
-      <x:c r="H5" s="36" t="str">
+      <x:c r="H5" s="48" t="str">
         <x:v>6104</x:v>
       </x:c>
       <x:c r="I5" s="31" t="str">
@@ -54901,10 +55370,10 @@
       <x:c r="F6" s="31" t="str">
         <x:v>2026-09-21</x:v>
       </x:c>
-      <x:c r="G6" s="35" t="n">
+      <x:c r="G6" s="43" t="n">
         <x:v>1200000</x:v>
       </x:c>
-      <x:c r="H6" s="36" t="str">
+      <x:c r="H6" s="48" t="str">
         <x:v>2692</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
@@ -54937,10 +55406,10 @@
       <x:c r="F7" s="31" t="str">
         <x:v>2026-09-21</x:v>
       </x:c>
-      <x:c r="G7" s="35" t="n">
+      <x:c r="G7" s="43" t="n">
         <x:v>2400000</x:v>
       </x:c>
-      <x:c r="H7" s="36" t="str"/>
+      <x:c r="H7" s="48" t="str"/>
       <x:c r="I7" s="31" t="str">
         <x:v>Explicit user confirmation that payment to Alireza was instructor fee for Abolfazl.</x:v>
       </x:c>
@@ -54971,10 +55440,10 @@
       <x:c r="F8" s="31" t="str">
         <x:v>2026-09-23</x:v>
       </x:c>
-      <x:c r="G8" s="35" t="n">
+      <x:c r="G8" s="43" t="n">
         <x:v>4700000</x:v>
       </x:c>
-      <x:c r="H8" s="36" t="str">
+      <x:c r="H8" s="48" t="str">
         <x:v>5740</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
@@ -55007,10 +55476,10 @@
       <x:c r="F9" s="31" t="str">
         <x:v>2026-09-23</x:v>
       </x:c>
-      <x:c r="G9" s="35" t="n">
+      <x:c r="G9" s="43" t="n">
         <x:v>2600000</x:v>
       </x:c>
-      <x:c r="H9" s="36" t="str">
+      <x:c r="H9" s="48" t="str">
         <x:v>6676</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
@@ -55098,7 +55567,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree2b4ec7ce2d4059"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffbc5b7a559045e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55119,30 +55588,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
-      <x:c r="C1" s="33"/>
-      <x:c r="D1" s="33"/>
-      <x:c r="E1" s="33"/>
-      <x:c r="F1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Original ledger rows reconciled to evidence</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
-      <x:c r="C2" s="33"/>
-      <x:c r="D2" s="33"/>
-      <x:c r="E2" s="33"/>
-      <x:c r="F2" s="33"/>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="39"/>
+      <x:c r="E2" s="39"/>
+      <x:c r="F2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
-      <x:c r="F3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
+      <x:c r="F3" s="39"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -55171,7 +55640,7 @@
       <x:c r="B5" s="31" t="str">
         <x:v>B3</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="n">
+      <x:c r="C5" s="43" t="n">
         <x:v>33642000</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
@@ -55191,7 +55660,7 @@
       <x:c r="B6" s="31" t="str">
         <x:v>D2</x:v>
       </x:c>
-      <x:c r="C6" s="35" t="n">
+      <x:c r="C6" s="43" t="n">
         <x:v>3500000</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
@@ -55211,7 +55680,7 @@
       <x:c r="B7" s="31" t="str">
         <x:v>D3</x:v>
       </x:c>
-      <x:c r="C7" s="35" t="n">
+      <x:c r="C7" s="43" t="n">
         <x:v>3000000</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
@@ -55231,7 +55700,7 @@
       <x:c r="B8" s="31" t="str">
         <x:v>D4</x:v>
       </x:c>
-      <x:c r="C8" s="35" t="n">
+      <x:c r="C8" s="43" t="n">
         <x:v>3700000</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
@@ -55251,7 +55720,7 @@
       <x:c r="B9" s="31" t="str">
         <x:v>D5</x:v>
       </x:c>
-      <x:c r="C9" s="35" t="n">
+      <x:c r="C9" s="43" t="n">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
@@ -55271,7 +55740,7 @@
       <x:c r="B10" s="31" t="str">
         <x:v>D6</x:v>
       </x:c>
-      <x:c r="C10" s="35" t="n">
+      <x:c r="C10" s="43" t="n">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
@@ -55291,7 +55760,7 @@
       <x:c r="B11" s="31" t="str">
         <x:v>D7</x:v>
       </x:c>
-      <x:c r="C11" s="35" t="n">
+      <x:c r="C11" s="43" t="n">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
@@ -55311,7 +55780,7 @@
       <x:c r="B12" s="31" t="str">
         <x:v>D8</x:v>
       </x:c>
-      <x:c r="C12" s="35" t="n">
+      <x:c r="C12" s="43" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
@@ -55331,7 +55800,7 @@
       <x:c r="B13" s="31" t="str">
         <x:v>D9</x:v>
       </x:c>
-      <x:c r="C13" s="35" t="n">
+      <x:c r="C13" s="43" t="n">
         <x:v>400000</x:v>
       </x:c>
       <x:c r="D13" s="31" t="str">
@@ -55351,7 +55820,7 @@
       <x:c r="B14" s="31" t="str">
         <x:v>D10</x:v>
       </x:c>
-      <x:c r="C14" s="35" t="n">
+      <x:c r="C14" s="43" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D14" s="31" t="str">
@@ -55371,7 +55840,7 @@
       <x:c r="B15" s="31" t="str">
         <x:v>D11</x:v>
       </x:c>
-      <x:c r="C15" s="35" t="n">
+      <x:c r="C15" s="43" t="n">
         <x:v>750000</x:v>
       </x:c>
       <x:c r="D15" s="31" t="str">
@@ -55391,7 +55860,7 @@
       <x:c r="B16" s="31" t="str">
         <x:v>D12</x:v>
       </x:c>
-      <x:c r="C16" s="35" t="n">
+      <x:c r="C16" s="43" t="n">
         <x:v>400000</x:v>
       </x:c>
       <x:c r="D16" s="31" t="str">
@@ -55411,7 +55880,7 @@
       <x:c r="B17" s="31" t="str">
         <x:v>B15</x:v>
       </x:c>
-      <x:c r="C17" s="35" t="n">
+      <x:c r="C17" s="43" t="n">
         <x:v>4920000</x:v>
       </x:c>
       <x:c r="D17" s="31" t="str">
@@ -55431,7 +55900,7 @@
       <x:c r="B18" s="31" t="str">
         <x:v>D15</x:v>
       </x:c>
-      <x:c r="C18" s="35" t="n">
+      <x:c r="C18" s="43" t="n">
         <x:v>100000</x:v>
       </x:c>
       <x:c r="D18" s="31" t="str">
@@ -55451,7 +55920,7 @@
       <x:c r="B19" s="31" t="str">
         <x:v>D16</x:v>
       </x:c>
-      <x:c r="C19" s="35" t="n">
+      <x:c r="C19" s="43" t="n">
         <x:v>2866000</x:v>
       </x:c>
       <x:c r="D19" s="31" t="str">
@@ -55471,7 +55940,7 @@
       <x:c r="B20" s="31" t="str">
         <x:v>D17</x:v>
       </x:c>
-      <x:c r="C20" s="35" t="n">
+      <x:c r="C20" s="43" t="n">
         <x:v>189000</x:v>
       </x:c>
       <x:c r="D20" s="31" t="str">
@@ -55491,7 +55960,7 @@
       <x:c r="B21" s="31" t="str">
         <x:v>B19</x:v>
       </x:c>
-      <x:c r="C21" s="35" t="n">
+      <x:c r="C21" s="43" t="n">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D21" s="31" t="str">
@@ -55511,7 +55980,7 @@
       <x:c r="B22" s="31" t="str">
         <x:v>D19</x:v>
       </x:c>
-      <x:c r="C22" s="35" t="n">
+      <x:c r="C22" s="43" t="n">
         <x:v>90000</x:v>
       </x:c>
       <x:c r="D22" s="31" t="str">
@@ -55531,7 +56000,7 @@
       <x:c r="B23" s="31" t="str">
         <x:v>D20</x:v>
       </x:c>
-      <x:c r="C23" s="35" t="n">
+      <x:c r="C23" s="43" t="n">
         <x:v>1052375</x:v>
       </x:c>
       <x:c r="D23" s="31" t="str">
@@ -55551,7 +56020,7 @@
       <x:c r="B24" s="31" t="str">
         <x:v>D21</x:v>
       </x:c>
-      <x:c r="C24" s="35" t="n">
+      <x:c r="C24" s="43" t="n">
         <x:v>790000</x:v>
       </x:c>
       <x:c r="D24" s="31" t="str">
@@ -55571,7 +56040,7 @@
       <x:c r="B25" s="31" t="str">
         <x:v>D22</x:v>
       </x:c>
-      <x:c r="C25" s="35" t="n">
+      <x:c r="C25" s="43" t="n">
         <x:v>912850</x:v>
       </x:c>
       <x:c r="D25" s="31" t="str">
@@ -55591,7 +56060,7 @@
       <x:c r="B26" s="31" t="str">
         <x:v>D23</x:v>
       </x:c>
-      <x:c r="C26" s="35" t="n">
+      <x:c r="C26" s="43" t="n">
         <x:v>1052375</x:v>
       </x:c>
       <x:c r="D26" s="31" t="str">
@@ -55611,7 +56080,7 @@
       <x:c r="B27" s="31" t="str">
         <x:v>B25</x:v>
       </x:c>
-      <x:c r="C27" s="35" t="n">
+      <x:c r="C27" s="43" t="n">
         <x:v>11000000</x:v>
       </x:c>
       <x:c r="D27" s="31" t="str">
@@ -55631,7 +56100,7 @@
       <x:c r="B28" s="31" t="str">
         <x:v>D25</x:v>
       </x:c>
-      <x:c r="C28" s="35" t="n">
+      <x:c r="C28" s="43" t="n">
         <x:v>725000</x:v>
       </x:c>
       <x:c r="D28" s="31" t="str">
@@ -55651,7 +56120,7 @@
       <x:c r="B29" s="31" t="str">
         <x:v>D26</x:v>
       </x:c>
-      <x:c r="C29" s="35" t="n">
+      <x:c r="C29" s="43" t="n">
         <x:v>120000</x:v>
       </x:c>
       <x:c r="D29" s="31" t="str">
@@ -55671,7 +56140,7 @@
       <x:c r="B30" s="31" t="str">
         <x:v>D27</x:v>
       </x:c>
-      <x:c r="C30" s="35" t="n">
+      <x:c r="C30" s="43" t="n">
         <x:v>1310000</x:v>
       </x:c>
       <x:c r="D30" s="31" t="str">
@@ -55691,7 +56160,7 @@
       <x:c r="B31" s="31" t="str">
         <x:v>D28</x:v>
       </x:c>
-      <x:c r="C31" s="35" t="n">
+      <x:c r="C31" s="43" t="n">
         <x:v>4344000</x:v>
       </x:c>
       <x:c r="D31" s="31" t="str">
@@ -55711,7 +56180,7 @@
       <x:c r="B32" s="31" t="str">
         <x:v>D29</x:v>
       </x:c>
-      <x:c r="C32" s="35" t="n">
+      <x:c r="C32" s="43" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D32" s="31" t="str">
@@ -55731,7 +56200,7 @@
       <x:c r="B33" s="31" t="str">
         <x:v>D30</x:v>
       </x:c>
-      <x:c r="C33" s="35" t="n">
+      <x:c r="C33" s="43" t="n">
         <x:v>70000</x:v>
       </x:c>
       <x:c r="D33" s="31" t="str">
@@ -55751,7 +56220,7 @@
       <x:c r="B34" s="31" t="str">
         <x:v>D31</x:v>
       </x:c>
-      <x:c r="C34" s="35" t="n">
+      <x:c r="C34" s="43" t="n">
         <x:v>310000</x:v>
       </x:c>
       <x:c r="D34" s="31" t="str">
@@ -55771,7 +56240,7 @@
       <x:c r="B35" s="31" t="str">
         <x:v>D32</x:v>
       </x:c>
-      <x:c r="C35" s="35" t="n">
+      <x:c r="C35" s="43" t="n">
         <x:v>1760000</x:v>
       </x:c>
       <x:c r="D35" s="31" t="str">
@@ -55791,7 +56260,7 @@
       <x:c r="B36" s="31" t="str">
         <x:v>D33</x:v>
       </x:c>
-      <x:c r="C36" s="35" t="n">
+      <x:c r="C36" s="43" t="n">
         <x:v>230000</x:v>
       </x:c>
       <x:c r="D36" s="31" t="str">
@@ -55811,7 +56280,7 @@
       <x:c r="B37" s="31" t="str">
         <x:v>D34</x:v>
       </x:c>
-      <x:c r="C37" s="35" t="n">
+      <x:c r="C37" s="43" t="n">
         <x:v>1226100</x:v>
       </x:c>
       <x:c r="D37" s="31" t="str">
@@ -55831,7 +56300,7 @@
       <x:c r="B38" s="31" t="str">
         <x:v>D35</x:v>
       </x:c>
-      <x:c r="C38" s="35" t="n">
+      <x:c r="C38" s="43" t="n">
         <x:v>2300</x:v>
       </x:c>
       <x:c r="D38" s="31" t="str">
@@ -55851,7 +56320,7 @@
       <x:c r="B39" s="31" t="str">
         <x:v>D36</x:v>
       </x:c>
-      <x:c r="C39" s="35" t="n">
+      <x:c r="C39" s="43" t="n">
         <x:v>1300</x:v>
       </x:c>
       <x:c r="D39" s="31" t="str">
@@ -55871,7 +56340,7 @@
       <x:c r="B40" s="31" t="str">
         <x:v>B38</x:v>
       </x:c>
-      <x:c r="C40" s="35" t="n">
+      <x:c r="C40" s="43" t="n">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="D40" s="31" t="str">
@@ -55891,7 +56360,7 @@
       <x:c r="B41" s="31" t="str">
         <x:v>B39</x:v>
       </x:c>
-      <x:c r="C41" s="35" t="n">
+      <x:c r="C41" s="43" t="n">
         <x:v>7000000</x:v>
       </x:c>
       <x:c r="D41" s="31" t="str">
@@ -55911,7 +56380,7 @@
       <x:c r="B42" s="31" t="str">
         <x:v>B40</x:v>
       </x:c>
-      <x:c r="C42" s="35" t="n">
+      <x:c r="C42" s="43" t="n">
         <x:v>6000000</x:v>
       </x:c>
       <x:c r="D42" s="31" t="str">
@@ -55931,7 +56400,7 @@
       <x:c r="B43" s="31" t="str">
         <x:v>B42</x:v>
       </x:c>
-      <x:c r="C43" s="35" t="n">
+      <x:c r="C43" s="43" t="n">
         <x:v>15790000</x:v>
       </x:c>
       <x:c r="D43" s="31" t="str">
@@ -55951,7 +56420,7 @@
       <x:c r="B44" s="31" t="str">
         <x:v>D42</x:v>
       </x:c>
-      <x:c r="C44" s="35" t="n">
+      <x:c r="C44" s="43" t="n">
         <x:v>2137000</x:v>
       </x:c>
       <x:c r="D44" s="31" t="str">
@@ -55971,7 +56440,7 @@
       <x:c r="B45" s="31" t="str">
         <x:v>B43</x:v>
       </x:c>
-      <x:c r="C45" s="35" t="n">
+      <x:c r="C45" s="43" t="n">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D45" s="31" t="str">
@@ -55991,7 +56460,7 @@
       <x:c r="B46" s="31" t="str">
         <x:v>B45</x:v>
       </x:c>
-      <x:c r="C46" s="35" t="n">
+      <x:c r="C46" s="43" t="n">
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="D46" s="31" t="str">
@@ -56011,7 +56480,7 @@
       <x:c r="B47" s="31" t="str">
         <x:v>D45</x:v>
       </x:c>
-      <x:c r="C47" s="35" t="n">
+      <x:c r="C47" s="43" t="n">
         <x:v>5000000</x:v>
       </x:c>
       <x:c r="D47" s="31" t="str">
@@ -56030,7 +56499,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdd9538190054bb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8088b86e17384170"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -63397,24 +63866,94 @@
         <x:v>-5000000</x:v>
       </x:c>
     </x:row>
+    <x:row r="100" ht="24" hidden="0" customHeight="1">
+      <x:c r="A100" s="8" t="str">
+        <x:v>TX0096</x:v>
+      </x:c>
+      <x:c r="B100" s="9"/>
+      <x:c r="C100" s="8"/>
+      <x:c r="D100" s="8" t="str">
+        <x:v>Undated</x:v>
+      </x:c>
+      <x:c r="E100" s="8" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="F100" s="11" t="n">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="G100" s="12" t="str">
+        <x:v>toman</x:v>
+      </x:c>
+      <x:c r="H100" s="11" t="n">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="I100" s="8" t="str">
+        <x:v>Domain registrar not supplied</x:v>
+      </x:c>
+      <x:c r="J100" s="31" t="str">
+        <x:v>Purchase of alenush.com for the association website; user-declared expense without receipt</x:v>
+      </x:c>
+      <x:c r="K100" s="31" t="str">
+        <x:v>خرید دامنهٔ alenush.com برای وب‌سایت انجمن؛ هزینهٔ اعلام‌شده توسط کاربر، بدون رسید</x:v>
+      </x:c>
+      <x:c r="L100" s="8" t="str">
+        <x:v>Website domain</x:v>
+      </x:c>
+      <x:c r="M100" s="8" t="str">
+        <x:v>Association website</x:v>
+      </x:c>
+      <x:c r="N100" s="8" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="O100" s="8" t="str">
+        <x:v>User declaration dated 2026-10-11; no receipt</x:v>
+      </x:c>
+      <x:c r="P100" s="8" t="str">
+        <x:v>Unknown funding source</x:v>
+      </x:c>
+      <x:c r="Q100" s="8" t="str"/>
+      <x:c r="R100" s="8"/>
+      <x:c r="S100" s="8"/>
+      <x:c r="T100" s="31" t="str">
+        <x:v>Purpose and reported purchase amount confirmed by user. Purchase date, funding source and any reimbursement are unknown; not yet included in the cutoff cash totals.</x:v>
+      </x:c>
+      <x:c r="U100" s="31" t="str">
+        <x:v>The VM creation date is not used as the domain purchase date. Keep the declared domain expense separate from confirmed association cash disbursements until date and funding are clarified.</x:v>
+      </x:c>
+      <x:c r="V100" s="31" t="str">
+        <x:v>reports/2026-10-10/website_user_confirmation_2026-10-11.json</x:v>
+      </x:c>
+      <x:c r="W100" s="13" t="n">
+        <x:f>IF(AND(N100="Supported",E100="Receipt",ISNUMBER(H100)),H100,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X100" s="13" t="n">
+        <x:f>IF(AND(N100="Supported",E100="Payment",ISNUMBER(H100)),H100,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y100" s="13" t="n">
+        <x:f>W100-X100</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="N5:N99">
+  <x:conditionalFormatting sqref="N5:N100">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Review"/>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="N5:N99">
+    <x:dataValidation type="list" sqref="N5:N100">
       <x:formula1>"Supported,Review,Duplicate,Invoice only,Summary only"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E5:E99">
+    <x:dataValidation type="list" sqref="E5:E100">
       <x:formula1>"Receipt,Payment,Internal transfer,Unknown"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ab8608d7634931"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4306b05e5e124627"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -63440,45 +63979,45 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
-      <x:c r="C1" s="33"/>
-      <x:c r="D1" s="33"/>
-      <x:c r="E1" s="33"/>
-      <x:c r="F1" s="33"/>
-      <x:c r="G1" s="33"/>
-      <x:c r="H1" s="33"/>
-      <x:c r="I1" s="33"/>
-      <x:c r="J1" s="33"/>
-      <x:c r="K1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="39"/>
+      <x:c r="I1" s="39"/>
+      <x:c r="J1" s="39"/>
+      <x:c r="K1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Supplier invoice and payment matching register</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
-      <x:c r="C2" s="33"/>
-      <x:c r="D2" s="33"/>
-      <x:c r="E2" s="33"/>
-      <x:c r="F2" s="33"/>
-      <x:c r="G2" s="33"/>
-      <x:c r="H2" s="33"/>
-      <x:c r="I2" s="33"/>
-      <x:c r="J2" s="33"/>
-      <x:c r="K2" s="33"/>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="39"/>
+      <x:c r="E2" s="39"/>
+      <x:c r="F2" s="39"/>
+      <x:c r="G2" s="39"/>
+      <x:c r="H2" s="39"/>
+      <x:c r="I2" s="39"/>
+      <x:c r="J2" s="39"/>
+      <x:c r="K2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
-      <x:c r="F3" s="33"/>
-      <x:c r="G3" s="33"/>
-      <x:c r="H3" s="33"/>
-      <x:c r="I3" s="33"/>
-      <x:c r="J3" s="33"/>
-      <x:c r="K3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
+      <x:c r="F3" s="39"/>
+      <x:c r="G3" s="39"/>
+      <x:c r="H3" s="39"/>
+      <x:c r="I3" s="39"/>
+      <x:c r="J3" s="39"/>
+      <x:c r="K3" s="39"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -63529,10 +64068,10 @@
         <x:v>Sony NP-FV50 battery, invoice 15628595</x:v>
       </x:c>
       <x:c r="E5" s="31"/>
-      <x:c r="F5" s="35" t="n">
+      <x:c r="F5" s="43" t="n">
         <x:v>696000</x:v>
       </x:c>
-      <x:c r="G5" s="35" t="n">
+      <x:c r="G5" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="31" t="str">
@@ -63562,10 +64101,10 @@
         <x:v>Shipping and insurance, invoice 12050044</x:v>
       </x:c>
       <x:c r="E6" s="31"/>
-      <x:c r="F6" s="35" t="n">
+      <x:c r="F6" s="43" t="n">
         <x:v>29000</x:v>
       </x:c>
-      <x:c r="G6" s="35" t="n">
+      <x:c r="G6" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
@@ -63595,10 +64134,10 @@
         <x:v>4 balloon glue, invoice 29449</x:v>
       </x:c>
       <x:c r="E7" s="31"/>
-      <x:c r="F7" s="35" t="n">
+      <x:c r="F7" s="43" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="G7" s="35"/>
+      <x:c r="G7" s="43"/>
       <x:c r="H7" s="31" t="str">
         <x:v>TX0037</x:v>
       </x:c>
@@ -63627,10 +64166,10 @@
         <x:v>Balloons, pump, thread, foils; invoice 2935/29350</x:v>
       </x:c>
       <x:c r="E8" s="31"/>
-      <x:c r="F8" s="35" t="n">
+      <x:c r="F8" s="43" t="n">
         <x:v>1310000</x:v>
       </x:c>
-      <x:c r="G8" s="35"/>
+      <x:c r="G8" s="43"/>
       <x:c r="H8" s="31" t="str">
         <x:v>TX0038</x:v>
       </x:c>
@@ -63657,8 +64196,8 @@
         <x:v>Freshman prizes: holders, spinners, bow ties</x:v>
       </x:c>
       <x:c r="E9" s="31"/>
-      <x:c r="F9" s="35"/>
-      <x:c r="G9" s="35"/>
+      <x:c r="F9" s="43"/>
+      <x:c r="G9" s="43"/>
       <x:c r="H9" s="31" t="str">
         <x:v>TX0033</x:v>
       </x:c>
@@ -63686,10 +64225,10 @@
         <x:v>USB flash 32G and earphones</x:v>
       </x:c>
       <x:c r="E10" s="31"/>
-      <x:c r="F10" s="35" t="n">
+      <x:c r="F10" s="43" t="n">
         <x:v>1500000</x:v>
       </x:c>
-      <x:c r="G10" s="35"/>
+      <x:c r="G10" s="43"/>
       <x:c r="H10" s="31" t="str">
         <x:v>TX0034</x:v>
       </x:c>
@@ -63717,10 +64256,10 @@
         <x:v>Pineapple pie and pastry order</x:v>
       </x:c>
       <x:c r="E11" s="31"/>
-      <x:c r="F11" s="35" t="n">
+      <x:c r="F11" s="43" t="n">
         <x:v>1052375</x:v>
       </x:c>
-      <x:c r="G11" s="35"/>
+      <x:c r="G11" s="43"/>
       <x:c r="H11" s="31" t="str">
         <x:v>TX0024</x:v>
       </x:c>
@@ -63748,10 +64287,10 @@
         <x:v>French chocolate cream pastry</x:v>
       </x:c>
       <x:c r="E12" s="31"/>
-      <x:c r="F12" s="35" t="n">
+      <x:c r="F12" s="43" t="n">
         <x:v>912850</x:v>
       </x:c>
-      <x:c r="G12" s="35"/>
+      <x:c r="G12" s="43"/>
       <x:c r="H12" s="31" t="str">
         <x:v>TX0023</x:v>
       </x:c>
@@ -63777,10 +64316,10 @@
         <x:v>7 × 2kg pomegranates</x:v>
       </x:c>
       <x:c r="E13" s="31"/>
-      <x:c r="F13" s="35" t="n">
+      <x:c r="F13" s="43" t="n">
         <x:v>1664700</x:v>
       </x:c>
-      <x:c r="G13" s="35"/>
+      <x:c r="G13" s="43"/>
       <x:c r="H13" s="31" t="str"/>
       <x:c r="I13" s="31" t="str">
         <x:v>Unmatched invoice</x:v>
@@ -63806,10 +64345,10 @@
         <x:v>Jelly powder and cherry syrup</x:v>
       </x:c>
       <x:c r="E14" s="31"/>
-      <x:c r="F14" s="35" t="n">
+      <x:c r="F14" s="43" t="n">
         <x:v>2150000</x:v>
       </x:c>
-      <x:c r="G14" s="35" t="n">
+      <x:c r="G14" s="43" t="n">
         <x:v>195454.5</x:v>
       </x:c>
       <x:c r="H14" s="31" t="str">
@@ -63840,10 +64379,10 @@
         <x:v>Snack receipts C1-C8 (eight slips)</x:v>
       </x:c>
       <x:c r="E15" s="31"/>
-      <x:c r="F15" s="35" t="n">
+      <x:c r="F15" s="43" t="n">
         <x:v>1306700</x:v>
       </x:c>
-      <x:c r="G15" s="35"/>
+      <x:c r="G15" s="43"/>
       <x:c r="H15" s="31" t="str">
         <x:v>TX0064, TX0065, TX0066, TX0067, TX0068, TX0069, TX0072, TX0073</x:v>
       </x:c>
@@ -63871,10 +64410,10 @@
         <x:v>99 Mozmoz snacks</x:v>
       </x:c>
       <x:c r="E16" s="31"/>
-      <x:c r="F16" s="35" t="n">
+      <x:c r="F16" s="43" t="n">
         <x:v>1916640</x:v>
       </x:c>
-      <x:c r="G16" s="35" t="n">
+      <x:c r="G16" s="43" t="n">
         <x:v>174240</x:v>
       </x:c>
       <x:c r="H16" s="31" t="str">
@@ -63904,10 +64443,10 @@
         <x:v>Gala chocolate</x:v>
       </x:c>
       <x:c r="E17" s="31"/>
-      <x:c r="F17" s="35" t="n">
+      <x:c r="F17" s="43" t="n">
         <x:v>135800</x:v>
       </x:c>
-      <x:c r="G17" s="35" t="n">
+      <x:c r="G17" s="43" t="n">
         <x:v>12345.4</x:v>
       </x:c>
       <x:c r="H17" s="31" t="str">
@@ -63935,10 +64474,10 @@
         <x:v>Handwritten, likely chocolate cookies</x:v>
       </x:c>
       <x:c r="E18" s="31"/>
-      <x:c r="F18" s="35" t="n">
+      <x:c r="F18" s="43" t="n">
         <x:v>495000</x:v>
       </x:c>
-      <x:c r="G18" s="35"/>
+      <x:c r="G18" s="43"/>
       <x:c r="H18" s="31" t="str"/>
       <x:c r="I18" s="31" t="str">
         <x:v>Unmatched invoice</x:v>
@@ -63964,10 +64503,10 @@
         <x:v>Skyroom licence + recording, invoice 61150</x:v>
       </x:c>
       <x:c r="E19" s="31"/>
-      <x:c r="F19" s="35" t="n">
+      <x:c r="F19" s="43" t="n">
         <x:v>4257000</x:v>
       </x:c>
-      <x:c r="G19" s="35" t="n">
+      <x:c r="G19" s="43" t="n">
         <x:v>387000</x:v>
       </x:c>
       <x:c r="H19" s="31" t="str"/>
@@ -63995,10 +64534,10 @@
         <x:v>190 dairy drinks and cakes, order 165826</x:v>
       </x:c>
       <x:c r="E20" s="31"/>
-      <x:c r="F20" s="35" t="n">
+      <x:c r="F20" s="43" t="n">
         <x:v>9987900</x:v>
       </x:c>
-      <x:c r="G20" s="35"/>
+      <x:c r="G20" s="43"/>
       <x:c r="H20" s="31" t="str">
         <x:v>TX0089</x:v>
       </x:c>
@@ -64019,7 +64558,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44849797a5ce4847"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb42093059a64c5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -64042,36 +64581,36 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="33"/>
-      <x:c r="B1" s="33"/>
-      <x:c r="C1" s="33"/>
-      <x:c r="D1" s="33"/>
-      <x:c r="E1" s="33"/>
-      <x:c r="F1" s="33"/>
-      <x:c r="G1" s="33"/>
-      <x:c r="H1" s="33"/>
+      <x:c r="A1" s="39"/>
+      <x:c r="B1" s="39"/>
+      <x:c r="C1" s="39"/>
+      <x:c r="D1" s="39"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="39"/>
     </x:row>
     <x:row r="2" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A2" s="34" t="str">
+      <x:c r="A2" s="40" t="str">
         <x:v>Reconciliation issues and required follow-up</x:v>
       </x:c>
-      <x:c r="B2" s="33"/>
-      <x:c r="C2" s="33"/>
-      <x:c r="D2" s="33"/>
-      <x:c r="E2" s="33"/>
-      <x:c r="F2" s="33"/>
-      <x:c r="G2" s="33"/>
-      <x:c r="H2" s="33"/>
+      <x:c r="B2" s="39"/>
+      <x:c r="C2" s="39"/>
+      <x:c r="D2" s="39"/>
+      <x:c r="E2" s="39"/>
+      <x:c r="F2" s="39"/>
+      <x:c r="G2" s="39"/>
+      <x:c r="H2" s="39"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
-      <x:c r="F3" s="33"/>
-      <x:c r="G3" s="33"/>
-      <x:c r="H3" s="33"/>
+      <x:c r="A3" s="39"/>
+      <x:c r="B3" s="39"/>
+      <x:c r="C3" s="39"/>
+      <x:c r="D3" s="39"/>
+      <x:c r="E3" s="39"/>
+      <x:c r="F3" s="39"/>
+      <x:c r="G3" s="39"/>
+      <x:c r="H3" s="39"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -64112,7 +64651,7 @@
       <x:c r="D5" s="31" t="str">
         <x:v>Only fragments are available: receipts, SMS and screenshots. There is no opening balance, and balance snapshots conflict (230,203,965 rial on 1404/05/02; 22,953,913 rial on 1404/07/20; '560,800,163' on 1404/07/22; 22,765,000 in message52; 29,200 in message86). The 560,800,163 and 565,800,163 rial snapshots are mutually consistent with a 5,000,000 rial deposit; their relation to the earlier 22,953,913 snapshot remains unexplained. On 1404/05/03 the balance drop of 9,614,400 rial is 7,394,600 smaller than recorded intervening debits of 17,009,000 rial, requiring inflows or other explanation.</x:v>
       </x:c>
-      <x:c r="E5" s="35"/>
+      <x:c r="E5" s="43"/>
       <x:c r="F5" s="31" t="str"/>
       <x:c r="G5" s="31" t="str">
         <x:v>Obtain full Shahr 400816808774, Sepah 3001254062925 and Blu statements.</x:v>
@@ -64134,7 +64673,7 @@
       <x:c r="D6" s="31" t="str">
         <x:v>User confirms all eleven Blu outflows totaling 33,937,250 are association expenses. Five identified Summer School 1405 fees total 11,500,000; sticker packs cost 950,000. Remaining 21,487,250 requires purpose/project allocation, not income/expense-direction confirmation.</x:v>
       </x:c>
-      <x:c r="E6" s="35" t="n">
+      <x:c r="E6" s="43" t="n">
         <x:v>33937250</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
@@ -64160,7 +64699,7 @@
       <x:c r="D7" s="31" t="str">
         <x:v>User confirms seven Shahr-folder outflows totaling 14,038,220 are association expenses, including TX0061 previously unclassified in direction. Merchant/project allocation remains pending. The unlogged balance movement remains unexplained.</x:v>
       </x:c>
-      <x:c r="E7" s="35" t="n">
+      <x:c r="E7" s="43" t="n">
         <x:v>14038220</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
@@ -64186,7 +64725,7 @@
       <x:c r="D8" s="31" t="str">
         <x:v>Platform gross sales 27,235,000 vs original-ledger receipts 23,000,000 remain unreconciled. Skyroom invoice 4,257,000 remains unmatched. Food invoice 9,987,900 is now user-confirmed paid (TX0089); sticker purchase 950,000 belongs to this event (TX0088). No new registration receipts are inferred.</x:v>
       </x:c>
-      <x:c r="E8" s="35" t="n">
+      <x:c r="E8" s="43" t="n">
         <x:v>4235000</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
@@ -64213,7 +64752,7 @@
       <x:c r="D9" s="31" t="str">
         <x:v>17,650,000 without a unit. As rial (1,765,000 toman) it equals ledger M3 net. Treated as an internal transfer.</x:v>
       </x:c>
-      <x:c r="E9" s="35"/>
+      <x:c r="E9" s="43"/>
       <x:c r="F9" s="31" t="str">
         <x:v>TX0018, TX0014</x:v>
       </x:c>
@@ -64237,7 +64776,7 @@
       <x:c r="D10" s="31" t="str">
         <x:v>مجموع D23 duplicates the D20 pastry (1,052,375). D12 likely duplicates the D9 ad (400,000).</x:v>
       </x:c>
-      <x:c r="E10" s="35" t="n">
+      <x:c r="E10" s="43" t="n">
         <x:v>1452375</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
@@ -64264,7 +64803,7 @@
       <x:c r="D11" s="31" t="str">
         <x:v>message111 reads '300000 cash shabash for the party'. The ledger treats it as an expense (D29), but it could be cash received. This Telegram/workbook item is outside recipts/ and is not resolved by the folder-wide expense confirmation.</x:v>
       </x:c>
-      <x:c r="E11" s="35" t="n">
+      <x:c r="E11" s="43" t="n">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
@@ -64290,7 +64829,7 @@
       <x:c r="D12" s="31" t="str">
         <x:v>Parnian reimbursement 4,050,000 is absent from the original ledger. Printed purchases total 3,359,139.9, or 3,180,139.9 excluding possible C6 duplicate. Including invoice-only Ribar 495,000 gives 3,854,139.9 or 3,675,139.9. These are provisional documentation gaps, not confirmed overpayment. Hossein reimbursement is undocumented. Bardia claims vs payment need a separate bridge.</x:v>
       </x:c>
-      <x:c r="E12" s="35" t="n">
+      <x:c r="E12" s="43" t="n">
         <x:v>4050000</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
@@ -64316,7 +64855,7 @@
       <x:c r="D13" s="31" t="str">
         <x:v>The SMS withdrawal is 100,037,800 in an unprinted unit (10,003,780 toman if rial). Message120 describes expense payments or transfers, not income. It remains unconverted and may overlap recorded expenses. Deposit lines are explicitly rial: 150,000, 500,000 and 1,000,000 toman; they do not sum to the treasurer total 15,790,000. Balances imply unlogged movements.</x:v>
       </x:c>
-      <x:c r="E13" s="35"/>
+      <x:c r="E13" s="43"/>
       <x:c r="F13" s="31" t="str">
         <x:v>TX0049, TX0047</x:v>
       </x:c>
@@ -64340,7 +64879,7 @@
       <x:c r="D14" s="31" t="str">
         <x:v>The receipt shows 235,000; the ledger and message show 230,000.</x:v>
       </x:c>
-      <x:c r="E14" s="35" t="n">
+      <x:c r="E14" s="43" t="n">
         <x:v>5000</x:v>
       </x:c>
       <x:c r="F14" s="31" t="str">
@@ -64366,7 +64905,7 @@
       <x:c r="D15" s="31" t="str">
         <x:v>Transfer fee 900, Dina Zali 180,000, Parnian 4,050,000. The poster print of 13,000 is unmatched.</x:v>
       </x:c>
-      <x:c r="E15" s="35" t="n">
+      <x:c r="E15" s="43" t="n">
         <x:v>4230900</x:v>
       </x:c>
       <x:c r="F15" s="31" t="str">
@@ -64390,7 +64929,7 @@
       <x:c r="D16" s="31" t="str">
         <x:v>Refined تطبیق!B7 is circular (=B6-B7; should be B5-B6). TX-00002 counterparty is wrong. TX-00044 is marked confirmed with no payment. The مرداد sheet omits D10-D12. Sohrab's fee does not follow the 100k rounding rule (2,934→3,000).</x:v>
       </x:c>
-      <x:c r="E16" s="35"/>
+      <x:c r="E16" s="43"/>
       <x:c r="F16" s="31" t="str">
         <x:v>TX0001, TX0002, TX0082</x:v>
       </x:c>
@@ -64414,7 +64953,7 @@
       <x:c r="D17" s="31" t="str">
         <x:v>Moghimi's 10m receipt has no date. The forward header is 1404/08/28 but the ledger month is آذر.</x:v>
       </x:c>
-      <x:c r="E17" s="35" t="n">
+      <x:c r="E17" s="43" t="n">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="F17" s="31" t="str">
@@ -64440,7 +64979,7 @@
       <x:c r="D18" s="31" t="str">
         <x:v>Course reports label 11,601, 12,261 and 9,781 as toman. The printed-unit total is 33,643 toman. A possible thousand-toman scale would total 33,643,000, versus the ledger 33,642,000; that scale is unconfirmed and is used only as a comparison, not additional revenue. Reports contain student phone numbers.</x:v>
       </x:c>
-      <x:c r="E18" s="35" t="n">
+      <x:c r="E18" s="43" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F18" s="31" t="str">
@@ -64466,7 +65005,7 @@
       <x:c r="D19" s="31" t="str">
         <x:v>User states six folder receipts are instructor payments. Five are matched by recipient-name evidence and explicit clarification: TX0083-87, total 11,500,000. TX0088 is explicitly sticker packs, not an instructor fee. The sixth remains unmatched among already recorded folder expenses.</x:v>
       </x:c>
-      <x:c r="E19" s="35"/>
+      <x:c r="E19" s="43"/>
       <x:c r="F19" s="31" t="str">
         <x:v>TX0083, TX0084, TX0085, TX0086, TX0087</x:v>
       </x:c>
@@ -64475,6 +65014,32 @@
       </x:c>
       <x:c r="H19" s="31" t="str">
         <x:v>reports/2026-10-10/user_confirmation_2026-10-10.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="24" hidden="0" customHeight="1">
+      <x:c r="A20" s="31" t="str">
+        <x:v>ISS016</x:v>
+      </x:c>
+      <x:c r="B20" s="31" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="str">
+        <x:v>Website domain payment date and funding source</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="str">
+        <x:v>User reports paying 3,000,000 toman for alenush.com, without a designated receipt. Association purpose is confirmed. The purchase date and whether association or personal funds paid it are unknown. Actual VM payments are also not supplied; the 92-day VM figure is a budget estimate.</x:v>
+      </x:c>
+      <x:c r="E20" s="43" t="n">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="F20" s="31" t="str">
+        <x:v>TX0096</x:v>
+      </x:c>
+      <x:c r="G20" s="31" t="str">
+        <x:v>Record the purchase date and funding account; identify any reimbursement and obtain registrar confirmation if available. Replace VM estimates with actual billing records when supplied.</x:v>
+      </x:c>
+      <x:c r="H20" s="31" t="str">
+        <x:v>reports/2026-10-10/website_user_confirmation_2026-10-11.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -64483,7 +65048,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9cbf4759baa4eb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5621255d72c24ad2"/>
   </x:tableParts>
 </x:worksheet>
 </file>